--- a/словари/переведённые_слова.xlsx
+++ b/словари/переведённые_слова.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD0016D-6AB1-4CE4-B50F-350D259950AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880831DC-BDC9-4DA8-A1FB-9963AD327BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="397">
   <si>
     <t>Абонемент - подписка</t>
   </si>
@@ -107,39 +107,1131 @@
   </si>
   <si>
     <t>хмельной яд</t>
+  </si>
+  <si>
+    <t>хмельного яда</t>
+  </si>
+  <si>
+    <t>алкоголя</t>
+  </si>
+  <si>
+    <t>алкоголю</t>
+  </si>
+  <si>
+    <t>хмельному яду</t>
+  </si>
+  <si>
+    <t>алкоголем</t>
+  </si>
+  <si>
+    <t>хмельным ядом</t>
+  </si>
+  <si>
+    <t>хмельном яде</t>
+  </si>
+  <si>
+    <t>алкоголи</t>
+  </si>
+  <si>
+    <t>алкоголей</t>
+  </si>
+  <si>
+    <t>алкоголям</t>
+  </si>
+  <si>
+    <t>алкоголями</t>
+  </si>
+  <si>
+    <t>алкоголях</t>
+  </si>
+  <si>
+    <t>хмельных ядов</t>
+  </si>
+  <si>
+    <t>хмельным ядам</t>
+  </si>
+  <si>
+    <t>алкоголе</t>
+  </si>
+  <si>
+    <t>хмельные яды</t>
+  </si>
+  <si>
+    <t>хмельными ядами</t>
+  </si>
+  <si>
+    <t>хмельных ядах</t>
+  </si>
+  <si>
+    <t xml:space="preserve">алкогольных </t>
+  </si>
+  <si>
+    <t>алкогольный</t>
+  </si>
+  <si>
+    <t>алкогольного</t>
+  </si>
+  <si>
+    <t>алкогольному</t>
+  </si>
+  <si>
+    <t>алкогольным</t>
+  </si>
+  <si>
+    <t>алкогольными</t>
+  </si>
+  <si>
+    <t>алкогольныом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">алкогольные </t>
+  </si>
+  <si>
+    <t>Аллею</t>
+  </si>
+  <si>
+    <t>Аллея</t>
+  </si>
+  <si>
+    <t>дорожка</t>
+  </si>
+  <si>
+    <t>Аллеи</t>
+  </si>
+  <si>
+    <t>дорожки</t>
+  </si>
+  <si>
+    <t>Аллее</t>
+  </si>
+  <si>
+    <t>Аллеей</t>
+  </si>
+  <si>
+    <t>дорожке</t>
+  </si>
+  <si>
+    <t>дорожкой</t>
+  </si>
+  <si>
+    <t>Аллей</t>
+  </si>
+  <si>
+    <t>Аллеям</t>
+  </si>
+  <si>
+    <t>Аллеями</t>
+  </si>
+  <si>
+    <t>Аллеях</t>
+  </si>
+  <si>
+    <t>дорожкек</t>
+  </si>
+  <si>
+    <t>дорожкам</t>
+  </si>
+  <si>
+    <t>дорожками</t>
+  </si>
+  <si>
+    <t>дорожках</t>
+  </si>
+  <si>
+    <t>Алчность</t>
+  </si>
+  <si>
+    <t>Алчности</t>
+  </si>
+  <si>
+    <t>Алчностью</t>
+  </si>
+  <si>
+    <t>жадность</t>
+  </si>
+  <si>
+    <t>жадности</t>
+  </si>
+  <si>
+    <t>жадностью</t>
+  </si>
+  <si>
+    <t>аминокислот</t>
+  </si>
+  <si>
+    <t>аминокислота</t>
+  </si>
+  <si>
+    <t>аминокислоты</t>
+  </si>
+  <si>
+    <t>аминокислоте</t>
+  </si>
+  <si>
+    <t>аминокислотой</t>
+  </si>
+  <si>
+    <t>органическое соединение</t>
+  </si>
+  <si>
+    <t>органического соединения</t>
+  </si>
+  <si>
+    <t>органическому соединению</t>
+  </si>
+  <si>
+    <t>органическим соединением</t>
+  </si>
+  <si>
+    <t>органическом соединении</t>
+  </si>
+  <si>
+    <t>аминокислотам</t>
+  </si>
+  <si>
+    <t>аминокислотами</t>
+  </si>
+  <si>
+    <t>аминокислотах</t>
+  </si>
+  <si>
+    <t>органические соединения</t>
+  </si>
+  <si>
+    <t>органических соединений</t>
+  </si>
+  <si>
+    <t>органическим соединениям</t>
+  </si>
+  <si>
+    <t>органическими соединениями</t>
+  </si>
+  <si>
+    <t>органических соединениях</t>
+  </si>
+  <si>
+    <t>анус</t>
+  </si>
+  <si>
+    <t>ануса</t>
+  </si>
+  <si>
+    <t>анусу</t>
+  </si>
+  <si>
+    <t>анусом</t>
+  </si>
+  <si>
+    <t>анусе</t>
+  </si>
+  <si>
+    <t>задний проход</t>
+  </si>
+  <si>
+    <t>заднего прохода</t>
+  </si>
+  <si>
+    <t>заднему проходу</t>
+  </si>
+  <si>
+    <t>задним проходом</t>
+  </si>
+  <si>
+    <t>заднем проходе</t>
+  </si>
+  <si>
+    <t>апатия</t>
+  </si>
+  <si>
+    <t>апатии</t>
+  </si>
+  <si>
+    <t>апатией</t>
+  </si>
+  <si>
+    <t>безразличие</t>
+  </si>
+  <si>
+    <t>безразличия</t>
+  </si>
+  <si>
+    <t>безразличию</t>
+  </si>
+  <si>
+    <t>безразличием</t>
+  </si>
+  <si>
+    <t>безразличии</t>
+  </si>
+  <si>
+    <t>апробация</t>
+  </si>
+  <si>
+    <t>апробации</t>
+  </si>
+  <si>
+    <t>апробацией</t>
+  </si>
+  <si>
+    <t>проверка</t>
+  </si>
+  <si>
+    <t>апробацию</t>
+  </si>
+  <si>
+    <t>проверки</t>
+  </si>
+  <si>
+    <t>проверке</t>
+  </si>
+  <si>
+    <t>проверкой</t>
+  </si>
+  <si>
+    <t>апробаций</t>
+  </si>
+  <si>
+    <t>апробациям</t>
+  </si>
+  <si>
+    <t>апробациями</t>
+  </si>
+  <si>
+    <t>апробациямиях</t>
+  </si>
+  <si>
+    <t>проверок</t>
+  </si>
+  <si>
+    <t>проверкам</t>
+  </si>
+  <si>
+    <t>проверками</t>
+  </si>
+  <si>
+    <t>проверках</t>
+  </si>
+  <si>
+    <t>аптеку</t>
+  </si>
+  <si>
+    <t>аптека</t>
+  </si>
+  <si>
+    <t>аптек</t>
+  </si>
+  <si>
+    <t>аптеке</t>
+  </si>
+  <si>
+    <t>аптекой</t>
+  </si>
+  <si>
+    <t>медицинский магазин</t>
+  </si>
+  <si>
+    <t>медицинского магазина</t>
+  </si>
+  <si>
+    <t>медицинскому магазину</t>
+  </si>
+  <si>
+    <t>медицинским магазином</t>
+  </si>
+  <si>
+    <t>медицинском магазине</t>
+  </si>
+  <si>
+    <t>аптеки</t>
+  </si>
+  <si>
+    <t>аптекам</t>
+  </si>
+  <si>
+    <t>аптеками</t>
+  </si>
+  <si>
+    <t>аптеках</t>
+  </si>
+  <si>
+    <t>медицинские магазины</t>
+  </si>
+  <si>
+    <t>медицинских магазинов</t>
+  </si>
+  <si>
+    <t>медицинскийм магазинам</t>
+  </si>
+  <si>
+    <t>медицинскими магазинами</t>
+  </si>
+  <si>
+    <t>медицинских магазинах</t>
+  </si>
+  <si>
+    <t>аркебузы</t>
+  </si>
+  <si>
+    <t>оружие</t>
+  </si>
+  <si>
+    <t>аркебузам</t>
+  </si>
+  <si>
+    <t>аркебузами</t>
+  </si>
+  <si>
+    <t>аркебузах</t>
+  </si>
+  <si>
+    <t>оружия</t>
+  </si>
+  <si>
+    <t>оружию</t>
+  </si>
+  <si>
+    <t>оружием</t>
+  </si>
+  <si>
+    <t>оружии</t>
+  </si>
+  <si>
+    <t>артефакт</t>
+  </si>
+  <si>
+    <t>артефакта</t>
+  </si>
+  <si>
+    <t>артефакту</t>
+  </si>
+  <si>
+    <t>артефактом</t>
+  </si>
+  <si>
+    <t>артефакте</t>
+  </si>
+  <si>
+    <t>артефакты</t>
+  </si>
+  <si>
+    <t>артефактов</t>
+  </si>
+  <si>
+    <t>артефактами</t>
+  </si>
+  <si>
+    <t>артефактах</t>
+  </si>
+  <si>
+    <t>творение</t>
+  </si>
+  <si>
+    <t>творения</t>
+  </si>
+  <si>
+    <t>творению</t>
+  </si>
+  <si>
+    <t>творением</t>
+  </si>
+  <si>
+    <t>творении</t>
+  </si>
+  <si>
+    <t>творений</t>
+  </si>
+  <si>
+    <t>творениям</t>
+  </si>
+  <si>
+    <t>творениях</t>
+  </si>
+  <si>
+    <t>астрофизический</t>
+  </si>
+  <si>
+    <t>звездный</t>
+  </si>
+  <si>
+    <t>астрофизического</t>
+  </si>
+  <si>
+    <t>астрофизическому</t>
+  </si>
+  <si>
+    <t>астрофизическим</t>
+  </si>
+  <si>
+    <t>астрофизическом</t>
+  </si>
+  <si>
+    <t>звездного</t>
+  </si>
+  <si>
+    <t>звездному</t>
+  </si>
+  <si>
+    <t>звездном</t>
+  </si>
+  <si>
+    <t>звездным</t>
+  </si>
+  <si>
+    <t>астрофизические</t>
+  </si>
+  <si>
+    <t>астрофизических</t>
+  </si>
+  <si>
+    <t>астрофизическими</t>
+  </si>
+  <si>
+    <t>звездные</t>
+  </si>
+  <si>
+    <t>звездных</t>
+  </si>
+  <si>
+    <t>звездными</t>
+  </si>
+  <si>
+    <t>асфальтированной</t>
+  </si>
+  <si>
+    <t>асфальтированная</t>
+  </si>
+  <si>
+    <t>асфальтированному</t>
+  </si>
+  <si>
+    <t>асфальтированным</t>
+  </si>
+  <si>
+    <t>асфальтированном</t>
+  </si>
+  <si>
+    <t>атеросклеротическая</t>
+  </si>
+  <si>
+    <t>атеросклеротического</t>
+  </si>
+  <si>
+    <t>атеросклеротическому</t>
+  </si>
+  <si>
+    <t>атеросклеротическим</t>
+  </si>
+  <si>
+    <t>атеросклеротическом</t>
+  </si>
+  <si>
+    <t>атлас</t>
+  </si>
+  <si>
+    <t>атласа</t>
+  </si>
+  <si>
+    <t>атласу</t>
+  </si>
+  <si>
+    <t>атласом</t>
+  </si>
+  <si>
+    <t>атласе</t>
+  </si>
+  <si>
+    <t>атласы</t>
+  </si>
+  <si>
+    <t>атласов</t>
+  </si>
+  <si>
+    <t>атласам</t>
+  </si>
+  <si>
+    <t>атласами</t>
+  </si>
+  <si>
+    <t>атласах</t>
+  </si>
+  <si>
+    <t>карта</t>
+  </si>
+  <si>
+    <t>карты</t>
+  </si>
+  <si>
+    <t>карте</t>
+  </si>
+  <si>
+    <t>картой</t>
+  </si>
+  <si>
+    <t>карт</t>
+  </si>
+  <si>
+    <t>картам</t>
+  </si>
+  <si>
+    <t>картами</t>
+  </si>
+  <si>
+    <t>картах</t>
+  </si>
+  <si>
+    <t>Атлет</t>
+  </si>
+  <si>
+    <t>Атлета</t>
+  </si>
+  <si>
+    <t>Атлету</t>
+  </si>
+  <si>
+    <t>Атлетом</t>
+  </si>
+  <si>
+    <t>Атлете</t>
+  </si>
+  <si>
+    <t>Атлеты</t>
+  </si>
+  <si>
+    <t>Атлетов</t>
+  </si>
+  <si>
+    <t>Атлетам</t>
+  </si>
+  <si>
+    <t>Атлетами</t>
+  </si>
+  <si>
+    <t>Атлетах</t>
+  </si>
+  <si>
+    <t>спортсмен</t>
+  </si>
+  <si>
+    <t>спортсмена</t>
+  </si>
+  <si>
+    <t>спортсмену</t>
+  </si>
+  <si>
+    <t>спортсменом</t>
+  </si>
+  <si>
+    <t>спортсмене</t>
+  </si>
+  <si>
+    <t>спортсмены</t>
+  </si>
+  <si>
+    <t>спортсменов</t>
+  </si>
+  <si>
+    <t>спортсменам</t>
+  </si>
+  <si>
+    <t>спортсменами</t>
+  </si>
+  <si>
+    <t>спортсменах</t>
+  </si>
+  <si>
+    <t>аудит</t>
+  </si>
+  <si>
+    <t>аудита</t>
+  </si>
+  <si>
+    <t>аудиту</t>
+  </si>
+  <si>
+    <t>аудитом</t>
+  </si>
+  <si>
+    <t>аудите</t>
+  </si>
+  <si>
+    <t>аудиты</t>
+  </si>
+  <si>
+    <t>аудитов</t>
+  </si>
+  <si>
+    <t>аудитам</t>
+  </si>
+  <si>
+    <t>аудитами</t>
+  </si>
+  <si>
+    <t>аудитах</t>
+  </si>
+  <si>
+    <t>проверкок</t>
+  </si>
+  <si>
+    <t>эффект</t>
+  </si>
+  <si>
+    <t>эффекта</t>
+  </si>
+  <si>
+    <t>эффекту</t>
+  </si>
+  <si>
+    <t>эффектом</t>
+  </si>
+  <si>
+    <t>эффекте</t>
+  </si>
+  <si>
+    <t>эффекты</t>
+  </si>
+  <si>
+    <t>эффектов</t>
+  </si>
+  <si>
+    <t>эффектам</t>
+  </si>
+  <si>
+    <t>эффектами</t>
+  </si>
+  <si>
+    <t>эффектах</t>
+  </si>
+  <si>
+    <t>результат</t>
+  </si>
+  <si>
+    <t>результата</t>
+  </si>
+  <si>
+    <t>результату</t>
+  </si>
+  <si>
+    <t>результатом</t>
+  </si>
+  <si>
+    <t>результате</t>
+  </si>
+  <si>
+    <t>результаты</t>
+  </si>
+  <si>
+    <t>результатов</t>
+  </si>
+  <si>
+    <t>результатам</t>
+  </si>
+  <si>
+    <t>результатами</t>
+  </si>
+  <si>
+    <t>результатах</t>
+  </si>
+  <si>
+    <t>азровокзал</t>
+  </si>
+  <si>
+    <t>воздушный вокзал</t>
+  </si>
+  <si>
+    <t>азровокзала</t>
+  </si>
+  <si>
+    <t>азровокзалу</t>
+  </si>
+  <si>
+    <t>азровокзалом</t>
+  </si>
+  <si>
+    <t>азровокзале</t>
+  </si>
+  <si>
+    <t>азровокзалы</t>
+  </si>
+  <si>
+    <t>азровокзалов</t>
+  </si>
+  <si>
+    <t>азровокзалам</t>
+  </si>
+  <si>
+    <t>азровокзалами</t>
+  </si>
+  <si>
+    <t>азровокзалах</t>
+  </si>
+  <si>
+    <t>воздушного вокзала</t>
+  </si>
+  <si>
+    <t>воздушному вокзалу</t>
+  </si>
+  <si>
+    <t>воздушным вокзалом</t>
+  </si>
+  <si>
+    <t>воздушном вокзале</t>
+  </si>
+  <si>
+    <t>воздушные вокзалы</t>
+  </si>
+  <si>
+    <t>воздушных вокзалов</t>
+  </si>
+  <si>
+    <t>воздушным вокзалам</t>
+  </si>
+  <si>
+    <t>воздушными вокзалами</t>
+  </si>
+  <si>
+    <t>воздушных вокзалах</t>
+  </si>
+  <si>
+    <t>аэропорт</t>
+  </si>
+  <si>
+    <t>воздушный порт</t>
+  </si>
+  <si>
+    <t>аэропорта</t>
+  </si>
+  <si>
+    <t>аэропорту</t>
+  </si>
+  <si>
+    <t>аэропортом</t>
+  </si>
+  <si>
+    <t>аэропорте</t>
+  </si>
+  <si>
+    <t>аэропорты</t>
+  </si>
+  <si>
+    <t>аэропортов</t>
+  </si>
+  <si>
+    <t>аэропортам</t>
+  </si>
+  <si>
+    <t>аэропортами</t>
+  </si>
+  <si>
+    <t>аэропортах</t>
+  </si>
+  <si>
+    <t>воздушного порта</t>
+  </si>
+  <si>
+    <t>воздушному порту</t>
+  </si>
+  <si>
+    <t>воздушным портом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">воздушном порте </t>
+  </si>
+  <si>
+    <t>воздушные порты</t>
+  </si>
+  <si>
+    <t>воздушных портов</t>
+  </si>
+  <si>
+    <t>воздушным портам</t>
+  </si>
+  <si>
+    <t>воздушными портами</t>
+  </si>
+  <si>
+    <t>воздушных портах</t>
+  </si>
+  <si>
+    <t>антивоенный</t>
+  </si>
+  <si>
+    <t>антивоенного</t>
+  </si>
+  <si>
+    <t>антивоенному</t>
+  </si>
+  <si>
+    <t>антивоенным</t>
+  </si>
+  <si>
+    <t>антивоенном</t>
+  </si>
+  <si>
+    <t>антивоенные</t>
+  </si>
+  <si>
+    <t>антивоенных</t>
+  </si>
+  <si>
+    <t>мирный</t>
+  </si>
+  <si>
+    <t>мирного</t>
+  </si>
+  <si>
+    <t>мирному</t>
+  </si>
+  <si>
+    <t>мирным</t>
+  </si>
+  <si>
+    <t>мирном</t>
+  </si>
+  <si>
+    <t>мирные</t>
+  </si>
+  <si>
+    <t>мирных</t>
+  </si>
+  <si>
+    <t>мирными</t>
+  </si>
+  <si>
+    <t>диктатура</t>
+  </si>
+  <si>
+    <t>демонтаж</t>
+  </si>
+  <si>
+    <t>легализация</t>
+  </si>
+  <si>
+    <t>диктатуры</t>
+  </si>
+  <si>
+    <t>диктатуре</t>
+  </si>
+  <si>
+    <t>диктатурой</t>
+  </si>
+  <si>
+    <t>диктатур</t>
+  </si>
+  <si>
+    <t>диктатурам</t>
+  </si>
+  <si>
+    <t>диктатурами</t>
+  </si>
+  <si>
+    <t>диктатурах</t>
+  </si>
+  <si>
+    <t>демонтажа</t>
+  </si>
+  <si>
+    <t>демонтажу</t>
+  </si>
+  <si>
+    <t>демонтажем</t>
+  </si>
+  <si>
+    <t>демонтаже</t>
+  </si>
+  <si>
+    <t>демонтажы</t>
+  </si>
+  <si>
+    <t>демонтажей</t>
+  </si>
+  <si>
+    <t>демонтажам</t>
+  </si>
+  <si>
+    <t>демонтажами</t>
+  </si>
+  <si>
+    <t>демонтажах</t>
+  </si>
+  <si>
+    <t>легализации</t>
+  </si>
+  <si>
+    <t>легализацией</t>
+  </si>
+  <si>
+    <t>легализаций</t>
+  </si>
+  <si>
+    <t>легализациям</t>
+  </si>
+  <si>
+    <t>легализациях</t>
+  </si>
+  <si>
+    <t>власть</t>
+  </si>
+  <si>
+    <t>власти</t>
+  </si>
+  <si>
+    <t>властью</t>
+  </si>
+  <si>
+    <t>властей</t>
+  </si>
+  <si>
+    <t>властям</t>
+  </si>
+  <si>
+    <t>властями</t>
+  </si>
+  <si>
+    <t>властях</t>
+  </si>
+  <si>
+    <t>снос</t>
+  </si>
+  <si>
+    <t>сноса</t>
+  </si>
+  <si>
+    <t>сносу</t>
+  </si>
+  <si>
+    <t>сносом</t>
+  </si>
+  <si>
+    <t>сносе</t>
+  </si>
+  <si>
+    <t>сносы</t>
+  </si>
+  <si>
+    <t>сносов</t>
+  </si>
+  <si>
+    <t>сносам</t>
+  </si>
+  <si>
+    <t>сносах</t>
+  </si>
+  <si>
+    <t>сносами</t>
+  </si>
+  <si>
+    <t>узаконивание</t>
+  </si>
+  <si>
+    <t>узаконивания</t>
+  </si>
+  <si>
+    <t>узакониванию</t>
+  </si>
+  <si>
+    <t>узакониванием</t>
+  </si>
+  <si>
+    <t>узаконивании</t>
+  </si>
+  <si>
+    <t>узакониваний</t>
+  </si>
+  <si>
+    <t>узакониваниям</t>
+  </si>
+  <si>
+    <t>узакониваниями</t>
+  </si>
+  <si>
+    <t>узакониваниях</t>
+  </si>
+  <si>
+    <t>консультационный</t>
+  </si>
+  <si>
+    <t>консультационного</t>
+  </si>
+  <si>
+    <t>консультационному</t>
+  </si>
+  <si>
+    <t>консультационным</t>
+  </si>
+  <si>
+    <t>консультационном</t>
+  </si>
+  <si>
+    <t>консультационные</t>
+  </si>
+  <si>
+    <t>консультационных</t>
+  </si>
+  <si>
+    <t>консультационными</t>
+  </si>
+  <si>
+    <t>совещательный</t>
+  </si>
+  <si>
+    <t>совещательного</t>
+  </si>
+  <si>
+    <t>совещательному</t>
+  </si>
+  <si>
+    <t>совещательным</t>
+  </si>
+  <si>
+    <t>совещательном</t>
+  </si>
+  <si>
+    <t>совещательные</t>
+  </si>
+  <si>
+    <t>совещательных</t>
+  </si>
+  <si>
+    <t>совещательными</t>
+  </si>
+  <si>
+    <t>релевантен</t>
+  </si>
+  <si>
+    <t>важный</t>
+  </si>
+  <si>
+    <t>важного</t>
+  </si>
+  <si>
+    <t>важному</t>
+  </si>
+  <si>
+    <t>важным</t>
+  </si>
+  <si>
+    <t>важном</t>
+  </si>
+  <si>
+    <t>важные</t>
+  </si>
+  <si>
+    <t>важных</t>
+  </si>
+  <si>
+    <t>важными</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="204"/>
     </font>
     <font>
@@ -163,6 +1255,19 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -184,18 +1289,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -458,67 +1564,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="3"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-    </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-    </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-    </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-    </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-    </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -528,19 +1627,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:C23"/>
+  <dimension ref="A2:C290"/>
   <sheetFormatPr defaultColWidth="12.85546875" defaultRowHeight="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.42578125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="34.5703125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="31.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="35.42578125" style="2" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
@@ -548,10 +1647,10 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
@@ -559,10 +1658,10 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
@@ -570,10 +1669,10 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="s">
@@ -581,10 +1680,10 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
@@ -592,10 +1691,10 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="s">
@@ -603,104 +1702,2195 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>24</v>
+      <c r="B17" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A238" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A252" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A262" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A263" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A264" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A265" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A266" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A267" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A268" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A269" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A270" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A271" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A272" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A273" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A274" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A275" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A276" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A277" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A278" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A279" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B280" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B281" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B282" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B283" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B284" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B285" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B286" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B287" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B288" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="289" spans="2:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B289" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="290" spans="2:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B290" s="2" t="s">
+        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/словари/переведённые_слова.xlsx
+++ b/словари/переведённые_слова.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC9EA13-2CB4-4541-82A6-2474EF8A93CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6E587B-2B9E-4556-9A54-1BA850E9A73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="750" yWindow="1785" windowWidth="18315" windowHeight="11715" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="переведенные слова" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3483" uniqueCount="2419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3556" uniqueCount="2471">
   <si>
     <t>Абонемент - подписка</t>
   </si>
@@ -7286,6 +7286,162 @@
   </si>
   <si>
     <t>кушамах</t>
+  </si>
+  <si>
+    <t>ламинат</t>
+  </si>
+  <si>
+    <t>наклейка</t>
+  </si>
+  <si>
+    <t>ламината</t>
+  </si>
+  <si>
+    <t>ламинату</t>
+  </si>
+  <si>
+    <t>ламинатом</t>
+  </si>
+  <si>
+    <t>ламинате</t>
+  </si>
+  <si>
+    <t>ламинаты</t>
+  </si>
+  <si>
+    <t>ламинатов</t>
+  </si>
+  <si>
+    <t>ламинатам</t>
+  </si>
+  <si>
+    <t>ламинатами</t>
+  </si>
+  <si>
+    <t>ламинатах</t>
+  </si>
+  <si>
+    <t>наклейки</t>
+  </si>
+  <si>
+    <t>наклейке</t>
+  </si>
+  <si>
+    <t>наклейкой</t>
+  </si>
+  <si>
+    <t>наклеек</t>
+  </si>
+  <si>
+    <t>наклейкам</t>
+  </si>
+  <si>
+    <t>наклейками</t>
+  </si>
+  <si>
+    <t>наклейках</t>
+  </si>
+  <si>
+    <t>покрытие</t>
+  </si>
+  <si>
+    <t>покрытия</t>
+  </si>
+  <si>
+    <t>покрытию</t>
+  </si>
+  <si>
+    <t>покрытием</t>
+  </si>
+  <si>
+    <t>покрытии</t>
+  </si>
+  <si>
+    <t>покрытий</t>
+  </si>
+  <si>
+    <t>покрытиями</t>
+  </si>
+  <si>
+    <t>покрытиях</t>
+  </si>
+  <si>
+    <t>ламинирование</t>
+  </si>
+  <si>
+    <t>ламинирования</t>
+  </si>
+  <si>
+    <t>ламинированию</t>
+  </si>
+  <si>
+    <t>ламинированием</t>
+  </si>
+  <si>
+    <t>ламинировании</t>
+  </si>
+  <si>
+    <t>ламинирований</t>
+  </si>
+  <si>
+    <t>ламинированиям</t>
+  </si>
+  <si>
+    <t>ламинированиями</t>
+  </si>
+  <si>
+    <t>ламинированиях</t>
+  </si>
+  <si>
+    <t>ландшафт</t>
+  </si>
+  <si>
+    <t>местность</t>
+  </si>
+  <si>
+    <t>ландшафта</t>
+  </si>
+  <si>
+    <t>ландшафту</t>
+  </si>
+  <si>
+    <t>ландшафтом</t>
+  </si>
+  <si>
+    <t>ландшафте</t>
+  </si>
+  <si>
+    <t>ландшафты</t>
+  </si>
+  <si>
+    <t>ландшафтов</t>
+  </si>
+  <si>
+    <t>ландшафтам</t>
+  </si>
+  <si>
+    <t>ландшафтами</t>
+  </si>
+  <si>
+    <t>ландшафтах</t>
+  </si>
+  <si>
+    <t>местности</t>
+  </si>
+  <si>
+    <t>местностью</t>
+  </si>
+  <si>
+    <t>местностей</t>
+  </si>
+  <si>
+    <t>местностям</t>
+  </si>
+  <si>
+    <t>местностях</t>
+  </si>
+  <si>
+    <t>лигатурами</t>
   </si>
 </sst>
 </file>
@@ -7687,7 +7843,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:C1773"/>
+  <dimension ref="A2:C1810"/>
   <sheetFormatPr defaultColWidth="12.85546875" defaultRowHeight="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.28515625" style="5" customWidth="1"/>
@@ -21652,6 +21808,299 @@
       </c>
       <c r="B1773" s="5" t="s">
         <v>2417</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1774" s="5" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B1774" s="5" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1775" s="5" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B1775" s="5" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1776" s="5" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B1776" s="5" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1777" s="5" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B1777" s="5" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1778" s="5" t="s">
+        <v>2423</v>
+      </c>
+      <c r="B1778" s="5" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1779" s="5" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B1779" s="5" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1780" s="5" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B1780" s="5" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1781" s="5" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B1781" s="5" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1782" s="5" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B1782" s="5" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1783" s="5" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B1783" s="5" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1784" s="5" t="s">
+        <v>2428</v>
+      </c>
+      <c r="B1784" s="5" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1785" s="5" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B1785" s="5" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1786" s="5" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B1786" s="5" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1787" s="5" t="s">
+        <v>2446</v>
+      </c>
+      <c r="B1787" s="5" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1788" s="5" t="s">
+        <v>2447</v>
+      </c>
+      <c r="B1788" s="5" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1789" s="5" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B1789" s="5" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1790" s="5" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B1790" s="5" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1791" s="5" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B1791" s="5" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1792" s="5" t="s">
+        <v>2446</v>
+      </c>
+      <c r="B1792" s="5" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1793" s="5" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B1793" s="5" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1794" s="5" t="s">
+        <v>2451</v>
+      </c>
+      <c r="B1794" s="5" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1795" s="5" t="s">
+        <v>2446</v>
+      </c>
+      <c r="B1795" s="5" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1796" s="5" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B1796" s="5" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1797" s="5" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B1797" s="5" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1798" s="5" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B1798" s="5" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1799" s="5" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B1799" s="5" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1800" s="5" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B1800" s="5" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1801" s="5" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B1801" s="5" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1802" s="5" t="s">
+        <v>2458</v>
+      </c>
+      <c r="B1802" s="5" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1803" s="5" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B1803" s="5" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1804" s="5" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B1804" s="5" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1805" s="5" t="s">
+        <v>2461</v>
+      </c>
+      <c r="B1805" s="5" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1806" s="5" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B1806" s="5" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1807" s="5" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B1807" s="5" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1808" s="5" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B1808" s="5" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1809" s="5" t="s">
+        <v>2464</v>
+      </c>
+      <c r="B1809" s="5" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1810" s="5" t="s">
+        <v>2470</v>
       </c>
     </row>
   </sheetData>

--- a/словари/переведённые_слова.xlsx
+++ b/словари/переведённые_слова.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E5E1F7-5414-46BC-808A-F2B29C9BFEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F13BB254-3908-4350-B14F-AF3E5ABA4C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13500" yWindow="150" windowWidth="14625" windowHeight="14085" tabRatio="831" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13455" yWindow="315" windowWidth="14175" windowHeight="14085" tabRatio="831" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="переведенные слова" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11223" uniqueCount="10186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11820" uniqueCount="10750">
   <si>
     <t>Абонемент - подписка</t>
   </si>
@@ -30591,6 +30591,1698 @@
   </si>
   <si>
     <t>полу криминальных</t>
+  </si>
+  <si>
+    <t>дворецкого</t>
+  </si>
+  <si>
+    <t>дворецкому</t>
+  </si>
+  <si>
+    <t>дворецким</t>
+  </si>
+  <si>
+    <t>дворецком</t>
+  </si>
+  <si>
+    <t>дворецкие</t>
+  </si>
+  <si>
+    <t>дворецких</t>
+  </si>
+  <si>
+    <t>локомотив</t>
+  </si>
+  <si>
+    <t>тепловоз</t>
+  </si>
+  <si>
+    <t>локомотива</t>
+  </si>
+  <si>
+    <t>локомотиву</t>
+  </si>
+  <si>
+    <t>локомотиве</t>
+  </si>
+  <si>
+    <t>локомотивом</t>
+  </si>
+  <si>
+    <t>локомотивный</t>
+  </si>
+  <si>
+    <t>локомотивным</t>
+  </si>
+  <si>
+    <t>локомотивными</t>
+  </si>
+  <si>
+    <t>локомотивных</t>
+  </si>
+  <si>
+    <t>локомотивные</t>
+  </si>
+  <si>
+    <t>локомотивную</t>
+  </si>
+  <si>
+    <t>локомотивному</t>
+  </si>
+  <si>
+    <t>тепловоза</t>
+  </si>
+  <si>
+    <t>тепловозу</t>
+  </si>
+  <si>
+    <t>тепловозе</t>
+  </si>
+  <si>
+    <t>тепловозом</t>
+  </si>
+  <si>
+    <t>тепловозный</t>
+  </si>
+  <si>
+    <t>тепловозным</t>
+  </si>
+  <si>
+    <t>тепловозными</t>
+  </si>
+  <si>
+    <t>тепловозных</t>
+  </si>
+  <si>
+    <t>тепловозные</t>
+  </si>
+  <si>
+    <t>тепловозную</t>
+  </si>
+  <si>
+    <t>тепловозному</t>
+  </si>
+  <si>
+    <t>некритичны</t>
+  </si>
+  <si>
+    <t>некритичен</t>
+  </si>
+  <si>
+    <t>некритичена</t>
+  </si>
+  <si>
+    <t>некритиеная</t>
+  </si>
+  <si>
+    <t>некритичные</t>
+  </si>
+  <si>
+    <t>некритичую</t>
+  </si>
+  <si>
+    <t>некритичный</t>
+  </si>
+  <si>
+    <t>некритичым</t>
+  </si>
+  <si>
+    <t>некритичыми</t>
+  </si>
+  <si>
+    <t>некритичых</t>
+  </si>
+  <si>
+    <t>незначительны</t>
+  </si>
+  <si>
+    <t>незначителен</t>
+  </si>
+  <si>
+    <t>незначительна</t>
+  </si>
+  <si>
+    <t>незначительная</t>
+  </si>
+  <si>
+    <t>незначительные</t>
+  </si>
+  <si>
+    <t>незначительную</t>
+  </si>
+  <si>
+    <t>незначительный</t>
+  </si>
+  <si>
+    <t>незначительным</t>
+  </si>
+  <si>
+    <t>незначительными</t>
+  </si>
+  <si>
+    <t>незначительных</t>
+  </si>
+  <si>
+    <t>тренинг</t>
+  </si>
+  <si>
+    <t>обучение</t>
+  </si>
+  <si>
+    <t>тренинга</t>
+  </si>
+  <si>
+    <t>тренинге</t>
+  </si>
+  <si>
+    <t>тренингу</t>
+  </si>
+  <si>
+    <t>тренингом</t>
+  </si>
+  <si>
+    <t>обучения</t>
+  </si>
+  <si>
+    <t>обучении</t>
+  </si>
+  <si>
+    <t>обучению</t>
+  </si>
+  <si>
+    <t>обучением</t>
+  </si>
+  <si>
+    <t>скидки</t>
+  </si>
+  <si>
+    <t>форам</t>
+  </si>
+  <si>
+    <t>форах</t>
+  </si>
+  <si>
+    <t>скидка</t>
+  </si>
+  <si>
+    <t>скадкам</t>
+  </si>
+  <si>
+    <t>скидках</t>
+  </si>
+  <si>
+    <t>скидку</t>
+  </si>
+  <si>
+    <t>фертильности</t>
+  </si>
+  <si>
+    <t>плодородности</t>
+  </si>
+  <si>
+    <t>фертильность</t>
+  </si>
+  <si>
+    <t>фертильностью</t>
+  </si>
+  <si>
+    <t>фертильный</t>
+  </si>
+  <si>
+    <t>фертильные</t>
+  </si>
+  <si>
+    <t>фертильным</t>
+  </si>
+  <si>
+    <t>фертильных</t>
+  </si>
+  <si>
+    <t>фертильная</t>
+  </si>
+  <si>
+    <t>фертильную</t>
+  </si>
+  <si>
+    <t>фертильному</t>
+  </si>
+  <si>
+    <t>плодородие</t>
+  </si>
+  <si>
+    <t>плодородностью</t>
+  </si>
+  <si>
+    <t>плодородный</t>
+  </si>
+  <si>
+    <t>плодородные</t>
+  </si>
+  <si>
+    <t>плодородным</t>
+  </si>
+  <si>
+    <t>плодородных</t>
+  </si>
+  <si>
+    <t>плодородная</t>
+  </si>
+  <si>
+    <t>плодородную</t>
+  </si>
+  <si>
+    <t>плодородному</t>
+  </si>
+  <si>
+    <t>транспорант</t>
+  </si>
+  <si>
+    <t>транспоранта</t>
+  </si>
+  <si>
+    <t>транспоранту</t>
+  </si>
+  <si>
+    <t>транспоранте</t>
+  </si>
+  <si>
+    <t>транспорантом</t>
+  </si>
+  <si>
+    <t>транспорантов</t>
+  </si>
+  <si>
+    <t>транспорантами</t>
+  </si>
+  <si>
+    <t>транспорантные</t>
+  </si>
+  <si>
+    <t>транспорантный</t>
+  </si>
+  <si>
+    <t>транспорантным</t>
+  </si>
+  <si>
+    <t>транспорантными</t>
+  </si>
+  <si>
+    <t>транспорантных</t>
+  </si>
+  <si>
+    <t>вывешеные</t>
+  </si>
+  <si>
+    <t>вывешеный</t>
+  </si>
+  <si>
+    <t>вывешеным</t>
+  </si>
+  <si>
+    <t>вывешеными</t>
+  </si>
+  <si>
+    <t>вывешеных</t>
+  </si>
+  <si>
+    <t>флудилка</t>
+  </si>
+  <si>
+    <t>болталка</t>
+  </si>
+  <si>
+    <t>флудилки</t>
+  </si>
+  <si>
+    <t>флудилке</t>
+  </si>
+  <si>
+    <t>флудилку</t>
+  </si>
+  <si>
+    <t>флудилкой</t>
+  </si>
+  <si>
+    <t>болталки</t>
+  </si>
+  <si>
+    <t>болталке</t>
+  </si>
+  <si>
+    <t>болталку</t>
+  </si>
+  <si>
+    <t>болталкой</t>
+  </si>
+  <si>
+    <t>комплименты</t>
+  </si>
+  <si>
+    <t>пожелание</t>
+  </si>
+  <si>
+    <t>комплиментов</t>
+  </si>
+  <si>
+    <t>комплиментам</t>
+  </si>
+  <si>
+    <t>комплиментами</t>
+  </si>
+  <si>
+    <t>комплиментах</t>
+  </si>
+  <si>
+    <t>комплиментные</t>
+  </si>
+  <si>
+    <t>комплиментный</t>
+  </si>
+  <si>
+    <t>комплиментным</t>
+  </si>
+  <si>
+    <t>комплиментными</t>
+  </si>
+  <si>
+    <t>комплиментных</t>
+  </si>
+  <si>
+    <t>транжирство</t>
+  </si>
+  <si>
+    <t>расточительство</t>
+  </si>
+  <si>
+    <t>транжирства</t>
+  </si>
+  <si>
+    <t>транжирству</t>
+  </si>
+  <si>
+    <t>транжирстве</t>
+  </si>
+  <si>
+    <t>транжирством</t>
+  </si>
+  <si>
+    <t>транжира</t>
+  </si>
+  <si>
+    <t>транжире</t>
+  </si>
+  <si>
+    <t>транжиру</t>
+  </si>
+  <si>
+    <t>транжирой</t>
+  </si>
+  <si>
+    <t>расточительства</t>
+  </si>
+  <si>
+    <t>расточительству</t>
+  </si>
+  <si>
+    <t>расточительстве</t>
+  </si>
+  <si>
+    <t>расточительством</t>
+  </si>
+  <si>
+    <t>расточитель</t>
+  </si>
+  <si>
+    <t>расточителе</t>
+  </si>
+  <si>
+    <t>расточителю</t>
+  </si>
+  <si>
+    <t>расточителем</t>
+  </si>
+  <si>
+    <t>гламурной</t>
+  </si>
+  <si>
+    <t>яркой</t>
+  </si>
+  <si>
+    <t>гламурный</t>
+  </si>
+  <si>
+    <t>гламурная</t>
+  </si>
+  <si>
+    <t>гламурные</t>
+  </si>
+  <si>
+    <t>гламурное</t>
+  </si>
+  <si>
+    <t>гламурную</t>
+  </si>
+  <si>
+    <t>гламурным</t>
+  </si>
+  <si>
+    <t>гламурных</t>
+  </si>
+  <si>
+    <t>гламурному</t>
+  </si>
+  <si>
+    <t>гламурными</t>
+  </si>
+  <si>
+    <t>яркий</t>
+  </si>
+  <si>
+    <t>яркая</t>
+  </si>
+  <si>
+    <t>яркие</t>
+  </si>
+  <si>
+    <t>яркое</t>
+  </si>
+  <si>
+    <t>яркую</t>
+  </si>
+  <si>
+    <t>ярким</t>
+  </si>
+  <si>
+    <t>ярких</t>
+  </si>
+  <si>
+    <t>яркому</t>
+  </si>
+  <si>
+    <t>яркими</t>
+  </si>
+  <si>
+    <t>афкризм</t>
+  </si>
+  <si>
+    <t>позиционирует</t>
+  </si>
+  <si>
+    <t>обозначать</t>
+  </si>
+  <si>
+    <t>позиционируется</t>
+  </si>
+  <si>
+    <t>позиционируем</t>
+  </si>
+  <si>
+    <t>позиционируете</t>
+  </si>
+  <si>
+    <t>позиционируют</t>
+  </si>
+  <si>
+    <t>позиционируются</t>
+  </si>
+  <si>
+    <t>обозначаться</t>
+  </si>
+  <si>
+    <t>обозначаем</t>
+  </si>
+  <si>
+    <t>обозначаете</t>
+  </si>
+  <si>
+    <t>обозначают</t>
+  </si>
+  <si>
+    <t>обозначаются</t>
+  </si>
+  <si>
+    <t>претендует</t>
+  </si>
+  <si>
+    <t>добивается</t>
+  </si>
+  <si>
+    <t>претендуется</t>
+  </si>
+  <si>
+    <t>претендуем</t>
+  </si>
+  <si>
+    <t>претендуете</t>
+  </si>
+  <si>
+    <t>претендуют</t>
+  </si>
+  <si>
+    <t>претендуются</t>
+  </si>
+  <si>
+    <t>добивает</t>
+  </si>
+  <si>
+    <t>добиваем</t>
+  </si>
+  <si>
+    <t>добиваете</t>
+  </si>
+  <si>
+    <t>добивают</t>
+  </si>
+  <si>
+    <t>добиваются</t>
+  </si>
+  <si>
+    <t>динамит</t>
+  </si>
+  <si>
+    <t>взрывчатка</t>
+  </si>
+  <si>
+    <t>динамита</t>
+  </si>
+  <si>
+    <t>динамиту</t>
+  </si>
+  <si>
+    <t>динамите</t>
+  </si>
+  <si>
+    <t>динамитом</t>
+  </si>
+  <si>
+    <t>динамитами</t>
+  </si>
+  <si>
+    <t>динамиты</t>
+  </si>
+  <si>
+    <t>взрывчатки</t>
+  </si>
+  <si>
+    <t>взрывчатку</t>
+  </si>
+  <si>
+    <t>взрывчатке</t>
+  </si>
+  <si>
+    <t>взрывчаткой</t>
+  </si>
+  <si>
+    <t>взрывчатками</t>
+  </si>
+  <si>
+    <t>алименты</t>
+  </si>
+  <si>
+    <t>долг</t>
+  </si>
+  <si>
+    <t>алиментов</t>
+  </si>
+  <si>
+    <t>алиментам</t>
+  </si>
+  <si>
+    <t>алиментами</t>
+  </si>
+  <si>
+    <t>алиментах</t>
+  </si>
+  <si>
+    <t>долгов</t>
+  </si>
+  <si>
+    <t>долгам</t>
+  </si>
+  <si>
+    <t>долгами</t>
+  </si>
+  <si>
+    <t>долгах</t>
+  </si>
+  <si>
+    <t>понторез</t>
+  </si>
+  <si>
+    <t>хвастун</t>
+  </si>
+  <si>
+    <t>понтореза</t>
+  </si>
+  <si>
+    <t>понторезу</t>
+  </si>
+  <si>
+    <t>понторезе</t>
+  </si>
+  <si>
+    <t>понторезом</t>
+  </si>
+  <si>
+    <t>хвастуна</t>
+  </si>
+  <si>
+    <t>хвастуну</t>
+  </si>
+  <si>
+    <t>хвастуне</t>
+  </si>
+  <si>
+    <t>хвастуном</t>
+  </si>
+  <si>
+    <t>психифизиологии</t>
+  </si>
+  <si>
+    <t>апартаментами</t>
+  </si>
+  <si>
+    <t>жилье</t>
+  </si>
+  <si>
+    <t>апартаменты</t>
+  </si>
+  <si>
+    <t>апартаментов</t>
+  </si>
+  <si>
+    <t>апартаментам</t>
+  </si>
+  <si>
+    <t>апартаментах</t>
+  </si>
+  <si>
+    <t>жилья</t>
+  </si>
+  <si>
+    <t>жильем</t>
+  </si>
+  <si>
+    <t>кузов</t>
+  </si>
+  <si>
+    <t>минивэна</t>
+  </si>
+  <si>
+    <t>минивэну</t>
+  </si>
+  <si>
+    <t>минивэне</t>
+  </si>
+  <si>
+    <t>минивэном</t>
+  </si>
+  <si>
+    <t>кузова</t>
+  </si>
+  <si>
+    <t>кузову</t>
+  </si>
+  <si>
+    <t>кузове</t>
+  </si>
+  <si>
+    <t>кузовом</t>
+  </si>
+  <si>
+    <t>стадион</t>
+  </si>
+  <si>
+    <t>спортплощадка</t>
+  </si>
+  <si>
+    <t>стадиона</t>
+  </si>
+  <si>
+    <t>стадиону</t>
+  </si>
+  <si>
+    <t>стадионе</t>
+  </si>
+  <si>
+    <t>стадионом</t>
+  </si>
+  <si>
+    <t>спортплощадки</t>
+  </si>
+  <si>
+    <t>спортплощадку</t>
+  </si>
+  <si>
+    <t>спортплощадке</t>
+  </si>
+  <si>
+    <t>спортплощадкой</t>
+  </si>
+  <si>
+    <t>тент</t>
+  </si>
+  <si>
+    <t>навес</t>
+  </si>
+  <si>
+    <t>тента</t>
+  </si>
+  <si>
+    <t>тенту</t>
+  </si>
+  <si>
+    <t>тенте</t>
+  </si>
+  <si>
+    <t>тентом</t>
+  </si>
+  <si>
+    <t>тентованный</t>
+  </si>
+  <si>
+    <t>навеса</t>
+  </si>
+  <si>
+    <t>навесу</t>
+  </si>
+  <si>
+    <t>навесе</t>
+  </si>
+  <si>
+    <t>навесом</t>
+  </si>
+  <si>
+    <t>укрытый навес</t>
+  </si>
+  <si>
+    <t>тентованным</t>
+  </si>
+  <si>
+    <t>тентованных</t>
+  </si>
+  <si>
+    <t>тентованные</t>
+  </si>
+  <si>
+    <t>укрытым навесом</t>
+  </si>
+  <si>
+    <t>укрытых навесов</t>
+  </si>
+  <si>
+    <t>укрытые навесы</t>
+  </si>
+  <si>
+    <t>психует</t>
+  </si>
+  <si>
+    <t>волнуется</t>
+  </si>
+  <si>
+    <t>психуют</t>
+  </si>
+  <si>
+    <t>психуете</t>
+  </si>
+  <si>
+    <t>психуем</t>
+  </si>
+  <si>
+    <t>волнуются</t>
+  </si>
+  <si>
+    <t>волнуетесь</t>
+  </si>
+  <si>
+    <t>волнуемся</t>
+  </si>
+  <si>
+    <t>шизанулась</t>
+  </si>
+  <si>
+    <t>сошла с ума</t>
+  </si>
+  <si>
+    <t>шизанулись</t>
+  </si>
+  <si>
+    <t>шизанулся</t>
+  </si>
+  <si>
+    <t>сошли с ума</t>
+  </si>
+  <si>
+    <t>сошел  с ума</t>
+  </si>
+  <si>
+    <t>пассии</t>
+  </si>
+  <si>
+    <t>подруги</t>
+  </si>
+  <si>
+    <t>пассия</t>
+  </si>
+  <si>
+    <t>пассией</t>
+  </si>
+  <si>
+    <t>подруга</t>
+  </si>
+  <si>
+    <t>подругой</t>
+  </si>
+  <si>
+    <t>чайлдфри</t>
+  </si>
+  <si>
+    <t>бездетная</t>
+  </si>
+  <si>
+    <t>смайликов</t>
+  </si>
+  <si>
+    <t>улыбок</t>
+  </si>
+  <si>
+    <t>смайлик</t>
+  </si>
+  <si>
+    <t>смайликам</t>
+  </si>
+  <si>
+    <t>смайликах</t>
+  </si>
+  <si>
+    <t>смайлики</t>
+  </si>
+  <si>
+    <t>смайлика</t>
+  </si>
+  <si>
+    <t>улыбка</t>
+  </si>
+  <si>
+    <t>улыбкам</t>
+  </si>
+  <si>
+    <t>улыбках</t>
+  </si>
+  <si>
+    <t>улыбки</t>
+  </si>
+  <si>
+    <t>обычный</t>
+  </si>
+  <si>
+    <t>обычными</t>
+  </si>
+  <si>
+    <t>обычного</t>
+  </si>
+  <si>
+    <t>обычному</t>
+  </si>
+  <si>
+    <t>обычном</t>
+  </si>
+  <si>
+    <t>обычные</t>
+  </si>
+  <si>
+    <t>обычных</t>
+  </si>
+  <si>
+    <t>обычным</t>
+  </si>
+  <si>
+    <t>экивоков</t>
+  </si>
+  <si>
+    <t>намеков</t>
+  </si>
+  <si>
+    <t>экивок</t>
+  </si>
+  <si>
+    <t>экивокам</t>
+  </si>
+  <si>
+    <t>экивоках</t>
+  </si>
+  <si>
+    <t>экивоками</t>
+  </si>
+  <si>
+    <t>намек</t>
+  </si>
+  <si>
+    <t>намекам</t>
+  </si>
+  <si>
+    <t>намеках</t>
+  </si>
+  <si>
+    <t>намеками</t>
+  </si>
+  <si>
+    <t>френдзонщиц</t>
+  </si>
+  <si>
+    <t>динамщица</t>
+  </si>
+  <si>
+    <t>динамщиц</t>
+  </si>
+  <si>
+    <t>динамщицу</t>
+  </si>
+  <si>
+    <t>динамщице</t>
+  </si>
+  <si>
+    <t>динамщицей</t>
+  </si>
+  <si>
+    <t>лентяйка</t>
+  </si>
+  <si>
+    <t>лентяек</t>
+  </si>
+  <si>
+    <t>лентяйку</t>
+  </si>
+  <si>
+    <t>лентяйке</t>
+  </si>
+  <si>
+    <t>лентяйкой</t>
+  </si>
+  <si>
+    <t>корректуры</t>
+  </si>
+  <si>
+    <t>исправление</t>
+  </si>
+  <si>
+    <t>корректура</t>
+  </si>
+  <si>
+    <t>корректуре</t>
+  </si>
+  <si>
+    <t>корректуру</t>
+  </si>
+  <si>
+    <t>корректурой</t>
+  </si>
+  <si>
+    <t>исправления</t>
+  </si>
+  <si>
+    <t>исправлению</t>
+  </si>
+  <si>
+    <t>исправлением</t>
+  </si>
+  <si>
+    <t>форумчане</t>
+  </si>
+  <si>
+    <t>участники сообщества</t>
+  </si>
+  <si>
+    <t>форумчанам</t>
+  </si>
+  <si>
+    <t>форумчан</t>
+  </si>
+  <si>
+    <t>форумчанах</t>
+  </si>
+  <si>
+    <t>форумчанами</t>
+  </si>
+  <si>
+    <t>участникам сообщества</t>
+  </si>
+  <si>
+    <t>участников сообщества</t>
+  </si>
+  <si>
+    <t>участниках сообщества</t>
+  </si>
+  <si>
+    <t>участниками сообщества</t>
+  </si>
+  <si>
+    <t>хронофагов</t>
+  </si>
+  <si>
+    <t>вешалка</t>
+  </si>
+  <si>
+    <t>фотомоделью</t>
+  </si>
+  <si>
+    <t>вешалки</t>
+  </si>
+  <si>
+    <t>вешалкой</t>
+  </si>
+  <si>
+    <t>мимикрирует</t>
+  </si>
+  <si>
+    <t>притворяется</t>
+  </si>
+  <si>
+    <t>мимикрируем</t>
+  </si>
+  <si>
+    <t>мимикрируют</t>
+  </si>
+  <si>
+    <t>мимикрируются</t>
+  </si>
+  <si>
+    <t>мимикрируешь</t>
+  </si>
+  <si>
+    <t>притворяемся</t>
+  </si>
+  <si>
+    <t>притворяют</t>
+  </si>
+  <si>
+    <t>притворяются</t>
+  </si>
+  <si>
+    <t>притворяешся</t>
+  </si>
+  <si>
+    <t>пассию</t>
+  </si>
+  <si>
+    <t>подругу</t>
+  </si>
+  <si>
+    <t>акцептором</t>
+  </si>
+  <si>
+    <t>получатель</t>
+  </si>
+  <si>
+    <t>получателем</t>
+  </si>
+  <si>
+    <t>акцептор</t>
+  </si>
+  <si>
+    <t>акцептора</t>
+  </si>
+  <si>
+    <t>акцептору</t>
+  </si>
+  <si>
+    <t>акцепторе</t>
+  </si>
+  <si>
+    <t>получателя</t>
+  </si>
+  <si>
+    <t>получателю</t>
+  </si>
+  <si>
+    <t>получателе</t>
+  </si>
+  <si>
+    <t>арбитр</t>
+  </si>
+  <si>
+    <t>судья</t>
+  </si>
+  <si>
+    <t>арбитра</t>
+  </si>
+  <si>
+    <t>арбитру</t>
+  </si>
+  <si>
+    <t>арбитре</t>
+  </si>
+  <si>
+    <t>арбитром</t>
+  </si>
+  <si>
+    <t>судьи</t>
+  </si>
+  <si>
+    <t>судье</t>
+  </si>
+  <si>
+    <t>судьей</t>
+  </si>
+  <si>
+    <t>атаманша</t>
+  </si>
+  <si>
+    <t>начальница</t>
+  </si>
+  <si>
+    <t>атаманши</t>
+  </si>
+  <si>
+    <t>атаманше</t>
+  </si>
+  <si>
+    <t>атаманшу</t>
+  </si>
+  <si>
+    <t>атаманшей</t>
+  </si>
+  <si>
+    <t>начальницы</t>
+  </si>
+  <si>
+    <t>начальнице</t>
+  </si>
+  <si>
+    <t>начальницу</t>
+  </si>
+  <si>
+    <t>начальницей</t>
+  </si>
+  <si>
+    <t>шизофреник</t>
+  </si>
+  <si>
+    <t>сумашедший</t>
+  </si>
+  <si>
+    <t>шизофреником</t>
+  </si>
+  <si>
+    <t>сумашедшим</t>
+  </si>
+  <si>
+    <t>тактильный</t>
+  </si>
+  <si>
+    <t>чувствительный</t>
+  </si>
+  <si>
+    <t>тактильные</t>
+  </si>
+  <si>
+    <t>тактильным</t>
+  </si>
+  <si>
+    <t>тактильными</t>
+  </si>
+  <si>
+    <t>тактильных</t>
+  </si>
+  <si>
+    <t>тактильному</t>
+  </si>
+  <si>
+    <t>тактильного</t>
+  </si>
+  <si>
+    <t>тактильное</t>
+  </si>
+  <si>
+    <t>тактильной</t>
+  </si>
+  <si>
+    <t>тактильном</t>
+  </si>
+  <si>
+    <t>тактильную</t>
+  </si>
+  <si>
+    <t>чувствительные</t>
+  </si>
+  <si>
+    <t>чувствительным</t>
+  </si>
+  <si>
+    <t>чувствительного</t>
+  </si>
+  <si>
+    <t>чувствительное</t>
+  </si>
+  <si>
+    <t>чувствительной</t>
+  </si>
+  <si>
+    <t>чувствительному</t>
+  </si>
+  <si>
+    <t>чувствительном</t>
+  </si>
+  <si>
+    <t>чувствительную</t>
+  </si>
+  <si>
+    <t>чувствительными</t>
+  </si>
+  <si>
+    <t>чувствительных</t>
+  </si>
+  <si>
+    <t>ироничным</t>
+  </si>
+  <si>
+    <t>остроумным</t>
+  </si>
+  <si>
+    <t>ироничный</t>
+  </si>
+  <si>
+    <t>ироничные</t>
+  </si>
+  <si>
+    <t>ироничными</t>
+  </si>
+  <si>
+    <t>ироничных</t>
+  </si>
+  <si>
+    <t>ироничная</t>
+  </si>
+  <si>
+    <t>ироничное</t>
+  </si>
+  <si>
+    <t>ироничной</t>
+  </si>
+  <si>
+    <t>ироничном</t>
+  </si>
+  <si>
+    <t>ироничному</t>
+  </si>
+  <si>
+    <t>ироничность</t>
+  </si>
+  <si>
+    <t>ироничную</t>
+  </si>
+  <si>
+    <t>иронизируем</t>
+  </si>
+  <si>
+    <t>иронизирует</t>
+  </si>
+  <si>
+    <t>иронизируется</t>
+  </si>
+  <si>
+    <t>иронизируете</t>
+  </si>
+  <si>
+    <t>иронизируют</t>
+  </si>
+  <si>
+    <t>иронизируются</t>
+  </si>
+  <si>
+    <t>иронизирующий</t>
+  </si>
+  <si>
+    <t>остроумный</t>
+  </si>
+  <si>
+    <t>остроумные</t>
+  </si>
+  <si>
+    <t>остроумными</t>
+  </si>
+  <si>
+    <t>остроумных</t>
+  </si>
+  <si>
+    <t>остроумная</t>
+  </si>
+  <si>
+    <t>остроумность</t>
+  </si>
+  <si>
+    <t>остроумную</t>
+  </si>
+  <si>
+    <t>остроумное</t>
+  </si>
+  <si>
+    <t>остроумной</t>
+  </si>
+  <si>
+    <t>остроумном</t>
+  </si>
+  <si>
+    <t>остроумному</t>
+  </si>
+  <si>
+    <t>остроумничаем</t>
+  </si>
+  <si>
+    <t>остроумничает</t>
+  </si>
+  <si>
+    <t>остроумничается</t>
+  </si>
+  <si>
+    <t>остроумничаете</t>
+  </si>
+  <si>
+    <t>остроумничают</t>
+  </si>
+  <si>
+    <t>остроумничаются</t>
+  </si>
+  <si>
+    <t>остроумничащий</t>
+  </si>
+  <si>
+    <t>контрацепции</t>
+  </si>
+  <si>
+    <t>смартфон</t>
+  </si>
+  <si>
+    <t>одногрупница</t>
+  </si>
+  <si>
+    <t>одноклассница</t>
+  </si>
+  <si>
+    <t>одногрупнице</t>
+  </si>
+  <si>
+    <t>одногрупницей</t>
+  </si>
+  <si>
+    <t>однокласснице</t>
+  </si>
+  <si>
+    <t>одноклассницей</t>
+  </si>
+  <si>
+    <t>дазадаптация</t>
+  </si>
+  <si>
+    <t>несоответствие</t>
+  </si>
+  <si>
+    <t>дазадаптации</t>
+  </si>
+  <si>
+    <t>несоответствии</t>
+  </si>
+  <si>
+    <t>фишкой</t>
+  </si>
+  <si>
+    <t>прикол</t>
+  </si>
+  <si>
+    <t>фишка</t>
+  </si>
+  <si>
+    <t>фишки</t>
+  </si>
+  <si>
+    <t>фишке</t>
+  </si>
+  <si>
+    <t>прикола</t>
+  </si>
+  <si>
+    <t>приколом</t>
+  </si>
+  <si>
+    <t>приколу</t>
+  </si>
+  <si>
+    <t>калибратор</t>
+  </si>
+  <si>
+    <t>измеритель</t>
+  </si>
+  <si>
+    <t>калибратора</t>
+  </si>
+  <si>
+    <t>калибратору</t>
+  </si>
+  <si>
+    <t>калибраторе</t>
+  </si>
+  <si>
+    <t>калибратором</t>
+  </si>
+  <si>
+    <t>калибровал</t>
+  </si>
+  <si>
+    <t>калибровала</t>
+  </si>
+  <si>
+    <t>калибровалась</t>
+  </si>
+  <si>
+    <t>калибровали</t>
+  </si>
+  <si>
+    <t>калибровались</t>
+  </si>
+  <si>
+    <t>калибровалось</t>
+  </si>
+  <si>
+    <t>калибровался</t>
+  </si>
+  <si>
+    <t>калиброван</t>
+  </si>
+  <si>
+    <t>калиброванная</t>
+  </si>
+  <si>
+    <t>калиброванного</t>
+  </si>
+  <si>
+    <t>калиброванное</t>
+  </si>
+  <si>
+    <t>калиброванной</t>
+  </si>
+  <si>
+    <t>калиброванном</t>
+  </si>
+  <si>
+    <t>калиброванному</t>
+  </si>
+  <si>
+    <t>калиброванную</t>
+  </si>
+  <si>
+    <t>калиброванные</t>
+  </si>
+  <si>
+    <t>калиброванный</t>
+  </si>
+  <si>
+    <t>калиброванным</t>
+  </si>
+  <si>
+    <t>калиброванными</t>
+  </si>
+  <si>
+    <t>калиброванных</t>
+  </si>
+  <si>
+    <t>калибрует</t>
+  </si>
+  <si>
+    <t>калибрем</t>
+  </si>
+  <si>
+    <t>калибрется</t>
+  </si>
+  <si>
+    <t>калибрете</t>
+  </si>
+  <si>
+    <t>калибрют</t>
+  </si>
+  <si>
+    <t>калибрются</t>
+  </si>
+  <si>
+    <t>калибрющие</t>
+  </si>
+  <si>
+    <t>калибрющий</t>
+  </si>
+  <si>
+    <t>измерителя</t>
+  </si>
+  <si>
+    <t>измерителю</t>
+  </si>
+  <si>
+    <t>измерителе</t>
+  </si>
+  <si>
+    <t>измерителем</t>
+  </si>
+  <si>
+    <t>измерял</t>
+  </si>
+  <si>
+    <t>измеряла</t>
+  </si>
+  <si>
+    <t>измерялась</t>
+  </si>
+  <si>
+    <t>измеряли</t>
+  </si>
+  <si>
+    <t>измерялись</t>
+  </si>
+  <si>
+    <t>измерялось</t>
+  </si>
+  <si>
+    <t>измерялся</t>
+  </si>
+  <si>
+    <t>измерен</t>
+  </si>
+  <si>
+    <t>измеренная</t>
+  </si>
+  <si>
+    <t>измеренного</t>
+  </si>
+  <si>
+    <t>измеренное</t>
+  </si>
+  <si>
+    <t>измеренной</t>
+  </si>
+  <si>
+    <t>измеренном</t>
+  </si>
+  <si>
+    <t>измеренному</t>
+  </si>
+  <si>
+    <t>измеренную</t>
+  </si>
+  <si>
+    <t>измеренные</t>
+  </si>
+  <si>
+    <t>измеренный</t>
+  </si>
+  <si>
+    <t>измеренным</t>
+  </si>
+  <si>
+    <t>измеренными</t>
+  </si>
+  <si>
+    <t>измеренных</t>
+  </si>
+  <si>
+    <t>измеряет</t>
+  </si>
+  <si>
+    <t>измерям</t>
+  </si>
+  <si>
+    <t>измеряется</t>
+  </si>
+  <si>
+    <t>измеряете</t>
+  </si>
+  <si>
+    <t>измеряют</t>
+  </si>
+  <si>
+    <t>измеряются</t>
+  </si>
+  <si>
+    <t>измерящие</t>
+  </si>
+  <si>
+    <t>измеряющий</t>
+  </si>
+  <si>
+    <t>альфонс</t>
+  </si>
+  <si>
+    <t>маменькин сынок</t>
+  </si>
+  <si>
+    <t>альфонса</t>
+  </si>
+  <si>
+    <t>альфонсу</t>
+  </si>
+  <si>
+    <t>альфонсе</t>
+  </si>
+  <si>
+    <t>альфонсом</t>
+  </si>
+  <si>
+    <t>маменькиного сынка</t>
+  </si>
+  <si>
+    <t>маменькиному сыноку</t>
+  </si>
+  <si>
+    <t>маменькином сынке</t>
+  </si>
+  <si>
+    <t>маменькиным сынком</t>
+  </si>
+  <si>
+    <t>экспресс- проверка</t>
+  </si>
+  <si>
+    <t>быстрая проверка</t>
+  </si>
+  <si>
+    <t>экспресс- проверки</t>
+  </si>
+  <si>
+    <t>экспресс- проверке</t>
+  </si>
+  <si>
+    <t>экспресс- проверку</t>
+  </si>
+  <si>
+    <t>экспресс- проверкой</t>
+  </si>
+  <si>
+    <t>быстрой проверки</t>
+  </si>
+  <si>
+    <t>быстрой проверке</t>
+  </si>
+  <si>
+    <t>быструю проверку</t>
+  </si>
+  <si>
+    <t>быстрой проверкой</t>
   </si>
 </sst>
 </file>
@@ -31005,7 +32697,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B5825"/>
+  <dimension ref="A1:B6122"/>
   <sheetFormatPr defaultColWidth="12.85546875" defaultRowHeight="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="35.140625" style="5" customWidth="1"/>
@@ -76242,45 +77934,2430 @@
       <c r="A5817" s="5" t="s">
         <v>10120</v>
       </c>
+      <c r="B5817" s="5" t="s">
+        <v>10186</v>
+      </c>
     </row>
     <row r="5818" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5818" s="5" t="s">
         <v>10121</v>
       </c>
+      <c r="B5818" s="5" t="s">
+        <v>10187</v>
+      </c>
     </row>
     <row r="5819" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5819" s="5" t="s">
         <v>10122</v>
       </c>
+      <c r="B5819" s="5" t="s">
+        <v>10188</v>
+      </c>
     </row>
     <row r="5820" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5820" s="5" t="s">
         <v>10123</v>
       </c>
+      <c r="B5820" s="5" t="s">
+        <v>10189</v>
+      </c>
     </row>
     <row r="5821" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5821" s="5" t="s">
         <v>10124</v>
       </c>
+      <c r="B5821" s="5" t="s">
+        <v>10190</v>
+      </c>
     </row>
     <row r="5822" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5822" s="5" t="s">
         <v>10125</v>
       </c>
+      <c r="B5822" s="5" t="s">
+        <v>10191</v>
+      </c>
     </row>
     <row r="5823" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5823" s="5" t="s">
-        <v>10125</v>
+        <v>10192</v>
+      </c>
+      <c r="B5823" s="5" t="s">
+        <v>10193</v>
       </c>
     </row>
     <row r="5824" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5824" s="5" t="s">
-        <v>10125</v>
-      </c>
-    </row>
-    <row r="5825" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10194</v>
+      </c>
+      <c r="B5824" s="5" t="s">
+        <v>10205</v>
+      </c>
+    </row>
+    <row r="5825" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5825" s="5" t="s">
-        <v>10125</v>
+        <v>10195</v>
+      </c>
+      <c r="B5825" s="5" t="s">
+        <v>10206</v>
+      </c>
+    </row>
+    <row r="5826" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5826" s="5" t="s">
+        <v>10196</v>
+      </c>
+      <c r="B5826" s="5" t="s">
+        <v>10207</v>
+      </c>
+    </row>
+    <row r="5827" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5827" s="5" t="s">
+        <v>10197</v>
+      </c>
+      <c r="B5827" s="5" t="s">
+        <v>10208</v>
+      </c>
+    </row>
+    <row r="5828" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5828" s="5" t="s">
+        <v>10198</v>
+      </c>
+      <c r="B5828" s="5" t="s">
+        <v>10209</v>
+      </c>
+    </row>
+    <row r="5829" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5829" s="5" t="s">
+        <v>10199</v>
+      </c>
+      <c r="B5829" s="5" t="s">
+        <v>10210</v>
+      </c>
+    </row>
+    <row r="5830" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5830" s="5" t="s">
+        <v>10200</v>
+      </c>
+      <c r="B5830" s="5" t="s">
+        <v>10211</v>
+      </c>
+    </row>
+    <row r="5831" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5831" s="5" t="s">
+        <v>10201</v>
+      </c>
+      <c r="B5831" s="5" t="s">
+        <v>10212</v>
+      </c>
+    </row>
+    <row r="5832" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5832" s="5" t="s">
+        <v>10202</v>
+      </c>
+      <c r="B5832" s="5" t="s">
+        <v>10213</v>
+      </c>
+    </row>
+    <row r="5833" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5833" s="5" t="s">
+        <v>10203</v>
+      </c>
+      <c r="B5833" s="5" t="s">
+        <v>10214</v>
+      </c>
+    </row>
+    <row r="5834" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5834" s="5" t="s">
+        <v>10204</v>
+      </c>
+      <c r="B5834" s="5" t="s">
+        <v>10215</v>
+      </c>
+    </row>
+    <row r="5835" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5835" s="5" t="s">
+        <v>10216</v>
+      </c>
+      <c r="B5835" s="5" t="s">
+        <v>10226</v>
+      </c>
+    </row>
+    <row r="5836" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5836" s="5" t="s">
+        <v>10217</v>
+      </c>
+      <c r="B5836" s="5" t="s">
+        <v>10227</v>
+      </c>
+    </row>
+    <row r="5837" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5837" s="5" t="s">
+        <v>10218</v>
+      </c>
+      <c r="B5837" s="5" t="s">
+        <v>10228</v>
+      </c>
+    </row>
+    <row r="5838" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5838" s="5" t="s">
+        <v>10219</v>
+      </c>
+      <c r="B5838" s="5" t="s">
+        <v>10229</v>
+      </c>
+    </row>
+    <row r="5839" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5839" s="5" t="s">
+        <v>10220</v>
+      </c>
+      <c r="B5839" s="5" t="s">
+        <v>10230</v>
+      </c>
+    </row>
+    <row r="5840" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5840" s="5" t="s">
+        <v>10221</v>
+      </c>
+      <c r="B5840" s="5" t="s">
+        <v>10231</v>
+      </c>
+    </row>
+    <row r="5841" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5841" s="5" t="s">
+        <v>10222</v>
+      </c>
+      <c r="B5841" s="5" t="s">
+        <v>10232</v>
+      </c>
+    </row>
+    <row r="5842" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5842" s="5" t="s">
+        <v>10223</v>
+      </c>
+      <c r="B5842" s="5" t="s">
+        <v>10233</v>
+      </c>
+    </row>
+    <row r="5843" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5843" s="5" t="s">
+        <v>10224</v>
+      </c>
+      <c r="B5843" s="5" t="s">
+        <v>10234</v>
+      </c>
+    </row>
+    <row r="5844" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5844" s="5" t="s">
+        <v>10225</v>
+      </c>
+      <c r="B5844" s="5" t="s">
+        <v>10235</v>
+      </c>
+    </row>
+    <row r="5845" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5845" s="5" t="s">
+        <v>10236</v>
+      </c>
+      <c r="B5845" s="5" t="s">
+        <v>10237</v>
+      </c>
+    </row>
+    <row r="5846" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5846" s="5" t="s">
+        <v>10238</v>
+      </c>
+      <c r="B5846" s="5" t="s">
+        <v>10242</v>
+      </c>
+    </row>
+    <row r="5847" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5847" s="5" t="s">
+        <v>10239</v>
+      </c>
+      <c r="B5847" s="5" t="s">
+        <v>10243</v>
+      </c>
+    </row>
+    <row r="5848" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5848" s="5" t="s">
+        <v>10240</v>
+      </c>
+      <c r="B5848" s="5" t="s">
+        <v>10244</v>
+      </c>
+    </row>
+    <row r="5849" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5849" s="5" t="s">
+        <v>10241</v>
+      </c>
+      <c r="B5849" s="5" t="s">
+        <v>10245</v>
+      </c>
+    </row>
+    <row r="5850" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5850" s="5" t="s">
+        <v>5501</v>
+      </c>
+      <c r="B5850" s="5" t="s">
+        <v>10246</v>
+      </c>
+    </row>
+    <row r="5851" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5851" s="5" t="s">
+        <v>5499</v>
+      </c>
+      <c r="B5851" s="5" t="s">
+        <v>10249</v>
+      </c>
+    </row>
+    <row r="5852" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5852" s="5" t="s">
+        <v>10247</v>
+      </c>
+      <c r="B5852" s="5" t="s">
+        <v>10250</v>
+      </c>
+    </row>
+    <row r="5853" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5853" s="5" t="s">
+        <v>10248</v>
+      </c>
+      <c r="B5853" s="5" t="s">
+        <v>10251</v>
+      </c>
+    </row>
+    <row r="5854" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5854" s="5" t="s">
+        <v>7374</v>
+      </c>
+      <c r="B5854" s="5" t="s">
+        <v>10252</v>
+      </c>
+    </row>
+    <row r="5855" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5855" s="5" t="s">
+        <v>10253</v>
+      </c>
+      <c r="B5855" s="5" t="s">
+        <v>10254</v>
+      </c>
+    </row>
+    <row r="5856" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5856" s="5" t="s">
+        <v>10255</v>
+      </c>
+      <c r="B5856" s="5" t="s">
+        <v>10264</v>
+      </c>
+    </row>
+    <row r="5857" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5857" s="5" t="s">
+        <v>10256</v>
+      </c>
+      <c r="B5857" s="5" t="s">
+        <v>10265</v>
+      </c>
+    </row>
+    <row r="5858" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5858" s="5" t="s">
+        <v>10257</v>
+      </c>
+      <c r="B5858" s="5" t="s">
+        <v>10266</v>
+      </c>
+    </row>
+    <row r="5859" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5859" s="5" t="s">
+        <v>10258</v>
+      </c>
+      <c r="B5859" s="5" t="s">
+        <v>10267</v>
+      </c>
+    </row>
+    <row r="5860" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5860" s="5" t="s">
+        <v>10259</v>
+      </c>
+      <c r="B5860" s="5" t="s">
+        <v>10268</v>
+      </c>
+    </row>
+    <row r="5861" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5861" s="5" t="s">
+        <v>10260</v>
+      </c>
+      <c r="B5861" s="5" t="s">
+        <v>10269</v>
+      </c>
+    </row>
+    <row r="5862" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5862" s="5" t="s">
+        <v>10261</v>
+      </c>
+      <c r="B5862" s="5" t="s">
+        <v>10270</v>
+      </c>
+    </row>
+    <row r="5863" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5863" s="5" t="s">
+        <v>10262</v>
+      </c>
+      <c r="B5863" s="5" t="s">
+        <v>10271</v>
+      </c>
+    </row>
+    <row r="5864" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5864" s="5" t="s">
+        <v>10263</v>
+      </c>
+      <c r="B5864" s="5" t="s">
+        <v>10272</v>
+      </c>
+    </row>
+    <row r="5865" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5865" s="5" t="s">
+        <v>10273</v>
+      </c>
+      <c r="B5865" s="5" t="s">
+        <v>10082</v>
+      </c>
+    </row>
+    <row r="5866" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5866" s="5" t="s">
+        <v>10274</v>
+      </c>
+      <c r="B5866" s="5" t="s">
+        <v>10092</v>
+      </c>
+    </row>
+    <row r="5867" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5867" s="5" t="s">
+        <v>10275</v>
+      </c>
+      <c r="B5867" s="5" t="s">
+        <v>10093</v>
+      </c>
+    </row>
+    <row r="5868" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5868" s="5" t="s">
+        <v>10276</v>
+      </c>
+      <c r="B5868" s="5" t="s">
+        <v>10094</v>
+      </c>
+    </row>
+    <row r="5869" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5869" s="5" t="s">
+        <v>10277</v>
+      </c>
+      <c r="B5869" s="5" t="s">
+        <v>10095</v>
+      </c>
+    </row>
+    <row r="5870" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5870" s="5" t="s">
+        <v>10278</v>
+      </c>
+      <c r="B5870" s="5" t="s">
+        <v>10096</v>
+      </c>
+    </row>
+    <row r="5871" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5871" s="5" t="s">
+        <v>10279</v>
+      </c>
+      <c r="B5871" s="5" t="s">
+        <v>10099</v>
+      </c>
+    </row>
+    <row r="5872" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5872" s="5" t="s">
+        <v>10280</v>
+      </c>
+      <c r="B5872" s="5" t="s">
+        <v>10285</v>
+      </c>
+    </row>
+    <row r="5873" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5873" s="5" t="s">
+        <v>10281</v>
+      </c>
+      <c r="B5873" s="5" t="s">
+        <v>10286</v>
+      </c>
+    </row>
+    <row r="5874" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5874" s="5" t="s">
+        <v>10282</v>
+      </c>
+      <c r="B5874" s="5" t="s">
+        <v>10287</v>
+      </c>
+    </row>
+    <row r="5875" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5875" s="5" t="s">
+        <v>10283</v>
+      </c>
+      <c r="B5875" s="5" t="s">
+        <v>10288</v>
+      </c>
+    </row>
+    <row r="5876" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5876" s="5" t="s">
+        <v>10284</v>
+      </c>
+      <c r="B5876" s="5" t="s">
+        <v>10289</v>
+      </c>
+    </row>
+    <row r="5877" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5877" s="5" t="s">
+        <v>10290</v>
+      </c>
+      <c r="B5877" s="5" t="s">
+        <v>10291</v>
+      </c>
+    </row>
+    <row r="5878" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5878" s="5" t="s">
+        <v>10292</v>
+      </c>
+      <c r="B5878" s="5" t="s">
+        <v>10296</v>
+      </c>
+    </row>
+    <row r="5879" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5879" s="5" t="s">
+        <v>10293</v>
+      </c>
+      <c r="B5879" s="5" t="s">
+        <v>10297</v>
+      </c>
+    </row>
+    <row r="5880" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5880" s="5" t="s">
+        <v>10294</v>
+      </c>
+      <c r="B5880" s="5" t="s">
+        <v>10298</v>
+      </c>
+    </row>
+    <row r="5881" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5881" s="5" t="s">
+        <v>10295</v>
+      </c>
+      <c r="B5881" s="5" t="s">
+        <v>10299</v>
+      </c>
+    </row>
+    <row r="5882" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5882" s="5" t="s">
+        <v>10300</v>
+      </c>
+      <c r="B5882" s="5" t="s">
+        <v>10301</v>
+      </c>
+    </row>
+    <row r="5883" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5883" s="5" t="s">
+        <v>10302</v>
+      </c>
+      <c r="B5883" s="5" t="s">
+        <v>10301</v>
+      </c>
+    </row>
+    <row r="5884" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5884" s="5" t="s">
+        <v>10303</v>
+      </c>
+      <c r="B5884" s="5" t="s">
+        <v>10301</v>
+      </c>
+    </row>
+    <row r="5885" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5885" s="5" t="s">
+        <v>10304</v>
+      </c>
+      <c r="B5885" s="5" t="s">
+        <v>10301</v>
+      </c>
+    </row>
+    <row r="5886" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5886" s="5" t="s">
+        <v>10305</v>
+      </c>
+      <c r="B5886" s="5" t="s">
+        <v>10301</v>
+      </c>
+    </row>
+    <row r="5887" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5887" s="5" t="s">
+        <v>10306</v>
+      </c>
+      <c r="B5887" s="5" t="s">
+        <v>10301</v>
+      </c>
+    </row>
+    <row r="5888" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5888" s="5" t="s">
+        <v>10307</v>
+      </c>
+      <c r="B5888" s="5" t="s">
+        <v>10301</v>
+      </c>
+    </row>
+    <row r="5889" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5889" s="5" t="s">
+        <v>10308</v>
+      </c>
+      <c r="B5889" s="5" t="s">
+        <v>10301</v>
+      </c>
+    </row>
+    <row r="5890" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5890" s="5" t="s">
+        <v>10309</v>
+      </c>
+      <c r="B5890" s="5" t="s">
+        <v>10301</v>
+      </c>
+    </row>
+    <row r="5891" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5891" s="5" t="s">
+        <v>10310</v>
+      </c>
+      <c r="B5891" s="5" t="s">
+        <v>10301</v>
+      </c>
+    </row>
+    <row r="5892" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5892" s="5" t="s">
+        <v>10311</v>
+      </c>
+      <c r="B5892" s="5" t="s">
+        <v>10312</v>
+      </c>
+    </row>
+    <row r="5893" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5893" s="5" t="s">
+        <v>10313</v>
+      </c>
+      <c r="B5893" s="5" t="s">
+        <v>10321</v>
+      </c>
+    </row>
+    <row r="5894" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5894" s="5" t="s">
+        <v>10314</v>
+      </c>
+      <c r="B5894" s="5" t="s">
+        <v>10322</v>
+      </c>
+    </row>
+    <row r="5895" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5895" s="5" t="s">
+        <v>10315</v>
+      </c>
+      <c r="B5895" s="5" t="s">
+        <v>10323</v>
+      </c>
+    </row>
+    <row r="5896" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5896" s="5" t="s">
+        <v>10316</v>
+      </c>
+      <c r="B5896" s="5" t="s">
+        <v>10324</v>
+      </c>
+    </row>
+    <row r="5897" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5897" s="5" t="s">
+        <v>10317</v>
+      </c>
+      <c r="B5897" s="5" t="s">
+        <v>10325</v>
+      </c>
+    </row>
+    <row r="5898" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5898" s="5" t="s">
+        <v>10318</v>
+      </c>
+      <c r="B5898" s="5" t="s">
+        <v>10326</v>
+      </c>
+    </row>
+    <row r="5899" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5899" s="5" t="s">
+        <v>10319</v>
+      </c>
+      <c r="B5899" s="5" t="s">
+        <v>10327</v>
+      </c>
+    </row>
+    <row r="5900" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5900" s="5" t="s">
+        <v>10320</v>
+      </c>
+      <c r="B5900" s="5" t="s">
+        <v>10328</v>
+      </c>
+    </row>
+    <row r="5901" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5901" s="5" t="s">
+        <v>10329</v>
+      </c>
+      <c r="B5901" s="5" t="s">
+        <v>10330</v>
+      </c>
+    </row>
+    <row r="5902" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5902" s="5" t="s">
+        <v>10331</v>
+      </c>
+      <c r="B5902" s="5" t="s">
+        <v>10340</v>
+      </c>
+    </row>
+    <row r="5903" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5903" s="5" t="s">
+        <v>10332</v>
+      </c>
+      <c r="B5903" s="5" t="s">
+        <v>10341</v>
+      </c>
+    </row>
+    <row r="5904" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5904" s="5" t="s">
+        <v>10333</v>
+      </c>
+      <c r="B5904" s="5" t="s">
+        <v>10342</v>
+      </c>
+    </row>
+    <row r="5905" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5905" s="5" t="s">
+        <v>10334</v>
+      </c>
+      <c r="B5905" s="5" t="s">
+        <v>10343</v>
+      </c>
+    </row>
+    <row r="5906" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5906" s="5" t="s">
+        <v>10335</v>
+      </c>
+      <c r="B5906" s="5" t="s">
+        <v>10344</v>
+      </c>
+    </row>
+    <row r="5907" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5907" s="5" t="s">
+        <v>10336</v>
+      </c>
+      <c r="B5907" s="5" t="s">
+        <v>10345</v>
+      </c>
+    </row>
+    <row r="5908" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5908" s="5" t="s">
+        <v>10337</v>
+      </c>
+      <c r="B5908" s="5" t="s">
+        <v>10346</v>
+      </c>
+    </row>
+    <row r="5909" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5909" s="5" t="s">
+        <v>10338</v>
+      </c>
+      <c r="B5909" s="5" t="s">
+        <v>10347</v>
+      </c>
+    </row>
+    <row r="5910" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5910" s="5" t="s">
+        <v>10339</v>
+      </c>
+      <c r="B5910" s="5" t="s">
+        <v>10348</v>
+      </c>
+    </row>
+    <row r="5911" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5911" s="5" t="s">
+        <v>10349</v>
+      </c>
+    </row>
+    <row r="5912" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5912" s="5" t="s">
+        <v>10350</v>
+      </c>
+      <c r="B5912" s="5" t="s">
+        <v>10351</v>
+      </c>
+    </row>
+    <row r="5913" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5913" s="5" t="s">
+        <v>10352</v>
+      </c>
+      <c r="B5913" s="5" t="s">
+        <v>10357</v>
+      </c>
+    </row>
+    <row r="5914" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5914" s="5" t="s">
+        <v>10353</v>
+      </c>
+      <c r="B5914" s="5" t="s">
+        <v>10358</v>
+      </c>
+    </row>
+    <row r="5915" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5915" s="5" t="s">
+        <v>10354</v>
+      </c>
+      <c r="B5915" s="5" t="s">
+        <v>10359</v>
+      </c>
+    </row>
+    <row r="5916" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5916" s="5" t="s">
+        <v>10355</v>
+      </c>
+      <c r="B5916" s="5" t="s">
+        <v>10360</v>
+      </c>
+    </row>
+    <row r="5917" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5917" s="5" t="s">
+        <v>10356</v>
+      </c>
+      <c r="B5917" s="5" t="s">
+        <v>10361</v>
+      </c>
+    </row>
+    <row r="5918" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5918" s="5" t="s">
+        <v>10362</v>
+      </c>
+      <c r="B5918" s="5" t="s">
+        <v>10369</v>
+      </c>
+    </row>
+    <row r="5919" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5919" s="5" t="s">
+        <v>10364</v>
+      </c>
+      <c r="B5919" s="5" t="s">
+        <v>10363</v>
+      </c>
+    </row>
+    <row r="5920" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5920" s="5" t="s">
+        <v>10365</v>
+      </c>
+      <c r="B5920" s="5" t="s">
+        <v>10370</v>
+      </c>
+    </row>
+    <row r="5921" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5921" s="5" t="s">
+        <v>10366</v>
+      </c>
+      <c r="B5921" s="5" t="s">
+        <v>10371</v>
+      </c>
+    </row>
+    <row r="5922" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5922" s="5" t="s">
+        <v>10367</v>
+      </c>
+      <c r="B5922" s="5" t="s">
+        <v>10372</v>
+      </c>
+    </row>
+    <row r="5923" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5923" s="5" t="s">
+        <v>10368</v>
+      </c>
+      <c r="B5923" s="5" t="s">
+        <v>10373</v>
+      </c>
+    </row>
+    <row r="5924" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5924" s="5" t="s">
+        <v>10374</v>
+      </c>
+      <c r="B5924" s="5" t="s">
+        <v>10375</v>
+      </c>
+    </row>
+    <row r="5925" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5925" s="5" t="s">
+        <v>10376</v>
+      </c>
+      <c r="B5925" s="5" t="s">
+        <v>10382</v>
+      </c>
+    </row>
+    <row r="5926" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5926" s="5" t="s">
+        <v>10377</v>
+      </c>
+      <c r="B5926" s="5" t="s">
+        <v>10383</v>
+      </c>
+    </row>
+    <row r="5927" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5927" s="5" t="s">
+        <v>10378</v>
+      </c>
+      <c r="B5927" s="5" t="s">
+        <v>10384</v>
+      </c>
+    </row>
+    <row r="5928" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5928" s="5" t="s">
+        <v>10379</v>
+      </c>
+      <c r="B5928" s="5" t="s">
+        <v>10385</v>
+      </c>
+    </row>
+    <row r="5929" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5929" s="5" t="s">
+        <v>10380</v>
+      </c>
+      <c r="B5929" s="5" t="s">
+        <v>10386</v>
+      </c>
+    </row>
+    <row r="5930" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5930" s="5" t="s">
+        <v>10381</v>
+      </c>
+      <c r="B5930" s="5" t="s">
+        <v>10382</v>
+      </c>
+    </row>
+    <row r="5931" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5931" s="5" t="s">
+        <v>10387</v>
+      </c>
+      <c r="B5931" s="5" t="s">
+        <v>10388</v>
+      </c>
+    </row>
+    <row r="5932" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5932" s="5" t="s">
+        <v>10389</v>
+      </c>
+      <c r="B5932" s="5" t="s">
+        <v>10393</v>
+      </c>
+    </row>
+    <row r="5933" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5933" s="5" t="s">
+        <v>10390</v>
+      </c>
+      <c r="B5933" s="5" t="s">
+        <v>10394</v>
+      </c>
+    </row>
+    <row r="5934" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5934" s="5" t="s">
+        <v>10391</v>
+      </c>
+      <c r="B5934" s="5" t="s">
+        <v>10395</v>
+      </c>
+    </row>
+    <row r="5935" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5935" s="5" t="s">
+        <v>10392</v>
+      </c>
+      <c r="B5935" s="5" t="s">
+        <v>10396</v>
+      </c>
+    </row>
+    <row r="5936" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5936" s="5" t="s">
+        <v>10397</v>
+      </c>
+      <c r="B5936" s="5" t="s">
+        <v>10398</v>
+      </c>
+    </row>
+    <row r="5937" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5937" s="5" t="s">
+        <v>10399</v>
+      </c>
+      <c r="B5937" s="5" t="s">
+        <v>10403</v>
+      </c>
+    </row>
+    <row r="5938" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5938" s="5" t="s">
+        <v>10400</v>
+      </c>
+      <c r="B5938" s="5" t="s">
+        <v>10404</v>
+      </c>
+    </row>
+    <row r="5939" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5939" s="5" t="s">
+        <v>10401</v>
+      </c>
+      <c r="B5939" s="5" t="s">
+        <v>10405</v>
+      </c>
+    </row>
+    <row r="5940" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5940" s="5" t="s">
+        <v>10402</v>
+      </c>
+      <c r="B5940" s="5" t="s">
+        <v>10406</v>
+      </c>
+    </row>
+    <row r="5941" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5941" s="5" t="s">
+        <v>10407</v>
+      </c>
+    </row>
+    <row r="5942" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5942" s="5" t="s">
+        <v>10408</v>
+      </c>
+      <c r="B5942" s="5" t="s">
+        <v>10415</v>
+      </c>
+    </row>
+    <row r="5943" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5943" s="5" t="s">
+        <v>10410</v>
+      </c>
+      <c r="B5943" s="5" t="s">
+        <v>10409</v>
+      </c>
+    </row>
+    <row r="5944" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5944" s="5" t="s">
+        <v>10411</v>
+      </c>
+      <c r="B5944" s="5" t="s">
+        <v>10414</v>
+      </c>
+    </row>
+    <row r="5945" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5945" s="5" t="s">
+        <v>10412</v>
+      </c>
+      <c r="B5945" s="5" t="s">
+        <v>10415</v>
+      </c>
+    </row>
+    <row r="5946" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5946" s="5" t="s">
+        <v>10413</v>
+      </c>
+      <c r="B5946" s="5" t="s">
+        <v>10409</v>
+      </c>
+    </row>
+    <row r="5947" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5947" s="5" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B5947" s="5" t="s">
+        <v>10416</v>
+      </c>
+    </row>
+    <row r="5948" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5948" s="5" t="s">
+        <v>10417</v>
+      </c>
+      <c r="B5948" s="5" t="s">
+        <v>10421</v>
+      </c>
+    </row>
+    <row r="5949" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5949" s="5" t="s">
+        <v>10418</v>
+      </c>
+      <c r="B5949" s="5" t="s">
+        <v>10422</v>
+      </c>
+    </row>
+    <row r="5950" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5950" s="5" t="s">
+        <v>10419</v>
+      </c>
+      <c r="B5950" s="5" t="s">
+        <v>10423</v>
+      </c>
+    </row>
+    <row r="5951" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5951" s="5" t="s">
+        <v>10420</v>
+      </c>
+      <c r="B5951" s="5" t="s">
+        <v>10424</v>
+      </c>
+    </row>
+    <row r="5952" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5952" s="5" t="s">
+        <v>10425</v>
+      </c>
+      <c r="B5952" s="5" t="s">
+        <v>10426</v>
+      </c>
+    </row>
+    <row r="5953" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5953" s="5" t="s">
+        <v>10427</v>
+      </c>
+      <c r="B5953" s="5" t="s">
+        <v>10431</v>
+      </c>
+    </row>
+    <row r="5954" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5954" s="5" t="s">
+        <v>10428</v>
+      </c>
+      <c r="B5954" s="5" t="s">
+        <v>10432</v>
+      </c>
+    </row>
+    <row r="5955" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5955" s="5" t="s">
+        <v>10429</v>
+      </c>
+      <c r="B5955" s="5" t="s">
+        <v>10433</v>
+      </c>
+    </row>
+    <row r="5956" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5956" s="5" t="s">
+        <v>10430</v>
+      </c>
+      <c r="B5956" s="5" t="s">
+        <v>10434</v>
+      </c>
+    </row>
+    <row r="5957" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5957" s="5" t="s">
+        <v>10435</v>
+      </c>
+      <c r="B5957" s="5" t="s">
+        <v>10436</v>
+      </c>
+    </row>
+    <row r="5958" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5958" s="5" t="s">
+        <v>10437</v>
+      </c>
+      <c r="B5958" s="5" t="s">
+        <v>10442</v>
+      </c>
+    </row>
+    <row r="5959" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5959" s="5" t="s">
+        <v>10438</v>
+      </c>
+      <c r="B5959" s="5" t="s">
+        <v>10443</v>
+      </c>
+    </row>
+    <row r="5960" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5960" s="5" t="s">
+        <v>10439</v>
+      </c>
+      <c r="B5960" s="5" t="s">
+        <v>10444</v>
+      </c>
+    </row>
+    <row r="5961" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5961" s="5" t="s">
+        <v>10440</v>
+      </c>
+      <c r="B5961" s="5" t="s">
+        <v>10445</v>
+      </c>
+    </row>
+    <row r="5962" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5962" s="5" t="s">
+        <v>10441</v>
+      </c>
+      <c r="B5962" s="5" t="s">
+        <v>10446</v>
+      </c>
+    </row>
+    <row r="5963" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5963" s="5" t="s">
+        <v>10447</v>
+      </c>
+      <c r="B5963" s="5" t="s">
+        <v>10450</v>
+      </c>
+    </row>
+    <row r="5964" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5964" s="5" t="s">
+        <v>10448</v>
+      </c>
+      <c r="B5964" s="5" t="s">
+        <v>10451</v>
+      </c>
+    </row>
+    <row r="5965" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5965" s="5" t="s">
+        <v>10449</v>
+      </c>
+      <c r="B5965" s="5" t="s">
+        <v>10452</v>
+      </c>
+    </row>
+    <row r="5966" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5966" s="5" t="s">
+        <v>10453</v>
+      </c>
+      <c r="B5966" s="5" t="s">
+        <v>10454</v>
+      </c>
+    </row>
+    <row r="5967" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5967" s="5" t="s">
+        <v>10455</v>
+      </c>
+      <c r="B5967" s="5" t="s">
+        <v>10458</v>
+      </c>
+    </row>
+    <row r="5968" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5968" s="5" t="s">
+        <v>10456</v>
+      </c>
+      <c r="B5968" s="5" t="s">
+        <v>10459</v>
+      </c>
+    </row>
+    <row r="5969" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5969" s="5" t="s">
+        <v>10457</v>
+      </c>
+      <c r="B5969" s="5" t="s">
+        <v>10460</v>
+      </c>
+    </row>
+    <row r="5970" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5970" s="5" t="s">
+        <v>10461</v>
+      </c>
+      <c r="B5970" s="5" t="s">
+        <v>10462</v>
+      </c>
+    </row>
+    <row r="5971" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5971" s="5" t="s">
+        <v>10463</v>
+      </c>
+      <c r="B5971" s="5" t="s">
+        <v>10465</v>
+      </c>
+    </row>
+    <row r="5972" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5972" s="5" t="s">
+        <v>10464</v>
+      </c>
+      <c r="B5972" s="5" t="s">
+        <v>10466</v>
+      </c>
+    </row>
+    <row r="5973" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5973" s="5" t="s">
+        <v>10580</v>
+      </c>
+      <c r="B5973" s="5" t="s">
+        <v>10581</v>
+      </c>
+    </row>
+    <row r="5974" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5974" s="5" t="s">
+        <v>10582</v>
+      </c>
+      <c r="B5974" s="5" t="s">
+        <v>10583</v>
+      </c>
+    </row>
+    <row r="5975" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5975" s="5" t="s">
+        <v>10467</v>
+      </c>
+      <c r="B5975" s="5" t="s">
+        <v>10468</v>
+      </c>
+    </row>
+    <row r="5976" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5976" s="5" t="s">
+        <v>10469</v>
+      </c>
+      <c r="B5976" s="5" t="s">
+        <v>10471</v>
+      </c>
+    </row>
+    <row r="5977" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5977" s="5" t="s">
+        <v>10470</v>
+      </c>
+      <c r="B5977" s="5" t="s">
+        <v>10472</v>
+      </c>
+    </row>
+    <row r="5978" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5978" s="5" t="s">
+        <v>10549</v>
+      </c>
+      <c r="B5978" s="5" t="s">
+        <v>10550</v>
+      </c>
+    </row>
+    <row r="5979" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5979" s="5" t="s">
+        <v>10473</v>
+      </c>
+      <c r="B5979" s="5" t="s">
+        <v>10474</v>
+      </c>
+    </row>
+    <row r="5980" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5980" s="5" t="s">
+        <v>10475</v>
+      </c>
+      <c r="B5980" s="5" t="s">
+        <v>10476</v>
+      </c>
+    </row>
+    <row r="5981" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5981" s="5" t="s">
+        <v>10477</v>
+      </c>
+      <c r="B5981" s="5" t="s">
+        <v>10482</v>
+      </c>
+    </row>
+    <row r="5982" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5982" s="5" t="s">
+        <v>10478</v>
+      </c>
+      <c r="B5982" s="5" t="s">
+        <v>10483</v>
+      </c>
+    </row>
+    <row r="5983" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5983" s="5" t="s">
+        <v>10479</v>
+      </c>
+      <c r="B5983" s="5" t="s">
+        <v>10484</v>
+      </c>
+    </row>
+    <row r="5984" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5984" s="5" t="s">
+        <v>10480</v>
+      </c>
+      <c r="B5984" s="5" t="s">
+        <v>10485</v>
+      </c>
+    </row>
+    <row r="5985" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5985" s="5" t="s">
+        <v>10481</v>
+      </c>
+      <c r="B5985" s="5" t="s">
+        <v>10485</v>
+      </c>
+    </row>
+    <row r="5986" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5986" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="B5986" s="5" t="s">
+        <v>10487</v>
+      </c>
+    </row>
+    <row r="5987" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5987" s="5" t="s">
+        <v>4129</v>
+      </c>
+      <c r="B5987" s="5" t="s">
+        <v>10486</v>
+      </c>
+    </row>
+    <row r="5988" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5988" s="5" t="s">
+        <v>4124</v>
+      </c>
+      <c r="B5988" s="5" t="s">
+        <v>10488</v>
+      </c>
+    </row>
+    <row r="5989" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5989" s="5" t="s">
+        <v>4127</v>
+      </c>
+      <c r="B5989" s="5" t="s">
+        <v>10489</v>
+      </c>
+    </row>
+    <row r="5990" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5990" s="5" t="s">
+        <v>4126</v>
+      </c>
+      <c r="B5990" s="5" t="s">
+        <v>10490</v>
+      </c>
+    </row>
+    <row r="5991" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5991" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B5991" s="5" t="s">
+        <v>10491</v>
+      </c>
+    </row>
+    <row r="5992" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5992" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="B5992" s="5" t="s">
+        <v>10492</v>
+      </c>
+    </row>
+    <row r="5993" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5993" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="B5993" s="5" t="s">
+        <v>10493</v>
+      </c>
+    </row>
+    <row r="5994" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5994" s="5" t="s">
+        <v>10494</v>
+      </c>
+      <c r="B5994" s="5" t="s">
+        <v>10495</v>
+      </c>
+    </row>
+    <row r="5995" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5995" s="5" t="s">
+        <v>10496</v>
+      </c>
+      <c r="B5995" s="5" t="s">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="5996" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5996" s="5" t="s">
+        <v>10497</v>
+      </c>
+      <c r="B5996" s="5" t="s">
+        <v>10501</v>
+      </c>
+    </row>
+    <row r="5997" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5997" s="5" t="s">
+        <v>10498</v>
+      </c>
+      <c r="B5997" s="5" t="s">
+        <v>10502</v>
+      </c>
+    </row>
+    <row r="5998" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5998" s="5" t="s">
+        <v>10499</v>
+      </c>
+      <c r="B5998" s="5" t="s">
+        <v>10503</v>
+      </c>
+    </row>
+    <row r="5999" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5999" s="5" t="s">
+        <v>10504</v>
+      </c>
+    </row>
+    <row r="6000" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6000" s="5" t="s">
+        <v>10505</v>
+      </c>
+      <c r="B6000" s="5" t="s">
+        <v>10510</v>
+      </c>
+    </row>
+    <row r="6001" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6001" s="5" t="s">
+        <v>10506</v>
+      </c>
+      <c r="B6001" s="5" t="s">
+        <v>10511</v>
+      </c>
+    </row>
+    <row r="6002" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6002" s="5" t="s">
+        <v>10507</v>
+      </c>
+      <c r="B6002" s="5" t="s">
+        <v>10512</v>
+      </c>
+    </row>
+    <row r="6003" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6003" s="5" t="s">
+        <v>10508</v>
+      </c>
+      <c r="B6003" s="5" t="s">
+        <v>10513</v>
+      </c>
+    </row>
+    <row r="6004" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6004" s="5" t="s">
+        <v>10509</v>
+      </c>
+      <c r="B6004" s="5" t="s">
+        <v>10514</v>
+      </c>
+    </row>
+    <row r="6005" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6005" s="5" t="s">
+        <v>10515</v>
+      </c>
+      <c r="B6005" s="5" t="s">
+        <v>10521</v>
+      </c>
+    </row>
+    <row r="6006" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6006" s="5" t="s">
+        <v>10517</v>
+      </c>
+      <c r="B6006" s="5" t="s">
+        <v>10516</v>
+      </c>
+    </row>
+    <row r="6007" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6007" s="5" t="s">
+        <v>10518</v>
+      </c>
+      <c r="B6007" s="5" t="s">
+        <v>10522</v>
+      </c>
+    </row>
+    <row r="6008" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6008" s="5" t="s">
+        <v>10519</v>
+      </c>
+      <c r="B6008" s="5" t="s">
+        <v>10516</v>
+      </c>
+    </row>
+    <row r="6009" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6009" s="5" t="s">
+        <v>10520</v>
+      </c>
+      <c r="B6009" s="5" t="s">
+        <v>10523</v>
+      </c>
+    </row>
+    <row r="6010" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6010" s="5" t="s">
+        <v>10524</v>
+      </c>
+      <c r="B6010" s="5" t="s">
+        <v>10525</v>
+      </c>
+    </row>
+    <row r="6011" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6011" s="5" t="s">
+        <v>10526</v>
+      </c>
+      <c r="B6011" s="5" t="s">
+        <v>10530</v>
+      </c>
+    </row>
+    <row r="6012" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6012" s="5" t="s">
+        <v>10527</v>
+      </c>
+      <c r="B6012" s="5" t="s">
+        <v>10531</v>
+      </c>
+    </row>
+    <row r="6013" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6013" s="5" t="s">
+        <v>10528</v>
+      </c>
+      <c r="B6013" s="5" t="s">
+        <v>10532</v>
+      </c>
+    </row>
+    <row r="6014" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6014" s="5" t="s">
+        <v>10529</v>
+      </c>
+      <c r="B6014" s="5" t="s">
+        <v>10533</v>
+      </c>
+    </row>
+    <row r="6015" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6015" s="5" t="s">
+        <v>10534</v>
+      </c>
+    </row>
+    <row r="6016" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6016" s="5" t="s">
+        <v>3467</v>
+      </c>
+      <c r="B6016" s="5" t="s">
+        <v>10535</v>
+      </c>
+    </row>
+    <row r="6017" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6017" s="5" t="s">
+        <v>3468</v>
+      </c>
+      <c r="B6017" s="5" t="s">
+        <v>10537</v>
+      </c>
+    </row>
+    <row r="6018" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6018" s="5" t="s">
+        <v>10536</v>
+      </c>
+      <c r="B6018" s="5" t="s">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="6019" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6019" s="5" t="s">
+        <v>10539</v>
+      </c>
+      <c r="B6019" s="5" t="s">
+        <v>10540</v>
+      </c>
+    </row>
+    <row r="6020" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6020" s="5" t="s">
+        <v>10541</v>
+      </c>
+      <c r="B6020" s="5" t="s">
+        <v>10545</v>
+      </c>
+    </row>
+    <row r="6021" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6021" s="5" t="s">
+        <v>10542</v>
+      </c>
+      <c r="B6021" s="5" t="s">
+        <v>10546</v>
+      </c>
+    </row>
+    <row r="6022" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6022" s="5" t="s">
+        <v>10543</v>
+      </c>
+      <c r="B6022" s="5" t="s">
+        <v>10547</v>
+      </c>
+    </row>
+    <row r="6023" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6023" s="5" t="s">
+        <v>10544</v>
+      </c>
+      <c r="B6023" s="5" t="s">
+        <v>10548</v>
+      </c>
+    </row>
+    <row r="6024" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6024" s="5" t="s">
+        <v>10551</v>
+      </c>
+      <c r="B6024" s="5" t="s">
+        <v>10553</v>
+      </c>
+    </row>
+    <row r="6025" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6025" s="5" t="s">
+        <v>10554</v>
+      </c>
+      <c r="B6025" s="5" t="s">
+        <v>10552</v>
+      </c>
+    </row>
+    <row r="6026" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6026" s="5" t="s">
+        <v>10555</v>
+      </c>
+      <c r="B6026" s="5" t="s">
+        <v>10558</v>
+      </c>
+    </row>
+    <row r="6027" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6027" s="5" t="s">
+        <v>10556</v>
+      </c>
+      <c r="B6027" s="5" t="s">
+        <v>10559</v>
+      </c>
+    </row>
+    <row r="6028" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6028" s="5" t="s">
+        <v>10557</v>
+      </c>
+      <c r="B6028" s="5" t="s">
+        <v>10560</v>
+      </c>
+    </row>
+    <row r="6029" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6029" s="5" t="s">
+        <v>10561</v>
+      </c>
+      <c r="B6029" s="5" t="s">
+        <v>10562</v>
+      </c>
+    </row>
+    <row r="6030" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6030" s="5" t="s">
+        <v>10563</v>
+      </c>
+      <c r="B6030" s="5" t="s">
+        <v>10567</v>
+      </c>
+    </row>
+    <row r="6031" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6031" s="5" t="s">
+        <v>10564</v>
+      </c>
+      <c r="B6031" s="5" t="s">
+        <v>10568</v>
+      </c>
+    </row>
+    <row r="6032" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6032" s="5" t="s">
+        <v>10565</v>
+      </c>
+      <c r="B6032" s="5" t="s">
+        <v>10568</v>
+      </c>
+    </row>
+    <row r="6033" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6033" s="5" t="s">
+        <v>10566</v>
+      </c>
+      <c r="B6033" s="5" t="s">
+        <v>10569</v>
+      </c>
+    </row>
+    <row r="6034" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6034" s="5" t="s">
+        <v>10570</v>
+      </c>
+      <c r="B6034" s="5" t="s">
+        <v>10571</v>
+      </c>
+    </row>
+    <row r="6035" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6035" s="5" t="s">
+        <v>10572</v>
+      </c>
+      <c r="B6035" s="5" t="s">
+        <v>10576</v>
+      </c>
+    </row>
+    <row r="6036" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6036" s="5" t="s">
+        <v>10573</v>
+      </c>
+      <c r="B6036" s="5" t="s">
+        <v>10577</v>
+      </c>
+    </row>
+    <row r="6037" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6037" s="5" t="s">
+        <v>10574</v>
+      </c>
+      <c r="B6037" s="5" t="s">
+        <v>10578</v>
+      </c>
+    </row>
+    <row r="6038" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6038" s="5" t="s">
+        <v>10575</v>
+      </c>
+      <c r="B6038" s="5" t="s">
+        <v>10579</v>
+      </c>
+    </row>
+    <row r="6039" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6039" s="5" t="s">
+        <v>10584</v>
+      </c>
+      <c r="B6039" s="5" t="s">
+        <v>10585</v>
+      </c>
+    </row>
+    <row r="6040" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6040" s="5" t="s">
+        <v>10586</v>
+      </c>
+      <c r="B6040" s="5" t="s">
+        <v>10596</v>
+      </c>
+    </row>
+    <row r="6041" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6041" s="5" t="s">
+        <v>10587</v>
+      </c>
+      <c r="B6041" s="5" t="s">
+        <v>10597</v>
+      </c>
+    </row>
+    <row r="6042" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6042" s="5" t="s">
+        <v>10588</v>
+      </c>
+      <c r="B6042" s="5" t="s">
+        <v>10604</v>
+      </c>
+    </row>
+    <row r="6043" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6043" s="5" t="s">
+        <v>10589</v>
+      </c>
+      <c r="B6043" s="5" t="s">
+        <v>10605</v>
+      </c>
+    </row>
+    <row r="6044" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6044" s="5" t="s">
+        <v>10590</v>
+      </c>
+      <c r="B6044" s="5" t="s">
+        <v>10601</v>
+      </c>
+    </row>
+    <row r="6045" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6045" s="5" t="s">
+        <v>10591</v>
+      </c>
+      <c r="B6045" s="5" t="s">
+        <v>10598</v>
+      </c>
+    </row>
+    <row r="6046" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6046" s="5" t="s">
+        <v>10592</v>
+      </c>
+      <c r="B6046" s="5" t="s">
+        <v>10599</v>
+      </c>
+    </row>
+    <row r="6047" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6047" s="5" t="s">
+        <v>10593</v>
+      </c>
+      <c r="B6047" s="5" t="s">
+        <v>10600</v>
+      </c>
+    </row>
+    <row r="6048" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6048" s="5" t="s">
+        <v>10594</v>
+      </c>
+      <c r="B6048" s="5" t="s">
+        <v>10602</v>
+      </c>
+    </row>
+    <row r="6049" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6049" s="5" t="s">
+        <v>10595</v>
+      </c>
+      <c r="B6049" s="5" t="s">
+        <v>10603</v>
+      </c>
+    </row>
+    <row r="6050" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6050" s="5" t="s">
+        <v>10606</v>
+      </c>
+      <c r="B6050" s="5" t="s">
+        <v>10607</v>
+      </c>
+    </row>
+    <row r="6051" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6051" s="5" t="s">
+        <v>10608</v>
+      </c>
+      <c r="B6051" s="5" t="s">
+        <v>10626</v>
+      </c>
+    </row>
+    <row r="6052" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6052" s="5" t="s">
+        <v>10609</v>
+      </c>
+      <c r="B6052" s="5" t="s">
+        <v>10627</v>
+      </c>
+    </row>
+    <row r="6053" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6053" s="5" t="s">
+        <v>10610</v>
+      </c>
+      <c r="B6053" s="5" t="s">
+        <v>10628</v>
+      </c>
+    </row>
+    <row r="6054" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6054" s="5" t="s">
+        <v>10611</v>
+      </c>
+      <c r="B6054" s="5" t="s">
+        <v>10629</v>
+      </c>
+    </row>
+    <row r="6055" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6055" s="5" t="s">
+        <v>10612</v>
+      </c>
+      <c r="B6055" s="5" t="s">
+        <v>10630</v>
+      </c>
+    </row>
+    <row r="6056" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6056" s="5" t="s">
+        <v>10613</v>
+      </c>
+      <c r="B6056" s="5" t="s">
+        <v>10633</v>
+      </c>
+    </row>
+    <row r="6057" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6057" s="5" t="s">
+        <v>10614</v>
+      </c>
+      <c r="B6057" s="5" t="s">
+        <v>10634</v>
+      </c>
+    </row>
+    <row r="6058" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6058" s="5" t="s">
+        <v>10615</v>
+      </c>
+      <c r="B6058" s="5" t="s">
+        <v>10635</v>
+      </c>
+    </row>
+    <row r="6059" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6059" s="5" t="s">
+        <v>10616</v>
+      </c>
+      <c r="B6059" s="5" t="s">
+        <v>10636</v>
+      </c>
+    </row>
+    <row r="6060" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6060" s="5" t="s">
+        <v>10617</v>
+      </c>
+      <c r="B6060" s="5" t="s">
+        <v>10631</v>
+      </c>
+    </row>
+    <row r="6061" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6061" s="5" t="s">
+        <v>10618</v>
+      </c>
+      <c r="B6061" s="5" t="s">
+        <v>10632</v>
+      </c>
+    </row>
+    <row r="6062" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6062" s="5" t="s">
+        <v>10619</v>
+      </c>
+      <c r="B6062" s="5" t="s">
+        <v>10637</v>
+      </c>
+    </row>
+    <row r="6063" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6063" s="5" t="s">
+        <v>10620</v>
+      </c>
+      <c r="B6063" s="5" t="s">
+        <v>10638</v>
+      </c>
+    </row>
+    <row r="6064" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6064" s="5" t="s">
+        <v>10621</v>
+      </c>
+      <c r="B6064" s="5" t="s">
+        <v>10639</v>
+      </c>
+    </row>
+    <row r="6065" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6065" s="5" t="s">
+        <v>10622</v>
+      </c>
+      <c r="B6065" s="5" t="s">
+        <v>10640</v>
+      </c>
+    </row>
+    <row r="6066" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6066" s="5" t="s">
+        <v>10623</v>
+      </c>
+      <c r="B6066" s="5" t="s">
+        <v>10641</v>
+      </c>
+    </row>
+    <row r="6067" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6067" s="5" t="s">
+        <v>10624</v>
+      </c>
+      <c r="B6067" s="5" t="s">
+        <v>10642</v>
+      </c>
+    </row>
+    <row r="6068" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6068" s="5" t="s">
+        <v>10625</v>
+      </c>
+      <c r="B6068" s="5" t="s">
+        <v>10643</v>
+      </c>
+    </row>
+    <row r="6069" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6069" s="5" t="s">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="6070" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6070" s="5" t="s">
+        <v>10645</v>
+      </c>
+    </row>
+    <row r="6071" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6071" s="5" t="s">
+        <v>10646</v>
+      </c>
+      <c r="B6071" s="5" t="s">
+        <v>10647</v>
+      </c>
+    </row>
+    <row r="6072" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6072" s="5" t="s">
+        <v>10648</v>
+      </c>
+      <c r="B6072" s="5" t="s">
+        <v>10650</v>
+      </c>
+    </row>
+    <row r="6073" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6073" s="5" t="s">
+        <v>10649</v>
+      </c>
+      <c r="B6073" s="5" t="s">
+        <v>10651</v>
+      </c>
+    </row>
+    <row r="6074" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6074" s="5" t="s">
+        <v>10652</v>
+      </c>
+      <c r="B6074" s="5" t="s">
+        <v>10653</v>
+      </c>
+    </row>
+    <row r="6075" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6075" s="5" t="s">
+        <v>10654</v>
+      </c>
+      <c r="B6075" s="5" t="s">
+        <v>10655</v>
+      </c>
+    </row>
+    <row r="6076" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6076" s="5" t="s">
+        <v>10656</v>
+      </c>
+      <c r="B6076" s="5" t="s">
+        <v>10662</v>
+      </c>
+    </row>
+    <row r="6077" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6077" s="5" t="s">
+        <v>10658</v>
+      </c>
+      <c r="B6077" s="5" t="s">
+        <v>10657</v>
+      </c>
+    </row>
+    <row r="6078" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6078" s="5" t="s">
+        <v>10659</v>
+      </c>
+      <c r="B6078" s="5" t="s">
+        <v>10661</v>
+      </c>
+    </row>
+    <row r="6079" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6079" s="5" t="s">
+        <v>10660</v>
+      </c>
+      <c r="B6079" s="5" t="s">
+        <v>10663</v>
+      </c>
+    </row>
+    <row r="6080" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6080" s="5" t="s">
+        <v>10664</v>
+      </c>
+      <c r="B6080" s="5" t="s">
+        <v>10665</v>
+      </c>
+    </row>
+    <row r="6081" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6081" s="5" t="s">
+        <v>10666</v>
+      </c>
+      <c r="B6081" s="5" t="s">
+        <v>10698</v>
+      </c>
+    </row>
+    <row r="6082" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6082" s="5" t="s">
+        <v>10667</v>
+      </c>
+      <c r="B6082" s="5" t="s">
+        <v>10699</v>
+      </c>
+    </row>
+    <row r="6083" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6083" s="5" t="s">
+        <v>10668</v>
+      </c>
+      <c r="B6083" s="5" t="s">
+        <v>10700</v>
+      </c>
+    </row>
+    <row r="6084" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6084" s="5" t="s">
+        <v>10669</v>
+      </c>
+      <c r="B6084" s="5" t="s">
+        <v>10701</v>
+      </c>
+    </row>
+    <row r="6085" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6085" s="5" t="s">
+        <v>10670</v>
+      </c>
+      <c r="B6085" s="5" t="s">
+        <v>10702</v>
+      </c>
+    </row>
+    <row r="6086" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6086" s="5" t="s">
+        <v>10671</v>
+      </c>
+      <c r="B6086" s="5" t="s">
+        <v>10703</v>
+      </c>
+    </row>
+    <row r="6087" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6087" s="5" t="s">
+        <v>10672</v>
+      </c>
+      <c r="B6087" s="5" t="s">
+        <v>10704</v>
+      </c>
+    </row>
+    <row r="6088" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6088" s="5" t="s">
+        <v>10673</v>
+      </c>
+      <c r="B6088" s="5" t="s">
+        <v>10705</v>
+      </c>
+    </row>
+    <row r="6089" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6089" s="5" t="s">
+        <v>10674</v>
+      </c>
+      <c r="B6089" s="5" t="s">
+        <v>10706</v>
+      </c>
+    </row>
+    <row r="6090" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6090" s="5" t="s">
+        <v>10675</v>
+      </c>
+      <c r="B6090" s="5" t="s">
+        <v>10707</v>
+      </c>
+    </row>
+    <row r="6091" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6091" s="5" t="s">
+        <v>10676</v>
+      </c>
+      <c r="B6091" s="5" t="s">
+        <v>10708</v>
+      </c>
+    </row>
+    <row r="6092" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6092" s="5" t="s">
+        <v>10677</v>
+      </c>
+      <c r="B6092" s="5" t="s">
+        <v>10709</v>
+      </c>
+    </row>
+    <row r="6093" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6093" s="5" t="s">
+        <v>10678</v>
+      </c>
+      <c r="B6093" s="5" t="s">
+        <v>10710</v>
+      </c>
+    </row>
+    <row r="6094" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6094" s="5" t="s">
+        <v>10679</v>
+      </c>
+      <c r="B6094" s="5" t="s">
+        <v>10711</v>
+      </c>
+    </row>
+    <row r="6095" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6095" s="5" t="s">
+        <v>10680</v>
+      </c>
+      <c r="B6095" s="5" t="s">
+        <v>10712</v>
+      </c>
+    </row>
+    <row r="6096" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6096" s="5" t="s">
+        <v>10681</v>
+      </c>
+      <c r="B6096" s="5" t="s">
+        <v>10713</v>
+      </c>
+    </row>
+    <row r="6097" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6097" s="5" t="s">
+        <v>10682</v>
+      </c>
+      <c r="B6097" s="5" t="s">
+        <v>10714</v>
+      </c>
+    </row>
+    <row r="6098" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6098" s="5" t="s">
+        <v>10683</v>
+      </c>
+      <c r="B6098" s="5" t="s">
+        <v>10715</v>
+      </c>
+    </row>
+    <row r="6099" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6099" s="5" t="s">
+        <v>10684</v>
+      </c>
+      <c r="B6099" s="5" t="s">
+        <v>10716</v>
+      </c>
+    </row>
+    <row r="6100" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6100" s="5" t="s">
+        <v>10685</v>
+      </c>
+      <c r="B6100" s="5" t="s">
+        <v>10717</v>
+      </c>
+    </row>
+    <row r="6101" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6101" s="5" t="s">
+        <v>10686</v>
+      </c>
+      <c r="B6101" s="5" t="s">
+        <v>10718</v>
+      </c>
+    </row>
+    <row r="6102" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6102" s="5" t="s">
+        <v>10687</v>
+      </c>
+      <c r="B6102" s="5" t="s">
+        <v>10719</v>
+      </c>
+    </row>
+    <row r="6103" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6103" s="5" t="s">
+        <v>10688</v>
+      </c>
+      <c r="B6103" s="5" t="s">
+        <v>10720</v>
+      </c>
+    </row>
+    <row r="6104" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6104" s="5" t="s">
+        <v>10689</v>
+      </c>
+      <c r="B6104" s="5" t="s">
+        <v>10721</v>
+      </c>
+    </row>
+    <row r="6105" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6105" s="5" t="s">
+        <v>10690</v>
+      </c>
+      <c r="B6105" s="5" t="s">
+        <v>10722</v>
+      </c>
+    </row>
+    <row r="6106" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6106" s="5" t="s">
+        <v>10691</v>
+      </c>
+      <c r="B6106" s="5" t="s">
+        <v>10723</v>
+      </c>
+    </row>
+    <row r="6107" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6107" s="5" t="s">
+        <v>10692</v>
+      </c>
+      <c r="B6107" s="5" t="s">
+        <v>10724</v>
+      </c>
+    </row>
+    <row r="6108" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6108" s="5" t="s">
+        <v>10693</v>
+      </c>
+      <c r="B6108" s="5" t="s">
+        <v>10725</v>
+      </c>
+    </row>
+    <row r="6109" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6109" s="5" t="s">
+        <v>10694</v>
+      </c>
+      <c r="B6109" s="5" t="s">
+        <v>10726</v>
+      </c>
+    </row>
+    <row r="6110" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6110" s="5" t="s">
+        <v>10695</v>
+      </c>
+      <c r="B6110" s="5" t="s">
+        <v>10727</v>
+      </c>
+    </row>
+    <row r="6111" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6111" s="5" t="s">
+        <v>10696</v>
+      </c>
+      <c r="B6111" s="5" t="s">
+        <v>10728</v>
+      </c>
+    </row>
+    <row r="6112" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6112" s="5" t="s">
+        <v>10697</v>
+      </c>
+      <c r="B6112" s="5" t="s">
+        <v>10729</v>
+      </c>
+    </row>
+    <row r="6113" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6113" s="5" t="s">
+        <v>10730</v>
+      </c>
+      <c r="B6113" s="5" t="s">
+        <v>10731</v>
+      </c>
+    </row>
+    <row r="6114" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6114" s="5" t="s">
+        <v>10732</v>
+      </c>
+      <c r="B6114" s="5" t="s">
+        <v>10736</v>
+      </c>
+    </row>
+    <row r="6115" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6115" s="5" t="s">
+        <v>10733</v>
+      </c>
+      <c r="B6115" s="5" t="s">
+        <v>10737</v>
+      </c>
+    </row>
+    <row r="6116" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6116" s="5" t="s">
+        <v>10734</v>
+      </c>
+      <c r="B6116" s="5" t="s">
+        <v>10738</v>
+      </c>
+    </row>
+    <row r="6117" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6117" s="5" t="s">
+        <v>10735</v>
+      </c>
+      <c r="B6117" s="5" t="s">
+        <v>10739</v>
+      </c>
+    </row>
+    <row r="6118" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6118" s="5" t="s">
+        <v>10740</v>
+      </c>
+      <c r="B6118" s="5" t="s">
+        <v>10741</v>
+      </c>
+    </row>
+    <row r="6119" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6119" s="5" t="s">
+        <v>10742</v>
+      </c>
+      <c r="B6119" s="5" t="s">
+        <v>10746</v>
+      </c>
+    </row>
+    <row r="6120" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6120" s="5" t="s">
+        <v>10743</v>
+      </c>
+      <c r="B6120" s="5" t="s">
+        <v>10747</v>
+      </c>
+    </row>
+    <row r="6121" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6121" s="5" t="s">
+        <v>10744</v>
+      </c>
+      <c r="B6121" s="5" t="s">
+        <v>10748</v>
+      </c>
+    </row>
+    <row r="6122" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6122" s="5" t="s">
+        <v>10745</v>
+      </c>
+      <c r="B6122" s="5" t="s">
+        <v>10749</v>
       </c>
     </row>
   </sheetData>

--- a/словари/переведённые_слова.xlsx
+++ b/словари/переведённые_слова.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F13BB254-3908-4350-B14F-AF3E5ABA4C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2052F51E-E71E-4B3D-9C3D-6640DB6C3442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13455" yWindow="315" windowWidth="14175" windowHeight="14085" tabRatio="831" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="585" windowWidth="14175" windowHeight="14085" tabRatio="831" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="переведенные слова" sheetId="1" r:id="rId1"/>

--- a/словари/переведённые_слова.xlsx
+++ b/словари/переведённые_слова.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C72812D-A1A9-4C65-96C4-8BA8D6891BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DD05AA-26DC-40D3-BDF1-3EF97BA0D1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" tabRatio="831" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="831" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="переведенные слова" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Лист1" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Лист3!$A$1:$A$4110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Лист3!$A$1:$C$5814</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11540" uniqueCount="10650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11545" uniqueCount="10655">
   <si>
     <t>Абонемент - подписка</t>
   </si>
@@ -31983,6 +31983,21 @@
   </si>
   <si>
     <t>содержанец</t>
+  </si>
+  <si>
+    <t>альфонсам</t>
+  </si>
+  <si>
+    <t>альфонсами</t>
+  </si>
+  <si>
+    <t>альфонсах</t>
+  </si>
+  <si>
+    <t>альфонсы</t>
+  </si>
+  <si>
+    <t>альфонсов</t>
   </si>
 </sst>
 </file>
@@ -32470,7 +32485,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C5808"/>
+  <dimension ref="A1:C5813"/>
   <sheetFormatPr defaultColWidth="12.85546875" defaultRowHeight="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.140625" style="5" customWidth="1"/>
@@ -77985,8 +78000,33 @@
         <v>10168</v>
       </c>
     </row>
+    <row r="5809" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5809" s="5" t="s">
+        <v>10650</v>
+      </c>
+    </row>
+    <row r="5810" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5810" s="5" t="s">
+        <v>10651</v>
+      </c>
+    </row>
+    <row r="5811" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5811" s="5" t="s">
+        <v>10652</v>
+      </c>
+    </row>
+    <row r="5812" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5812" s="5" t="s">
+        <v>10653</v>
+      </c>
+    </row>
+    <row r="5813" spans="1:1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5813" s="5" t="s">
+        <v>10654</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A4110" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:C5814" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B1135">
     <sortCondition ref="A1:A1135"/>
   </sortState>

--- a/словари/переведённые_слова.xlsx
+++ b/словари/переведённые_слова.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DD05AA-26DC-40D3-BDF1-3EF97BA0D1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5CE391-3A62-47AB-97CB-C455F0ED6F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="831" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/словари/переведённые_слова.xlsx
+++ b/словари/переведённые_слова.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5CE391-3A62-47AB-97CB-C455F0ED6F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F33A8E-780C-417F-897F-75199587593E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="831" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="831" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="переведенные слова" sheetId="1" r:id="rId1"/>

--- a/словари/переведённые_слова.xlsx
+++ b/словари/переведённые_слова.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A7BACD-9F30-43F9-9072-B73D2504AC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C16E5B1-85EF-478F-995E-D5CFC30DD50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13575" yWindow="0" windowWidth="13890" windowHeight="14775" tabRatio="831" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9225" yWindow="60" windowWidth="18270" windowHeight="14100" tabRatio="831" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="переведенные слова" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12676" uniqueCount="11646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13374" uniqueCount="12306">
   <si>
     <t>Абонемент - подписка</t>
   </si>
@@ -34691,9 +34691,6 @@
     <t>феминизму</t>
   </si>
   <si>
-    <t>женское движение</t>
-  </si>
-  <si>
     <t>феминизм</t>
   </si>
   <si>
@@ -34706,15 +34703,6 @@
     <t>феминизмом</t>
   </si>
   <si>
-    <t>женского движения</t>
-  </si>
-  <si>
-    <t>женском движении</t>
-  </si>
-  <si>
-    <t>женским движением</t>
-  </si>
-  <si>
     <t>биржей</t>
   </si>
   <si>
@@ -34971,6 +34959,1998 @@
   </si>
   <si>
     <t>воздушным причалам</t>
+  </si>
+  <si>
+    <t>жено-властию</t>
+  </si>
+  <si>
+    <t>жено-властие</t>
+  </si>
+  <si>
+    <t>жено-властии</t>
+  </si>
+  <si>
+    <t>жено-властия</t>
+  </si>
+  <si>
+    <t>жено-властием</t>
+  </si>
+  <si>
+    <t>маскулинное</t>
+  </si>
+  <si>
+    <t>мужественное</t>
+  </si>
+  <si>
+    <t>маскулинной</t>
+  </si>
+  <si>
+    <t>маскулинном</t>
+  </si>
+  <si>
+    <t>маскулинному</t>
+  </si>
+  <si>
+    <t>маскулинности</t>
+  </si>
+  <si>
+    <t>маскулинность</t>
+  </si>
+  <si>
+    <t>маскулинную</t>
+  </si>
+  <si>
+    <t>маскулинные</t>
+  </si>
+  <si>
+    <t>маскулинный</t>
+  </si>
+  <si>
+    <t>маскулинным</t>
+  </si>
+  <si>
+    <t>маскулинными</t>
+  </si>
+  <si>
+    <t>маскулинных</t>
+  </si>
+  <si>
+    <t>маскулинного</t>
+  </si>
+  <si>
+    <t>мужественной</t>
+  </si>
+  <si>
+    <t>мужественном</t>
+  </si>
+  <si>
+    <t>мужественному</t>
+  </si>
+  <si>
+    <t>мужественности</t>
+  </si>
+  <si>
+    <t>мужественность</t>
+  </si>
+  <si>
+    <t>мужественную</t>
+  </si>
+  <si>
+    <t>мужественные</t>
+  </si>
+  <si>
+    <t>мужественный</t>
+  </si>
+  <si>
+    <t>мужественным</t>
+  </si>
+  <si>
+    <t>мужественными</t>
+  </si>
+  <si>
+    <t>мужественных</t>
+  </si>
+  <si>
+    <t>мужественного</t>
+  </si>
+  <si>
+    <t>феминное</t>
+  </si>
+  <si>
+    <t>женственное</t>
+  </si>
+  <si>
+    <t>феминного</t>
+  </si>
+  <si>
+    <t>феминной</t>
+  </si>
+  <si>
+    <t>феминном</t>
+  </si>
+  <si>
+    <t>феминному</t>
+  </si>
+  <si>
+    <t>феминную</t>
+  </si>
+  <si>
+    <t>феминные</t>
+  </si>
+  <si>
+    <t>феминный</t>
+  </si>
+  <si>
+    <t>феминным</t>
+  </si>
+  <si>
+    <t>феминными</t>
+  </si>
+  <si>
+    <t>феминных</t>
+  </si>
+  <si>
+    <t>женственного</t>
+  </si>
+  <si>
+    <t>женственной</t>
+  </si>
+  <si>
+    <t>женственном</t>
+  </si>
+  <si>
+    <t>женственному</t>
+  </si>
+  <si>
+    <t>женственную</t>
+  </si>
+  <si>
+    <t>женственные</t>
+  </si>
+  <si>
+    <t>женственный</t>
+  </si>
+  <si>
+    <t>женственным</t>
+  </si>
+  <si>
+    <t>женственными</t>
+  </si>
+  <si>
+    <t>женственных</t>
+  </si>
+  <si>
+    <t>физические</t>
+  </si>
+  <si>
+    <t>настоящие</t>
+  </si>
+  <si>
+    <t>физический</t>
+  </si>
+  <si>
+    <t>физическим</t>
+  </si>
+  <si>
+    <t>физическими</t>
+  </si>
+  <si>
+    <t>физических</t>
+  </si>
+  <si>
+    <t>физической</t>
+  </si>
+  <si>
+    <t>физическом</t>
+  </si>
+  <si>
+    <t>физическую</t>
+  </si>
+  <si>
+    <t>физическое</t>
+  </si>
+  <si>
+    <t>физическому</t>
+  </si>
+  <si>
+    <t>физического</t>
+  </si>
+  <si>
+    <t>настоящий</t>
+  </si>
+  <si>
+    <t>настоящим</t>
+  </si>
+  <si>
+    <t>настоящими</t>
+  </si>
+  <si>
+    <t>настоящих</t>
+  </si>
+  <si>
+    <t>настоящей</t>
+  </si>
+  <si>
+    <t>настоящую</t>
+  </si>
+  <si>
+    <t>настоящее</t>
+  </si>
+  <si>
+    <t>настоящему</t>
+  </si>
+  <si>
+    <t>настоящего</t>
+  </si>
+  <si>
+    <t>метаболизм</t>
+  </si>
+  <si>
+    <t>обмен веществ</t>
+  </si>
+  <si>
+    <t>метаболизма</t>
+  </si>
+  <si>
+    <t>метаболизму</t>
+  </si>
+  <si>
+    <t>метаболизме</t>
+  </si>
+  <si>
+    <t>метаболизмом</t>
+  </si>
+  <si>
+    <t>обмена веществ</t>
+  </si>
+  <si>
+    <t>обмену веществ</t>
+  </si>
+  <si>
+    <t>обмене веществ</t>
+  </si>
+  <si>
+    <t>обменом веществ</t>
+  </si>
+  <si>
+    <t>тонические</t>
+  </si>
+  <si>
+    <t>укрепляющие</t>
+  </si>
+  <si>
+    <t>тонический</t>
+  </si>
+  <si>
+    <t>тоническим</t>
+  </si>
+  <si>
+    <t>тоническими</t>
+  </si>
+  <si>
+    <t>тонических</t>
+  </si>
+  <si>
+    <t>тоническая</t>
+  </si>
+  <si>
+    <t>тоническом</t>
+  </si>
+  <si>
+    <t>тоническую</t>
+  </si>
+  <si>
+    <t>тоническое</t>
+  </si>
+  <si>
+    <t>тоническому</t>
+  </si>
+  <si>
+    <t>тонического</t>
+  </si>
+  <si>
+    <t>укрепляющий</t>
+  </si>
+  <si>
+    <t>укрепляющим</t>
+  </si>
+  <si>
+    <t>укрепляющими</t>
+  </si>
+  <si>
+    <t>укрепляющих</t>
+  </si>
+  <si>
+    <t>укрепляющая</t>
+  </si>
+  <si>
+    <t>укрепляющем</t>
+  </si>
+  <si>
+    <t>укрепляющую</t>
+  </si>
+  <si>
+    <t>укрепляющее</t>
+  </si>
+  <si>
+    <t>укрепляющему</t>
+  </si>
+  <si>
+    <t>укрепляющего</t>
+  </si>
+  <si>
+    <t>мускулатура</t>
+  </si>
+  <si>
+    <t>мышца</t>
+  </si>
+  <si>
+    <t>мускулатуры</t>
+  </si>
+  <si>
+    <t>мускулатуре</t>
+  </si>
+  <si>
+    <t>мускулатуру</t>
+  </si>
+  <si>
+    <t>мускулатурой</t>
+  </si>
+  <si>
+    <t>мышцы</t>
+  </si>
+  <si>
+    <t>мышце</t>
+  </si>
+  <si>
+    <t>мышцу</t>
+  </si>
+  <si>
+    <t>мышцей</t>
+  </si>
+  <si>
+    <t>оссификация</t>
+  </si>
+  <si>
+    <t>окостенение</t>
+  </si>
+  <si>
+    <t>оссификации</t>
+  </si>
+  <si>
+    <t>оссификацию</t>
+  </si>
+  <si>
+    <t>оссификацией</t>
+  </si>
+  <si>
+    <t>окостенении</t>
+  </si>
+  <si>
+    <t>окостенению</t>
+  </si>
+  <si>
+    <t>окостененией</t>
+  </si>
+  <si>
+    <t>психически</t>
+  </si>
+  <si>
+    <t>душевно</t>
+  </si>
+  <si>
+    <t>психические</t>
+  </si>
+  <si>
+    <t>психический</t>
+  </si>
+  <si>
+    <t>психическим</t>
+  </si>
+  <si>
+    <t>психическими</t>
+  </si>
+  <si>
+    <t>психических</t>
+  </si>
+  <si>
+    <t>психическом</t>
+  </si>
+  <si>
+    <t>психическую</t>
+  </si>
+  <si>
+    <t>психическое</t>
+  </si>
+  <si>
+    <t>душевные</t>
+  </si>
+  <si>
+    <t>душевный</t>
+  </si>
+  <si>
+    <t>душевным</t>
+  </si>
+  <si>
+    <t>душевными</t>
+  </si>
+  <si>
+    <t>душевных</t>
+  </si>
+  <si>
+    <t>душевном</t>
+  </si>
+  <si>
+    <t>душевную</t>
+  </si>
+  <si>
+    <t>душевное</t>
+  </si>
+  <si>
+    <t>ангедония</t>
+  </si>
+  <si>
+    <t>неумение радоваться</t>
+  </si>
+  <si>
+    <t>ангедонии</t>
+  </si>
+  <si>
+    <t>ангедонию</t>
+  </si>
+  <si>
+    <t>ангедонией</t>
+  </si>
+  <si>
+    <t>ангедониям</t>
+  </si>
+  <si>
+    <t>неумении радоваться</t>
+  </si>
+  <si>
+    <t>неумению радоваться</t>
+  </si>
+  <si>
+    <t>неумением радоваться</t>
+  </si>
+  <si>
+    <t>неумениям радоваться</t>
+  </si>
+  <si>
+    <t>иммунитет</t>
+  </si>
+  <si>
+    <t>невосприимчивость к болезням</t>
+  </si>
+  <si>
+    <t>иммунитета</t>
+  </si>
+  <si>
+    <t>иммунитету</t>
+  </si>
+  <si>
+    <t>иммунитете</t>
+  </si>
+  <si>
+    <t>иммунитетом</t>
+  </si>
+  <si>
+    <t>иммунитеты</t>
+  </si>
+  <si>
+    <t>иммунитетов</t>
+  </si>
+  <si>
+    <t>иммунитетам</t>
+  </si>
+  <si>
+    <t>иммунитетах</t>
+  </si>
+  <si>
+    <t>иммунитетами</t>
+  </si>
+  <si>
+    <t>невосприимчивости к болезням</t>
+  </si>
+  <si>
+    <t>невосприимчивостью к болезням</t>
+  </si>
+  <si>
+    <t>невосприимчивостей к болезням</t>
+  </si>
+  <si>
+    <t>невосприимчивостям к болезням</t>
+  </si>
+  <si>
+    <t>невосприимчивостях к болезням</t>
+  </si>
+  <si>
+    <t>невосприимчивостями к болезням</t>
+  </si>
+  <si>
+    <t>прогрессорской</t>
+  </si>
+  <si>
+    <t>современной</t>
+  </si>
+  <si>
+    <t>прогрессорская</t>
+  </si>
+  <si>
+    <t>прогрессорские</t>
+  </si>
+  <si>
+    <t>прогрессорский</t>
+  </si>
+  <si>
+    <t>прогрессорским</t>
+  </si>
+  <si>
+    <t>прогрессорскими</t>
+  </si>
+  <si>
+    <t>прогрессорских</t>
+  </si>
+  <si>
+    <t>прогрессорском</t>
+  </si>
+  <si>
+    <t>прогрессорскую</t>
+  </si>
+  <si>
+    <t>прогрессорскому</t>
+  </si>
+  <si>
+    <t>прогрессорского</t>
+  </si>
+  <si>
+    <t>современная</t>
+  </si>
+  <si>
+    <t>современные</t>
+  </si>
+  <si>
+    <t>современный</t>
+  </si>
+  <si>
+    <t>современним</t>
+  </si>
+  <si>
+    <t>современними</t>
+  </si>
+  <si>
+    <t>современних</t>
+  </si>
+  <si>
+    <t>современном</t>
+  </si>
+  <si>
+    <t>современную</t>
+  </si>
+  <si>
+    <t>современному</t>
+  </si>
+  <si>
+    <t>современного</t>
+  </si>
+  <si>
+    <t>стереотипизации</t>
+  </si>
+  <si>
+    <t>асоциальному</t>
+  </si>
+  <si>
+    <t>нелюдимому</t>
+  </si>
+  <si>
+    <t>асоциальные</t>
+  </si>
+  <si>
+    <t>асоциальный</t>
+  </si>
+  <si>
+    <t>асоциальным</t>
+  </si>
+  <si>
+    <t>асоциальными</t>
+  </si>
+  <si>
+    <t>асоциальных</t>
+  </si>
+  <si>
+    <t>асоциальная</t>
+  </si>
+  <si>
+    <t>асоциально</t>
+  </si>
+  <si>
+    <t>асоциальное</t>
+  </si>
+  <si>
+    <t>асоциальной</t>
+  </si>
+  <si>
+    <t>асоциальном</t>
+  </si>
+  <si>
+    <t>асоциальности</t>
+  </si>
+  <si>
+    <t>асоциальность</t>
+  </si>
+  <si>
+    <t>нелюдимые</t>
+  </si>
+  <si>
+    <t>нелюдимый</t>
+  </si>
+  <si>
+    <t>нелюдимым</t>
+  </si>
+  <si>
+    <t>нелюдимыми</t>
+  </si>
+  <si>
+    <t>нелюдимых</t>
+  </si>
+  <si>
+    <t>нелюдимая</t>
+  </si>
+  <si>
+    <t>нелюдимо</t>
+  </si>
+  <si>
+    <t>нелюдимое</t>
+  </si>
+  <si>
+    <t>нелюдимой</t>
+  </si>
+  <si>
+    <t>нелюдимом</t>
+  </si>
+  <si>
+    <t>нелюдимости</t>
+  </si>
+  <si>
+    <t>нелюдимость</t>
+  </si>
+  <si>
+    <t>социализация</t>
+  </si>
+  <si>
+    <t>процесс усвоения социальных норм</t>
+  </si>
+  <si>
+    <t>социализации</t>
+  </si>
+  <si>
+    <t>социализацией</t>
+  </si>
+  <si>
+    <t>социализациями</t>
+  </si>
+  <si>
+    <t>социализациях</t>
+  </si>
+  <si>
+    <t>процесса усвоения социальных норм</t>
+  </si>
+  <si>
+    <t>процессом усвоения социальных норм</t>
+  </si>
+  <si>
+    <t>процессами усвоения социальных норм</t>
+  </si>
+  <si>
+    <t>процессах усвоения социальных норм</t>
+  </si>
+  <si>
+    <t>гениев</t>
+  </si>
+  <si>
+    <t>гений</t>
+  </si>
+  <si>
+    <t>гениям</t>
+  </si>
+  <si>
+    <t>гениями</t>
+  </si>
+  <si>
+    <t>гениях</t>
+  </si>
+  <si>
+    <t>гении</t>
+  </si>
+  <si>
+    <t>гениальное</t>
+  </si>
+  <si>
+    <t>гениальной</t>
+  </si>
+  <si>
+    <t>гениальном</t>
+  </si>
+  <si>
+    <t>гениальному</t>
+  </si>
+  <si>
+    <t>гениальную</t>
+  </si>
+  <si>
+    <t>гениальные</t>
+  </si>
+  <si>
+    <t>гениальный</t>
+  </si>
+  <si>
+    <t>гениальным</t>
+  </si>
+  <si>
+    <t>гениальными</t>
+  </si>
+  <si>
+    <t>гениально</t>
+  </si>
+  <si>
+    <t>способность</t>
+  </si>
+  <si>
+    <t>способности</t>
+  </si>
+  <si>
+    <t>способностям</t>
+  </si>
+  <si>
+    <t>способностями</t>
+  </si>
+  <si>
+    <t>способностях</t>
+  </si>
+  <si>
+    <t>способное</t>
+  </si>
+  <si>
+    <t>способной</t>
+  </si>
+  <si>
+    <t>способном</t>
+  </si>
+  <si>
+    <t>способному</t>
+  </si>
+  <si>
+    <t>способную</t>
+  </si>
+  <si>
+    <t>способные</t>
+  </si>
+  <si>
+    <t>способный</t>
+  </si>
+  <si>
+    <t>способным</t>
+  </si>
+  <si>
+    <t>способными</t>
+  </si>
+  <si>
+    <t>способно</t>
+  </si>
+  <si>
+    <t>одиозных</t>
+  </si>
+  <si>
+    <t>неприятных</t>
+  </si>
+  <si>
+    <t>одиозный</t>
+  </si>
+  <si>
+    <t>одиозные</t>
+  </si>
+  <si>
+    <t>одиозным</t>
+  </si>
+  <si>
+    <t>одиозными</t>
+  </si>
+  <si>
+    <t>одиозная</t>
+  </si>
+  <si>
+    <t>одиозно</t>
+  </si>
+  <si>
+    <t>одиозное</t>
+  </si>
+  <si>
+    <t>одиозной</t>
+  </si>
+  <si>
+    <t>одиозном</t>
+  </si>
+  <si>
+    <t>одиозному</t>
+  </si>
+  <si>
+    <t>одиозности</t>
+  </si>
+  <si>
+    <t>одиозность</t>
+  </si>
+  <si>
+    <t>неприятный</t>
+  </si>
+  <si>
+    <t>неприятные</t>
+  </si>
+  <si>
+    <t>неприятным</t>
+  </si>
+  <si>
+    <t>неприятными</t>
+  </si>
+  <si>
+    <t>неприятная</t>
+  </si>
+  <si>
+    <t>неприятно</t>
+  </si>
+  <si>
+    <t>неприятное</t>
+  </si>
+  <si>
+    <t>неприятной</t>
+  </si>
+  <si>
+    <t>неприятном</t>
+  </si>
+  <si>
+    <t>неприятному</t>
+  </si>
+  <si>
+    <t>неприятности</t>
+  </si>
+  <si>
+    <t>неприятность</t>
+  </si>
+  <si>
+    <t>вариативность</t>
+  </si>
+  <si>
+    <t>разнообразие</t>
+  </si>
+  <si>
+    <t>вариативная</t>
+  </si>
+  <si>
+    <t>вариативно</t>
+  </si>
+  <si>
+    <t>вариативное</t>
+  </si>
+  <si>
+    <t>вариативной</t>
+  </si>
+  <si>
+    <t>вариативном</t>
+  </si>
+  <si>
+    <t>вариативному</t>
+  </si>
+  <si>
+    <t>вариативности</t>
+  </si>
+  <si>
+    <t>вариативные</t>
+  </si>
+  <si>
+    <t>вариативный</t>
+  </si>
+  <si>
+    <t>вариативным</t>
+  </si>
+  <si>
+    <t>вариативными</t>
+  </si>
+  <si>
+    <t>вариативных</t>
+  </si>
+  <si>
+    <t>разнообразная</t>
+  </si>
+  <si>
+    <t>разнообразно</t>
+  </si>
+  <si>
+    <t>разнообразное</t>
+  </si>
+  <si>
+    <t>разнообразной</t>
+  </si>
+  <si>
+    <t>разнообразном</t>
+  </si>
+  <si>
+    <t>разнообразному</t>
+  </si>
+  <si>
+    <t>разнообразности</t>
+  </si>
+  <si>
+    <t>разнообразные</t>
+  </si>
+  <si>
+    <t>разнообразный</t>
+  </si>
+  <si>
+    <t>разнообразным</t>
+  </si>
+  <si>
+    <t>разнообразными</t>
+  </si>
+  <si>
+    <t>разнообразных</t>
+  </si>
+  <si>
+    <t>компенсаторный</t>
+  </si>
+  <si>
+    <t>исправительный</t>
+  </si>
+  <si>
+    <t>компенсаторные</t>
+  </si>
+  <si>
+    <t>компенсаторным</t>
+  </si>
+  <si>
+    <t>компенсаторными</t>
+  </si>
+  <si>
+    <t>компенсаторных</t>
+  </si>
+  <si>
+    <t>компенсаторная</t>
+  </si>
+  <si>
+    <t>компенсаторно</t>
+  </si>
+  <si>
+    <t>компенсаторное</t>
+  </si>
+  <si>
+    <t>компенсаторной</t>
+  </si>
+  <si>
+    <t>компенсаторном</t>
+  </si>
+  <si>
+    <t>компенсаторному</t>
+  </si>
+  <si>
+    <t>компенсаторности</t>
+  </si>
+  <si>
+    <t>компенсаторность</t>
+  </si>
+  <si>
+    <t>исправительные</t>
+  </si>
+  <si>
+    <t>исправительным</t>
+  </si>
+  <si>
+    <t>исправительными</t>
+  </si>
+  <si>
+    <t>исправительных</t>
+  </si>
+  <si>
+    <t>исправительная</t>
+  </si>
+  <si>
+    <t>исправительно</t>
+  </si>
+  <si>
+    <t>исправительное</t>
+  </si>
+  <si>
+    <t>исправительной</t>
+  </si>
+  <si>
+    <t>исправительности</t>
+  </si>
+  <si>
+    <t>исправительность</t>
+  </si>
+  <si>
+    <t>исправительном</t>
+  </si>
+  <si>
+    <t>исправительному</t>
+  </si>
+  <si>
+    <t>алкоголизм</t>
+  </si>
+  <si>
+    <t>алкоголизма</t>
+  </si>
+  <si>
+    <t>алкоголизму</t>
+  </si>
+  <si>
+    <t>алкоголизме</t>
+  </si>
+  <si>
+    <t>алкоголизмом</t>
+  </si>
+  <si>
+    <t>алкоголизмами</t>
+  </si>
+  <si>
+    <t>алкоголизмах</t>
+  </si>
+  <si>
+    <t>алкоголному</t>
+  </si>
+  <si>
+    <t>алкоголную</t>
+  </si>
+  <si>
+    <t>алкоголные</t>
+  </si>
+  <si>
+    <t>алкоголный</t>
+  </si>
+  <si>
+    <t>алкоголным</t>
+  </si>
+  <si>
+    <t>алкоголными</t>
+  </si>
+  <si>
+    <t>алкоголных</t>
+  </si>
+  <si>
+    <t>пьянство</t>
+  </si>
+  <si>
+    <t>пьянства</t>
+  </si>
+  <si>
+    <t>пьянству</t>
+  </si>
+  <si>
+    <t>пьянстве</t>
+  </si>
+  <si>
+    <t>пьянством</t>
+  </si>
+  <si>
+    <t>пьянствами</t>
+  </si>
+  <si>
+    <t>пьянствах</t>
+  </si>
+  <si>
+    <t>пьяному</t>
+  </si>
+  <si>
+    <t>пьяную</t>
+  </si>
+  <si>
+    <t>пьяные</t>
+  </si>
+  <si>
+    <t>пьяный</t>
+  </si>
+  <si>
+    <t>пьяным</t>
+  </si>
+  <si>
+    <t>пьяными</t>
+  </si>
+  <si>
+    <t>пьяных</t>
+  </si>
+  <si>
+    <t>наркомания</t>
+  </si>
+  <si>
+    <t>зависимость</t>
+  </si>
+  <si>
+    <t>наркомании</t>
+  </si>
+  <si>
+    <t>наркоманить</t>
+  </si>
+  <si>
+    <t>наркоманят</t>
+  </si>
+  <si>
+    <t>зависимости</t>
+  </si>
+  <si>
+    <t>зависим</t>
+  </si>
+  <si>
+    <t>зависеть</t>
+  </si>
+  <si>
+    <t>зависят</t>
+  </si>
+  <si>
+    <t>допенсионном</t>
+  </si>
+  <si>
+    <t>миокарда</t>
+  </si>
+  <si>
+    <t>кафедра</t>
+  </si>
+  <si>
+    <t>учебный отдел</t>
+  </si>
+  <si>
+    <t>кафедры</t>
+  </si>
+  <si>
+    <t>кафедру</t>
+  </si>
+  <si>
+    <t>кафедре</t>
+  </si>
+  <si>
+    <t>кафедрой</t>
+  </si>
+  <si>
+    <t>кафедрами</t>
+  </si>
+  <si>
+    <t>кафедрах</t>
+  </si>
+  <si>
+    <t>кафедрам</t>
+  </si>
+  <si>
+    <t>учебные отделы</t>
+  </si>
+  <si>
+    <t>учебному отделу</t>
+  </si>
+  <si>
+    <t>учебным отделом</t>
+  </si>
+  <si>
+    <t>учебными отделами</t>
+  </si>
+  <si>
+    <t>учебных отделах</t>
+  </si>
+  <si>
+    <t>учебным отделам</t>
+  </si>
+  <si>
+    <t>профессорско</t>
+  </si>
+  <si>
+    <t>гуманитарных</t>
+  </si>
+  <si>
+    <t>человеческих</t>
+  </si>
+  <si>
+    <t>гуманитарным</t>
+  </si>
+  <si>
+    <t>гуманитарный</t>
+  </si>
+  <si>
+    <t>гуманитарные</t>
+  </si>
+  <si>
+    <t>гуманитарность</t>
+  </si>
+  <si>
+    <t>гуманитарностью</t>
+  </si>
+  <si>
+    <t>гуманитарному</t>
+  </si>
+  <si>
+    <t>гуманитарном</t>
+  </si>
+  <si>
+    <t>гуманитарной</t>
+  </si>
+  <si>
+    <t>гуманитарное</t>
+  </si>
+  <si>
+    <t>гуманитарная</t>
+  </si>
+  <si>
+    <t>гуманитарна</t>
+  </si>
+  <si>
+    <t>человеческим</t>
+  </si>
+  <si>
+    <t>человеческий</t>
+  </si>
+  <si>
+    <t>человеческие</t>
+  </si>
+  <si>
+    <t>человечность</t>
+  </si>
+  <si>
+    <t>человечностью</t>
+  </si>
+  <si>
+    <t>человечному</t>
+  </si>
+  <si>
+    <t>человечном</t>
+  </si>
+  <si>
+    <t>человечной</t>
+  </si>
+  <si>
+    <t>человечное</t>
+  </si>
+  <si>
+    <t>человечная</t>
+  </si>
+  <si>
+    <t>человечна</t>
+  </si>
+  <si>
+    <t>монографии</t>
+  </si>
+  <si>
+    <t>исследования</t>
+  </si>
+  <si>
+    <t>монография</t>
+  </si>
+  <si>
+    <t>монографий</t>
+  </si>
+  <si>
+    <t>монографиям</t>
+  </si>
+  <si>
+    <t>монографиями</t>
+  </si>
+  <si>
+    <t>монографиях</t>
+  </si>
+  <si>
+    <t>исследований</t>
+  </si>
+  <si>
+    <t>исследованиям</t>
+  </si>
+  <si>
+    <t>исследованиями</t>
+  </si>
+  <si>
+    <t>исследованиях</t>
+  </si>
+  <si>
+    <t>гендерных</t>
+  </si>
+  <si>
+    <t>половых</t>
+  </si>
+  <si>
+    <t>гендерные</t>
+  </si>
+  <si>
+    <t>гендерным</t>
+  </si>
+  <si>
+    <t>гендерными</t>
+  </si>
+  <si>
+    <t>гендерное</t>
+  </si>
+  <si>
+    <t>гендерном</t>
+  </si>
+  <si>
+    <t>гендерному</t>
+  </si>
+  <si>
+    <t>гендерную</t>
+  </si>
+  <si>
+    <t>гендерный</t>
+  </si>
+  <si>
+    <t>половые</t>
+  </si>
+  <si>
+    <t>половым</t>
+  </si>
+  <si>
+    <t>половыми</t>
+  </si>
+  <si>
+    <t>половое</t>
+  </si>
+  <si>
+    <t>половом</t>
+  </si>
+  <si>
+    <t>половому</t>
+  </si>
+  <si>
+    <t>половую</t>
+  </si>
+  <si>
+    <t>половой</t>
+  </si>
+  <si>
+    <t>ринг</t>
+  </si>
+  <si>
+    <t>помост</t>
+  </si>
+  <si>
+    <t>ринга</t>
+  </si>
+  <si>
+    <t>ринге</t>
+  </si>
+  <si>
+    <t>рингу</t>
+  </si>
+  <si>
+    <t>рингом</t>
+  </si>
+  <si>
+    <t>рингами</t>
+  </si>
+  <si>
+    <t>рингах</t>
+  </si>
+  <si>
+    <t>ринги</t>
+  </si>
+  <si>
+    <t>помоста</t>
+  </si>
+  <si>
+    <t>помосте</t>
+  </si>
+  <si>
+    <t>помосту</t>
+  </si>
+  <si>
+    <t>помостом</t>
+  </si>
+  <si>
+    <t>помостами</t>
+  </si>
+  <si>
+    <t>помостах</t>
+  </si>
+  <si>
+    <t>помосты</t>
+  </si>
+  <si>
+    <t>круиз</t>
+  </si>
+  <si>
+    <t>путешествие</t>
+  </si>
+  <si>
+    <t>круиза</t>
+  </si>
+  <si>
+    <t>круизе</t>
+  </si>
+  <si>
+    <t>круизу</t>
+  </si>
+  <si>
+    <t>круизом</t>
+  </si>
+  <si>
+    <t>круизами</t>
+  </si>
+  <si>
+    <t>круизах</t>
+  </si>
+  <si>
+    <t>круизов</t>
+  </si>
+  <si>
+    <t>путешествия</t>
+  </si>
+  <si>
+    <t>путешествии</t>
+  </si>
+  <si>
+    <t>путешествию</t>
+  </si>
+  <si>
+    <t>путешествием</t>
+  </si>
+  <si>
+    <t>путешествиями</t>
+  </si>
+  <si>
+    <t>путешествиях</t>
+  </si>
+  <si>
+    <t>путешествий</t>
+  </si>
+  <si>
+    <t>супермаркет</t>
+  </si>
+  <si>
+    <t>торговая  точка</t>
+  </si>
+  <si>
+    <t>супермаркета</t>
+  </si>
+  <si>
+    <t>супермаркету</t>
+  </si>
+  <si>
+    <t>супермаркете</t>
+  </si>
+  <si>
+    <t>супермаркетом</t>
+  </si>
+  <si>
+    <t>супермаркетах</t>
+  </si>
+  <si>
+    <t>супермаркетов</t>
+  </si>
+  <si>
+    <t>супермаркеты</t>
+  </si>
+  <si>
+    <t>супермаркетам</t>
+  </si>
+  <si>
+    <t>торговой  точки</t>
+  </si>
+  <si>
+    <t>торговаую  точку</t>
+  </si>
+  <si>
+    <t>торговой точке</t>
+  </si>
+  <si>
+    <t>торговой  точкой</t>
+  </si>
+  <si>
+    <t>торговых точках</t>
+  </si>
+  <si>
+    <t>торговаых точек</t>
+  </si>
+  <si>
+    <t>торговые  точки</t>
+  </si>
+  <si>
+    <t>торговым  точкам</t>
+  </si>
+  <si>
+    <t>урегулировать</t>
+  </si>
+  <si>
+    <t>решить</t>
+  </si>
+  <si>
+    <t>урегулированы</t>
+  </si>
+  <si>
+    <t>урегулироваться</t>
+  </si>
+  <si>
+    <t>урегулируем</t>
+  </si>
+  <si>
+    <t>урегулируема</t>
+  </si>
+  <si>
+    <t>урегулируемая</t>
+  </si>
+  <si>
+    <t>урегулируемого</t>
+  </si>
+  <si>
+    <t>урегулируемое</t>
+  </si>
+  <si>
+    <t>урегулируемой</t>
+  </si>
+  <si>
+    <t>урегулируемом</t>
+  </si>
+  <si>
+    <t>урегулируемому</t>
+  </si>
+  <si>
+    <t>урегулируемую</t>
+  </si>
+  <si>
+    <t>урегулируемые</t>
+  </si>
+  <si>
+    <t>урегулируемый</t>
+  </si>
+  <si>
+    <t>урегулируемым</t>
+  </si>
+  <si>
+    <t>урегулируемыми</t>
+  </si>
+  <si>
+    <t>урегулирует</t>
+  </si>
+  <si>
+    <t>урегулируют</t>
+  </si>
+  <si>
+    <t>урегулирующие</t>
+  </si>
+  <si>
+    <t>урегулирующий</t>
+  </si>
+  <si>
+    <t>решены</t>
+  </si>
+  <si>
+    <t>решиться</t>
+  </si>
+  <si>
+    <t>решаема</t>
+  </si>
+  <si>
+    <t>решаемая</t>
+  </si>
+  <si>
+    <t>решаемого</t>
+  </si>
+  <si>
+    <t>решаемое</t>
+  </si>
+  <si>
+    <t>решаемой</t>
+  </si>
+  <si>
+    <t>решаемом</t>
+  </si>
+  <si>
+    <t>решаемому</t>
+  </si>
+  <si>
+    <t>решаемую</t>
+  </si>
+  <si>
+    <t>решаемые</t>
+  </si>
+  <si>
+    <t>решаемый</t>
+  </si>
+  <si>
+    <t>решаемым</t>
+  </si>
+  <si>
+    <t>решаемыми</t>
+  </si>
+  <si>
+    <t>решает</t>
+  </si>
+  <si>
+    <t>решаем</t>
+  </si>
+  <si>
+    <t>решают</t>
+  </si>
+  <si>
+    <t>решающие</t>
+  </si>
+  <si>
+    <t>решающий</t>
+  </si>
+  <si>
+    <t>невротизированного</t>
+  </si>
+  <si>
+    <t>утилитарные</t>
+  </si>
+  <si>
+    <t>полезные</t>
+  </si>
+  <si>
+    <t>утилитарную</t>
+  </si>
+  <si>
+    <t>утилитарный</t>
+  </si>
+  <si>
+    <t>утилитарным</t>
+  </si>
+  <si>
+    <t>утилитарных</t>
+  </si>
+  <si>
+    <t>полезную</t>
+  </si>
+  <si>
+    <t>полезный</t>
+  </si>
+  <si>
+    <t>полезным</t>
+  </si>
+  <si>
+    <t>полезных</t>
+  </si>
+  <si>
+    <t>утилитарная</t>
+  </si>
+  <si>
+    <t>утилитарного</t>
+  </si>
+  <si>
+    <t>утилитарное</t>
+  </si>
+  <si>
+    <t>утилитарной</t>
+  </si>
+  <si>
+    <t>утилитарном</t>
+  </si>
+  <si>
+    <t>утилитарному</t>
+  </si>
+  <si>
+    <t>полезная</t>
+  </si>
+  <si>
+    <t>полезного</t>
+  </si>
+  <si>
+    <t>полезной</t>
+  </si>
+  <si>
+    <t>полезном</t>
+  </si>
+  <si>
+    <t>полезному</t>
+  </si>
+  <si>
+    <t>парфюма</t>
+  </si>
+  <si>
+    <t>запах</t>
+  </si>
+  <si>
+    <t>парфюм</t>
+  </si>
+  <si>
+    <t>парфюму</t>
+  </si>
+  <si>
+    <t>парфюмом</t>
+  </si>
+  <si>
+    <t>парфюме</t>
+  </si>
+  <si>
+    <t>парфюмах</t>
+  </si>
+  <si>
+    <t>парфюмерному</t>
+  </si>
+  <si>
+    <t>парфюмерную</t>
+  </si>
+  <si>
+    <t>парфюмерные</t>
+  </si>
+  <si>
+    <t>парфюмерный</t>
+  </si>
+  <si>
+    <t>парфюмерным</t>
+  </si>
+  <si>
+    <t>парфюмерными</t>
+  </si>
+  <si>
+    <t>парфюмерных</t>
+  </si>
+  <si>
+    <t>запаха</t>
+  </si>
+  <si>
+    <t>запаху</t>
+  </si>
+  <si>
+    <t>запахом</t>
+  </si>
+  <si>
+    <t>запахе</t>
+  </si>
+  <si>
+    <t>запахах</t>
+  </si>
+  <si>
+    <t>косметика</t>
+  </si>
+  <si>
+    <t>украшение</t>
+  </si>
+  <si>
+    <t>косметики</t>
+  </si>
+  <si>
+    <t>косметику</t>
+  </si>
+  <si>
+    <t>косметике</t>
+  </si>
+  <si>
+    <t>косметикой</t>
+  </si>
+  <si>
+    <t>косметическая</t>
+  </si>
+  <si>
+    <t>украшения</t>
+  </si>
+  <si>
+    <t>украшению</t>
+  </si>
+  <si>
+    <t>украшении</t>
+  </si>
+  <si>
+    <t>украшением</t>
+  </si>
+  <si>
+    <t>косметические</t>
+  </si>
+  <si>
+    <t>косметический</t>
+  </si>
+  <si>
+    <t>косметическим</t>
+  </si>
+  <si>
+    <t>косметическими</t>
+  </si>
+  <si>
+    <t>косметических</t>
+  </si>
+  <si>
+    <t>косметической</t>
+  </si>
+  <si>
+    <t>косметическом</t>
+  </si>
+  <si>
+    <t>косметическую</t>
+  </si>
+  <si>
+    <t>косметическое</t>
+  </si>
+  <si>
+    <t>косметическому</t>
+  </si>
+  <si>
+    <t>косметического</t>
+  </si>
+  <si>
+    <t>украшаемом</t>
+  </si>
+  <si>
+    <t>украшаемую</t>
+  </si>
+  <si>
+    <t>украшаемому</t>
+  </si>
+  <si>
+    <t>украшаемого</t>
+  </si>
+  <si>
+    <t>укпашаемое</t>
+  </si>
+  <si>
+    <t>парфюмерия</t>
+  </si>
+  <si>
+    <t>парфюмерией</t>
+  </si>
+  <si>
+    <t>парфюмерии</t>
+  </si>
+  <si>
+    <t>парфюмериям</t>
+  </si>
+  <si>
+    <t>украшенному</t>
+  </si>
+  <si>
+    <t>украшенную</t>
+  </si>
+  <si>
+    <t>украшенные</t>
+  </si>
+  <si>
+    <t>украшенный</t>
+  </si>
+  <si>
+    <t>украшенным</t>
+  </si>
+  <si>
+    <t>украшенными</t>
+  </si>
+  <si>
+    <t>украшенных</t>
+  </si>
+  <si>
+    <t>украшенния</t>
+  </si>
+  <si>
+    <t>украшеннием</t>
+  </si>
+  <si>
+    <t>украшениям</t>
+  </si>
+  <si>
+    <t>макияж</t>
+  </si>
+  <si>
+    <t>покраска</t>
+  </si>
+  <si>
+    <t>макияжа</t>
+  </si>
+  <si>
+    <t>макияжу</t>
+  </si>
+  <si>
+    <t>макияже</t>
+  </si>
+  <si>
+    <t>макияжом</t>
+  </si>
+  <si>
+    <t>макияжи</t>
+  </si>
+  <si>
+    <t>макияжами</t>
+  </si>
+  <si>
+    <t>макияжах</t>
+  </si>
+  <si>
+    <t>макияжам</t>
+  </si>
+  <si>
+    <t>покраски</t>
+  </si>
+  <si>
+    <t>покраске</t>
+  </si>
+  <si>
+    <t>покраской</t>
+  </si>
+  <si>
+    <t>покрасками</t>
+  </si>
+  <si>
+    <t>покрасках</t>
+  </si>
+  <si>
+    <t>покраскам</t>
+  </si>
+  <si>
+    <t>сомоиронии</t>
+  </si>
+  <si>
+    <t>стилистические</t>
+  </si>
+  <si>
+    <t>языковые</t>
+  </si>
+  <si>
+    <t>стилистический</t>
+  </si>
+  <si>
+    <t>стилистическим</t>
+  </si>
+  <si>
+    <t>стилистическими</t>
+  </si>
+  <si>
+    <t>стилистических</t>
+  </si>
+  <si>
+    <t>стилистическом</t>
+  </si>
+  <si>
+    <t>стилистическую</t>
+  </si>
+  <si>
+    <t>стилистическое</t>
+  </si>
+  <si>
+    <t>стилистическому</t>
+  </si>
+  <si>
+    <t>стилистического</t>
+  </si>
+  <si>
+    <t>языковый</t>
+  </si>
+  <si>
+    <t>языковым</t>
+  </si>
+  <si>
+    <t>языковыми</t>
+  </si>
+  <si>
+    <t>языковых</t>
+  </si>
+  <si>
+    <t>языковом</t>
+  </si>
+  <si>
+    <t>языковую</t>
+  </si>
+  <si>
+    <t>языковое</t>
+  </si>
+  <si>
+    <t>языковому</t>
+  </si>
+  <si>
+    <t>языкового</t>
+  </si>
+  <si>
+    <t>штамповкой</t>
+  </si>
+  <si>
+    <t>ковкой</t>
+  </si>
+  <si>
+    <t>штамповка</t>
+  </si>
+  <si>
+    <t>штамповки</t>
+  </si>
+  <si>
+    <t>штамповке</t>
+  </si>
+  <si>
+    <t>штамповку</t>
+  </si>
+  <si>
+    <t>ковка</t>
+  </si>
+  <si>
+    <t>ковки</t>
+  </si>
+  <si>
+    <t>ковке</t>
+  </si>
+  <si>
+    <t>ковку</t>
   </si>
 </sst>
 </file>
@@ -35443,7 +37423,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C6375"/>
+  <dimension ref="A1:C6727"/>
   <sheetFormatPr defaultColWidth="12.85546875" defaultRowHeight="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.140625" style="5" customWidth="1"/>
@@ -35473,7 +37453,7 @@
         <v>69</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>11645</v>
+        <v>11641</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -78608,7 +80588,7 @@
         <v>10630</v>
       </c>
     </row>
-    <row r="5507" spans="1:3" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5507" spans="1:3" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5507" s="5" t="s">
         <v>9094</v>
       </c>
@@ -85084,47 +87064,47 @@
         <v>11551</v>
       </c>
       <c r="B6323" s="5" t="s">
-        <v>11557</v>
+        <v>11642</v>
       </c>
     </row>
     <row r="6324" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6324" s="5" t="s">
-        <v>11553</v>
+        <v>11552</v>
       </c>
       <c r="B6324" s="5" t="s">
-        <v>11552</v>
+        <v>11643</v>
       </c>
     </row>
     <row r="6325" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6325" s="5" t="s">
-        <v>11554</v>
+        <v>11553</v>
       </c>
       <c r="B6325" s="5" t="s">
-        <v>11558</v>
+        <v>11644</v>
       </c>
     </row>
     <row r="6326" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6326" s="5" t="s">
-        <v>11555</v>
+        <v>11554</v>
       </c>
       <c r="B6326" s="5" t="s">
-        <v>11557</v>
+        <v>11645</v>
       </c>
     </row>
     <row r="6327" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6327" s="5" t="s">
-        <v>11556</v>
+        <v>11555</v>
       </c>
       <c r="B6327" s="5" t="s">
-        <v>11559</v>
+        <v>11646</v>
       </c>
     </row>
     <row r="6328" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6328" s="5" t="s">
+        <v>11556</v>
+      </c>
+      <c r="B6328" s="5" t="s">
         <v>11560</v>
-      </c>
-      <c r="B6328" s="5" t="s">
-        <v>11564</v>
       </c>
     </row>
     <row r="6329" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -85132,297 +87112,297 @@
         <v>8899</v>
       </c>
       <c r="B6329" s="5" t="s">
-        <v>11561</v>
+        <v>11557</v>
       </c>
     </row>
     <row r="6330" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6330" s="5" t="s">
-        <v>11562</v>
+        <v>11558</v>
       </c>
       <c r="B6330" s="5" t="s">
-        <v>11565</v>
+        <v>11561</v>
       </c>
     </row>
     <row r="6331" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6331" s="5" t="s">
-        <v>11563</v>
+        <v>11559</v>
       </c>
       <c r="B6331" s="5" t="s">
-        <v>11566</v>
+        <v>11562</v>
       </c>
     </row>
     <row r="6332" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6332" s="5" t="s">
-        <v>11567</v>
+        <v>11563</v>
       </c>
       <c r="B6332" s="5" t="s">
-        <v>11568</v>
+        <v>11564</v>
       </c>
     </row>
     <row r="6333" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6333" s="5" t="s">
-        <v>11569</v>
+        <v>11565</v>
       </c>
       <c r="B6333" s="5" t="s">
-        <v>11574</v>
+        <v>11570</v>
       </c>
     </row>
     <row r="6334" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6334" s="5" t="s">
-        <v>11570</v>
+        <v>11566</v>
       </c>
       <c r="B6334" s="5" t="s">
-        <v>11575</v>
+        <v>11571</v>
       </c>
     </row>
     <row r="6335" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6335" s="5" t="s">
-        <v>11571</v>
+        <v>11567</v>
       </c>
       <c r="B6335" s="5" t="s">
-        <v>11576</v>
+        <v>11572</v>
       </c>
     </row>
     <row r="6336" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6336" s="5" t="s">
-        <v>11572</v>
+        <v>11568</v>
       </c>
       <c r="B6336" s="5" t="s">
-        <v>11577</v>
+        <v>11573</v>
       </c>
     </row>
     <row r="6337" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6337" s="5" t="s">
-        <v>11573</v>
+        <v>11569</v>
       </c>
       <c r="B6337" s="5" t="s">
-        <v>11578</v>
+        <v>11574</v>
       </c>
     </row>
     <row r="6338" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6338" s="5" t="s">
-        <v>11579</v>
+        <v>11575</v>
       </c>
       <c r="B6338" s="5" t="s">
-        <v>11580</v>
+        <v>11576</v>
       </c>
     </row>
     <row r="6339" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6339" s="5" t="s">
-        <v>11581</v>
+        <v>11577</v>
       </c>
       <c r="B6339" s="5" t="s">
-        <v>11597</v>
+        <v>11593</v>
       </c>
     </row>
     <row r="6340" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6340" s="5" t="s">
-        <v>11582</v>
+        <v>11578</v>
       </c>
       <c r="B6340" s="5" t="s">
-        <v>11598</v>
+        <v>11594</v>
       </c>
     </row>
     <row r="6341" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6341" s="5" t="s">
-        <v>11583</v>
+        <v>11579</v>
       </c>
       <c r="B6341" s="5" t="s">
-        <v>11601</v>
+        <v>11597</v>
       </c>
     </row>
     <row r="6342" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6342" s="5" t="s">
-        <v>11584</v>
+        <v>11580</v>
       </c>
       <c r="B6342" s="5" t="s">
-        <v>11602</v>
+        <v>11598</v>
       </c>
     </row>
     <row r="6343" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6343" s="5" t="s">
-        <v>11581</v>
+        <v>11577</v>
       </c>
       <c r="B6343" s="5" t="s">
-        <v>11597</v>
+        <v>11593</v>
       </c>
     </row>
     <row r="6344" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6344" s="5" t="s">
-        <v>11585</v>
+        <v>11581</v>
       </c>
       <c r="B6344" s="5" t="s">
-        <v>11603</v>
+        <v>11599</v>
       </c>
     </row>
     <row r="6345" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6345" s="5" t="s">
-        <v>11586</v>
+        <v>11582</v>
       </c>
       <c r="B6345" s="5" t="s">
-        <v>11604</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="6346" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6346" s="5" t="s">
-        <v>11587</v>
+        <v>11583</v>
       </c>
       <c r="B6346" s="5" t="s">
-        <v>11605</v>
+        <v>11601</v>
       </c>
     </row>
     <row r="6347" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6347" s="5" t="s">
-        <v>11588</v>
+        <v>11584</v>
       </c>
       <c r="B6347" s="5" t="s">
-        <v>11606</v>
+        <v>11602</v>
       </c>
     </row>
     <row r="6348" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6348" s="5" t="s">
-        <v>11589</v>
+        <v>11585</v>
       </c>
       <c r="B6348" s="5" t="s">
-        <v>11607</v>
+        <v>11603</v>
       </c>
     </row>
     <row r="6349" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6349" s="5" t="s">
-        <v>11590</v>
+        <v>11586</v>
       </c>
       <c r="B6349" s="5" t="s">
-        <v>11599</v>
+        <v>11595</v>
       </c>
     </row>
     <row r="6350" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6350" s="5" t="s">
-        <v>11591</v>
+        <v>11587</v>
       </c>
       <c r="B6350" s="5" t="s">
-        <v>11600</v>
+        <v>11596</v>
       </c>
     </row>
     <row r="6351" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6351" s="5" t="s">
-        <v>11592</v>
+        <v>11588</v>
       </c>
       <c r="B6351" s="5" t="s">
-        <v>11608</v>
+        <v>11604</v>
       </c>
     </row>
     <row r="6352" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6352" s="5" t="s">
-        <v>11593</v>
+        <v>11589</v>
       </c>
       <c r="B6352" s="5" t="s">
-        <v>11609</v>
+        <v>11605</v>
       </c>
     </row>
     <row r="6353" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6353" s="5" t="s">
-        <v>11594</v>
+        <v>11590</v>
       </c>
       <c r="B6353" s="5" t="s">
-        <v>11610</v>
+        <v>11606</v>
       </c>
     </row>
     <row r="6354" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6354" s="5" t="s">
-        <v>11595</v>
+        <v>11591</v>
       </c>
       <c r="B6354" s="5" t="s">
-        <v>11611</v>
+        <v>11607</v>
       </c>
     </row>
     <row r="6355" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6355" s="5" t="s">
-        <v>11596</v>
+        <v>11592</v>
       </c>
       <c r="B6355" s="5" t="s">
-        <v>11612</v>
+        <v>11608</v>
       </c>
     </row>
     <row r="6356" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6356" s="5" t="s">
-        <v>11613</v>
+        <v>11609</v>
       </c>
       <c r="B6356" s="5" t="s">
-        <v>11614</v>
+        <v>11610</v>
       </c>
     </row>
     <row r="6357" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6357" s="5" t="s">
+        <v>11611</v>
+      </c>
+      <c r="B6357" s="5" t="s">
         <v>11615</v>
-      </c>
-      <c r="B6357" s="5" t="s">
-        <v>11619</v>
       </c>
     </row>
     <row r="6358" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6358" s="5" t="s">
+        <v>11612</v>
+      </c>
+      <c r="B6358" s="5" t="s">
         <v>11616</v>
-      </c>
-      <c r="B6358" s="5" t="s">
-        <v>11620</v>
       </c>
     </row>
     <row r="6359" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6359" s="5" t="s">
+        <v>11613</v>
+      </c>
+      <c r="B6359" s="5" t="s">
         <v>11617</v>
-      </c>
-      <c r="B6359" s="5" t="s">
-        <v>11621</v>
       </c>
     </row>
     <row r="6360" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6360" s="5" t="s">
+        <v>11614</v>
+      </c>
+      <c r="B6360" s="5" t="s">
         <v>11618</v>
-      </c>
-      <c r="B6360" s="5" t="s">
-        <v>11622</v>
       </c>
     </row>
     <row r="6361" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6361" s="5" t="s">
-        <v>11623</v>
+        <v>11619</v>
       </c>
     </row>
     <row r="6362" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6362" s="5" t="s">
-        <v>11624</v>
+        <v>11620</v>
       </c>
       <c r="B6362" s="5" t="s">
-        <v>11625</v>
+        <v>11621</v>
       </c>
     </row>
     <row r="6363" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6363" s="5" t="s">
-        <v>11626</v>
+        <v>11622</v>
       </c>
       <c r="B6363" s="5" t="s">
-        <v>11631</v>
+        <v>11627</v>
       </c>
     </row>
     <row r="6364" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6364" s="5" t="s">
-        <v>11627</v>
+        <v>11623</v>
       </c>
       <c r="B6364" s="5" t="s">
-        <v>11632</v>
+        <v>11628</v>
       </c>
     </row>
     <row r="6365" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6365" s="5" t="s">
-        <v>11628</v>
+        <v>11624</v>
       </c>
       <c r="B6365" s="5" t="s">
-        <v>11633</v>
+        <v>11629</v>
       </c>
     </row>
     <row r="6366" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6366" s="5" t="s">
-        <v>11629</v>
+        <v>11625</v>
       </c>
       <c r="B6366" s="5" t="s">
         <v>2382</v>
@@ -85430,7 +87410,7 @@
     </row>
     <row r="6367" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6367" s="5" t="s">
-        <v>11630</v>
+        <v>11626</v>
       </c>
       <c r="B6367" s="5" t="s">
         <v>2388</v>
@@ -85438,54 +87418,2852 @@
     </row>
     <row r="6368" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6368" s="5" t="s">
-        <v>11634</v>
+        <v>11630</v>
       </c>
       <c r="B6368" s="5" t="s">
-        <v>11635</v>
+        <v>11631</v>
       </c>
     </row>
     <row r="6369" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6369" s="5" t="s">
-        <v>11636</v>
+        <v>11632</v>
       </c>
       <c r="B6369" s="5" t="s">
-        <v>11635</v>
+        <v>11631</v>
       </c>
     </row>
     <row r="6370" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6370" s="5" t="s">
-        <v>11637</v>
+        <v>11633</v>
       </c>
       <c r="B6370" s="5" t="s">
-        <v>11639</v>
+        <v>11635</v>
       </c>
     </row>
     <row r="6371" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6371" s="5" t="s">
-        <v>11638</v>
+        <v>11634</v>
       </c>
       <c r="B6371" s="5" t="s">
-        <v>11640</v>
+        <v>11636</v>
       </c>
     </row>
     <row r="6372" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6372" s="5" t="s">
-        <v>11641</v>
+        <v>11637</v>
       </c>
     </row>
     <row r="6373" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6373" s="5" t="s">
-        <v>11642</v>
+        <v>11638</v>
       </c>
     </row>
     <row r="6374" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6374" s="5" t="s">
-        <v>11643</v>
+        <v>11639</v>
       </c>
     </row>
     <row r="6375" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6375" s="5" t="s">
-        <v>11644</v>
+        <v>11640</v>
+      </c>
+    </row>
+    <row r="6376" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6376" s="5" t="s">
+        <v>11647</v>
+      </c>
+      <c r="B6376" s="5" t="s">
+        <v>11648</v>
+      </c>
+    </row>
+    <row r="6377" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6377" s="5" t="s">
+        <v>11649</v>
+      </c>
+      <c r="B6377" s="5" t="s">
+        <v>11661</v>
+      </c>
+    </row>
+    <row r="6378" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6378" s="5" t="s">
+        <v>11650</v>
+      </c>
+      <c r="B6378" s="5" t="s">
+        <v>11662</v>
+      </c>
+    </row>
+    <row r="6379" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6379" s="5" t="s">
+        <v>11651</v>
+      </c>
+      <c r="B6379" s="5" t="s">
+        <v>11663</v>
+      </c>
+    </row>
+    <row r="6380" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6380" s="5" t="s">
+        <v>11652</v>
+      </c>
+      <c r="B6380" s="5" t="s">
+        <v>11664</v>
+      </c>
+    </row>
+    <row r="6381" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6381" s="5" t="s">
+        <v>11653</v>
+      </c>
+      <c r="B6381" s="5" t="s">
+        <v>11665</v>
+      </c>
+    </row>
+    <row r="6382" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6382" s="5" t="s">
+        <v>11654</v>
+      </c>
+      <c r="B6382" s="5" t="s">
+        <v>11666</v>
+      </c>
+    </row>
+    <row r="6383" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6383" s="5" t="s">
+        <v>11655</v>
+      </c>
+      <c r="B6383" s="5" t="s">
+        <v>11667</v>
+      </c>
+    </row>
+    <row r="6384" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6384" s="5" t="s">
+        <v>11656</v>
+      </c>
+      <c r="B6384" s="5" t="s">
+        <v>11668</v>
+      </c>
+    </row>
+    <row r="6385" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6385" s="5" t="s">
+        <v>11657</v>
+      </c>
+      <c r="B6385" s="5" t="s">
+        <v>11669</v>
+      </c>
+    </row>
+    <row r="6386" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6386" s="5" t="s">
+        <v>11658</v>
+      </c>
+      <c r="B6386" s="5" t="s">
+        <v>11670</v>
+      </c>
+    </row>
+    <row r="6387" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6387" s="5" t="s">
+        <v>11659</v>
+      </c>
+      <c r="B6387" s="5" t="s">
+        <v>11671</v>
+      </c>
+    </row>
+    <row r="6388" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6388" s="5" t="s">
+        <v>11660</v>
+      </c>
+      <c r="B6388" s="5" t="s">
+        <v>11672</v>
+      </c>
+    </row>
+    <row r="6389" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6389" s="5" t="s">
+        <v>11673</v>
+      </c>
+      <c r="B6389" s="5" t="s">
+        <v>11674</v>
+      </c>
+    </row>
+    <row r="6390" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6390" s="5" t="s">
+        <v>11675</v>
+      </c>
+      <c r="B6390" s="5" t="s">
+        <v>11685</v>
+      </c>
+    </row>
+    <row r="6391" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6391" s="5" t="s">
+        <v>11676</v>
+      </c>
+      <c r="B6391" s="5" t="s">
+        <v>11686</v>
+      </c>
+    </row>
+    <row r="6392" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6392" s="5" t="s">
+        <v>11677</v>
+      </c>
+      <c r="B6392" s="5" t="s">
+        <v>11687</v>
+      </c>
+    </row>
+    <row r="6393" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6393" s="5" t="s">
+        <v>11678</v>
+      </c>
+      <c r="B6393" s="5" t="s">
+        <v>11688</v>
+      </c>
+    </row>
+    <row r="6394" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6394" s="5" t="s">
+        <v>11679</v>
+      </c>
+      <c r="B6394" s="5" t="s">
+        <v>11689</v>
+      </c>
+    </row>
+    <row r="6395" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6395" s="5" t="s">
+        <v>11680</v>
+      </c>
+      <c r="B6395" s="5" t="s">
+        <v>11690</v>
+      </c>
+    </row>
+    <row r="6396" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6396" s="5" t="s">
+        <v>11681</v>
+      </c>
+      <c r="B6396" s="5" t="s">
+        <v>11691</v>
+      </c>
+    </row>
+    <row r="6397" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6397" s="5" t="s">
+        <v>11682</v>
+      </c>
+      <c r="B6397" s="5" t="s">
+        <v>11692</v>
+      </c>
+    </row>
+    <row r="6398" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6398" s="5" t="s">
+        <v>11683</v>
+      </c>
+      <c r="B6398" s="5" t="s">
+        <v>11693</v>
+      </c>
+    </row>
+    <row r="6399" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6399" s="5" t="s">
+        <v>11684</v>
+      </c>
+      <c r="B6399" s="5" t="s">
+        <v>11694</v>
+      </c>
+    </row>
+    <row r="6400" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6400" s="5" t="s">
+        <v>11695</v>
+      </c>
+      <c r="B6400" s="5" t="s">
+        <v>11696</v>
+      </c>
+    </row>
+    <row r="6401" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6401" s="5" t="s">
+        <v>11697</v>
+      </c>
+      <c r="B6401" s="5" t="s">
+        <v>11707</v>
+      </c>
+    </row>
+    <row r="6402" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6402" s="5" t="s">
+        <v>11698</v>
+      </c>
+      <c r="B6402" s="5" t="s">
+        <v>11708</v>
+      </c>
+    </row>
+    <row r="6403" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6403" s="5" t="s">
+        <v>11699</v>
+      </c>
+      <c r="B6403" s="5" t="s">
+        <v>11709</v>
+      </c>
+    </row>
+    <row r="6404" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6404" s="5" t="s">
+        <v>11700</v>
+      </c>
+      <c r="B6404" s="5" t="s">
+        <v>11710</v>
+      </c>
+    </row>
+    <row r="6405" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6405" s="5" t="s">
+        <v>11701</v>
+      </c>
+      <c r="B6405" s="5" t="s">
+        <v>11711</v>
+      </c>
+    </row>
+    <row r="6406" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6406" s="5" t="s">
+        <v>11702</v>
+      </c>
+      <c r="B6406" s="5" t="s">
+        <v>11708</v>
+      </c>
+    </row>
+    <row r="6407" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6407" s="5" t="s">
+        <v>11703</v>
+      </c>
+      <c r="B6407" s="5" t="s">
+        <v>11712</v>
+      </c>
+    </row>
+    <row r="6408" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6408" s="5" t="s">
+        <v>11704</v>
+      </c>
+      <c r="B6408" s="5" t="s">
+        <v>11713</v>
+      </c>
+    </row>
+    <row r="6409" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6409" s="5" t="s">
+        <v>11705</v>
+      </c>
+      <c r="B6409" s="5" t="s">
+        <v>11714</v>
+      </c>
+    </row>
+    <row r="6410" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6410" s="5" t="s">
+        <v>11706</v>
+      </c>
+      <c r="B6410" s="5" t="s">
+        <v>11715</v>
+      </c>
+    </row>
+    <row r="6411" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6411" s="5" t="s">
+        <v>11716</v>
+      </c>
+      <c r="B6411" s="5" t="s">
+        <v>11717</v>
+      </c>
+    </row>
+    <row r="6412" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6412" s="5" t="s">
+        <v>11718</v>
+      </c>
+      <c r="B6412" s="5" t="s">
+        <v>11722</v>
+      </c>
+    </row>
+    <row r="6413" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6413" s="5" t="s">
+        <v>11719</v>
+      </c>
+      <c r="B6413" s="5" t="s">
+        <v>11723</v>
+      </c>
+    </row>
+    <row r="6414" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6414" s="5" t="s">
+        <v>11720</v>
+      </c>
+      <c r="B6414" s="5" t="s">
+        <v>11724</v>
+      </c>
+    </row>
+    <row r="6415" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6415" s="5" t="s">
+        <v>11721</v>
+      </c>
+      <c r="B6415" s="5" t="s">
+        <v>11725</v>
+      </c>
+    </row>
+    <row r="6416" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6416" s="5" t="s">
+        <v>11726</v>
+      </c>
+      <c r="B6416" s="5" t="s">
+        <v>11727</v>
+      </c>
+    </row>
+    <row r="6417" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6417" s="5" t="s">
+        <v>11728</v>
+      </c>
+      <c r="B6417" s="5" t="s">
+        <v>11738</v>
+      </c>
+    </row>
+    <row r="6418" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6418" s="5" t="s">
+        <v>11729</v>
+      </c>
+      <c r="B6418" s="5" t="s">
+        <v>11739</v>
+      </c>
+    </row>
+    <row r="6419" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6419" s="5" t="s">
+        <v>11730</v>
+      </c>
+      <c r="B6419" s="5" t="s">
+        <v>11740</v>
+      </c>
+    </row>
+    <row r="6420" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6420" s="5" t="s">
+        <v>11731</v>
+      </c>
+      <c r="B6420" s="5" t="s">
+        <v>11741</v>
+      </c>
+    </row>
+    <row r="6421" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6421" s="5" t="s">
+        <v>11732</v>
+      </c>
+      <c r="B6421" s="5" t="s">
+        <v>11742</v>
+      </c>
+    </row>
+    <row r="6422" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6422" s="5" t="s">
+        <v>11733</v>
+      </c>
+      <c r="B6422" s="5" t="s">
+        <v>11743</v>
+      </c>
+    </row>
+    <row r="6423" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6423" s="5" t="s">
+        <v>11734</v>
+      </c>
+      <c r="B6423" s="5" t="s">
+        <v>11744</v>
+      </c>
+    </row>
+    <row r="6424" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6424" s="5" t="s">
+        <v>11735</v>
+      </c>
+      <c r="B6424" s="5" t="s">
+        <v>11745</v>
+      </c>
+    </row>
+    <row r="6425" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6425" s="5" t="s">
+        <v>11736</v>
+      </c>
+      <c r="B6425" s="5" t="s">
+        <v>11746</v>
+      </c>
+    </row>
+    <row r="6426" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6426" s="5" t="s">
+        <v>11737</v>
+      </c>
+      <c r="B6426" s="5" t="s">
+        <v>11747</v>
+      </c>
+    </row>
+    <row r="6427" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6427" s="5" t="s">
+        <v>11748</v>
+      </c>
+      <c r="B6427" s="5" t="s">
+        <v>11749</v>
+      </c>
+    </row>
+    <row r="6428" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6428" s="5" t="s">
+        <v>11750</v>
+      </c>
+      <c r="B6428" s="5" t="s">
+        <v>11754</v>
+      </c>
+    </row>
+    <row r="6429" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6429" s="5" t="s">
+        <v>11751</v>
+      </c>
+      <c r="B6429" s="5" t="s">
+        <v>11755</v>
+      </c>
+    </row>
+    <row r="6430" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6430" s="5" t="s">
+        <v>11752</v>
+      </c>
+      <c r="B6430" s="5" t="s">
+        <v>11756</v>
+      </c>
+    </row>
+    <row r="6431" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6431" s="5" t="s">
+        <v>11753</v>
+      </c>
+      <c r="B6431" s="5" t="s">
+        <v>11757</v>
+      </c>
+    </row>
+    <row r="6432" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6432" s="5" t="s">
+        <v>11758</v>
+      </c>
+      <c r="B6432" s="5" t="s">
+        <v>11759</v>
+      </c>
+    </row>
+    <row r="6433" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6433" s="5" t="s">
+        <v>11760</v>
+      </c>
+      <c r="B6433" s="5" t="s">
+        <v>11763</v>
+      </c>
+    </row>
+    <row r="6434" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6434" s="5" t="s">
+        <v>11761</v>
+      </c>
+      <c r="B6434" s="5" t="s">
+        <v>11764</v>
+      </c>
+    </row>
+    <row r="6435" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6435" s="5" t="s">
+        <v>11762</v>
+      </c>
+      <c r="B6435" s="5" t="s">
+        <v>11765</v>
+      </c>
+    </row>
+    <row r="6436" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6436" s="5" t="s">
+        <v>11766</v>
+      </c>
+      <c r="B6436" s="5" t="s">
+        <v>11767</v>
+      </c>
+    </row>
+    <row r="6437" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6437" s="5" t="s">
+        <v>11768</v>
+      </c>
+      <c r="B6437" s="5" t="s">
+        <v>11776</v>
+      </c>
+    </row>
+    <row r="6438" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6438" s="5" t="s">
+        <v>11769</v>
+      </c>
+      <c r="B6438" s="5" t="s">
+        <v>11777</v>
+      </c>
+    </row>
+    <row r="6439" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6439" s="5" t="s">
+        <v>11770</v>
+      </c>
+      <c r="B6439" s="5" t="s">
+        <v>11778</v>
+      </c>
+    </row>
+    <row r="6440" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6440" s="5" t="s">
+        <v>11771</v>
+      </c>
+      <c r="B6440" s="5" t="s">
+        <v>11779</v>
+      </c>
+    </row>
+    <row r="6441" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6441" s="5" t="s">
+        <v>11772</v>
+      </c>
+      <c r="B6441" s="5" t="s">
+        <v>11780</v>
+      </c>
+    </row>
+    <row r="6442" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6442" s="5" t="s">
+        <v>11773</v>
+      </c>
+      <c r="B6442" s="5" t="s">
+        <v>11781</v>
+      </c>
+    </row>
+    <row r="6443" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6443" s="5" t="s">
+        <v>11774</v>
+      </c>
+      <c r="B6443" s="5" t="s">
+        <v>11782</v>
+      </c>
+    </row>
+    <row r="6444" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6444" s="5" t="s">
+        <v>11775</v>
+      </c>
+      <c r="B6444" s="5" t="s">
+        <v>11783</v>
+      </c>
+    </row>
+    <row r="6445" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6445" s="5" t="s">
+        <v>11784</v>
+      </c>
+      <c r="B6445" s="5" t="s">
+        <v>11785</v>
+      </c>
+    </row>
+    <row r="6446" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6446" s="5" t="s">
+        <v>11786</v>
+      </c>
+      <c r="B6446" s="5" t="s">
+        <v>11790</v>
+      </c>
+    </row>
+    <row r="6447" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6447" s="5" t="s">
+        <v>11787</v>
+      </c>
+      <c r="B6447" s="5" t="s">
+        <v>11791</v>
+      </c>
+    </row>
+    <row r="6448" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6448" s="5" t="s">
+        <v>11788</v>
+      </c>
+      <c r="B6448" s="5" t="s">
+        <v>11792</v>
+      </c>
+    </row>
+    <row r="6449" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6449" s="5" t="s">
+        <v>11789</v>
+      </c>
+      <c r="B6449" s="5" t="s">
+        <v>11793</v>
+      </c>
+    </row>
+    <row r="6450" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6450" s="5" t="s">
+        <v>11794</v>
+      </c>
+      <c r="B6450" s="5" t="s">
+        <v>11795</v>
+      </c>
+    </row>
+    <row r="6451" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6451" s="5" t="s">
+        <v>11796</v>
+      </c>
+      <c r="B6451" s="5" t="s">
+        <v>11805</v>
+      </c>
+    </row>
+    <row r="6452" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6452" s="5" t="s">
+        <v>11797</v>
+      </c>
+      <c r="B6452" s="5" t="s">
+        <v>11805</v>
+      </c>
+    </row>
+    <row r="6453" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6453" s="5" t="s">
+        <v>11798</v>
+      </c>
+      <c r="B6453" s="5" t="s">
+        <v>11805</v>
+      </c>
+    </row>
+    <row r="6454" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6454" s="5" t="s">
+        <v>11799</v>
+      </c>
+      <c r="B6454" s="5" t="s">
+        <v>11806</v>
+      </c>
+    </row>
+    <row r="6455" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6455" s="5" t="s">
+        <v>11800</v>
+      </c>
+      <c r="B6455" s="5" t="s">
+        <v>11805</v>
+      </c>
+    </row>
+    <row r="6456" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6456" s="5" t="s">
+        <v>11801</v>
+      </c>
+      <c r="B6456" s="5" t="s">
+        <v>11807</v>
+      </c>
+    </row>
+    <row r="6457" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6457" s="5" t="s">
+        <v>11802</v>
+      </c>
+      <c r="B6457" s="5" t="s">
+        <v>11808</v>
+      </c>
+    </row>
+    <row r="6458" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6458" s="5" t="s">
+        <v>11803</v>
+      </c>
+      <c r="B6458" s="5" t="s">
+        <v>11809</v>
+      </c>
+    </row>
+    <row r="6459" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6459" s="5" t="s">
+        <v>11804</v>
+      </c>
+      <c r="B6459" s="5" t="s">
+        <v>11810</v>
+      </c>
+    </row>
+    <row r="6460" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6460" s="5" t="s">
+        <v>11811</v>
+      </c>
+      <c r="B6460" s="5" t="s">
+        <v>11812</v>
+      </c>
+    </row>
+    <row r="6461" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6461" s="5" t="s">
+        <v>11813</v>
+      </c>
+      <c r="B6461" s="5" t="s">
+        <v>11823</v>
+      </c>
+    </row>
+    <row r="6462" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6462" s="5" t="s">
+        <v>11814</v>
+      </c>
+      <c r="B6462" s="5" t="s">
+        <v>11824</v>
+      </c>
+    </row>
+    <row r="6463" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6463" s="5" t="s">
+        <v>11815</v>
+      </c>
+      <c r="B6463" s="5" t="s">
+        <v>11825</v>
+      </c>
+    </row>
+    <row r="6464" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6464" s="5" t="s">
+        <v>11816</v>
+      </c>
+      <c r="B6464" s="5" t="s">
+        <v>11826</v>
+      </c>
+    </row>
+    <row r="6465" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6465" s="5" t="s">
+        <v>11817</v>
+      </c>
+      <c r="B6465" s="5" t="s">
+        <v>11827</v>
+      </c>
+    </row>
+    <row r="6466" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6466" s="5" t="s">
+        <v>11818</v>
+      </c>
+      <c r="B6466" s="5" t="s">
+        <v>11828</v>
+      </c>
+    </row>
+    <row r="6467" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6467" s="5" t="s">
+        <v>11819</v>
+      </c>
+      <c r="B6467" s="5" t="s">
+        <v>11829</v>
+      </c>
+    </row>
+    <row r="6468" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6468" s="5" t="s">
+        <v>11820</v>
+      </c>
+      <c r="B6468" s="5" t="s">
+        <v>11830</v>
+      </c>
+    </row>
+    <row r="6469" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6469" s="5" t="s">
+        <v>11814</v>
+      </c>
+      <c r="B6469" s="5" t="s">
+        <v>11824</v>
+      </c>
+    </row>
+    <row r="6470" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6470" s="5" t="s">
+        <v>11821</v>
+      </c>
+      <c r="B6470" s="5" t="s">
+        <v>11831</v>
+      </c>
+    </row>
+    <row r="6471" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6471" s="5" t="s">
+        <v>11822</v>
+      </c>
+      <c r="B6471" s="5" t="s">
+        <v>11832</v>
+      </c>
+    </row>
+    <row r="6472" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6472" s="5" t="s">
+        <v>11833</v>
+      </c>
+    </row>
+    <row r="6473" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6473" s="5" t="s">
+        <v>11834</v>
+      </c>
+      <c r="B6473" s="5" t="s">
+        <v>11835</v>
+      </c>
+    </row>
+    <row r="6474" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6474" s="5" t="s">
+        <v>11836</v>
+      </c>
+      <c r="B6474" s="5" t="s">
+        <v>11848</v>
+      </c>
+    </row>
+    <row r="6475" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6475" s="5" t="s">
+        <v>11837</v>
+      </c>
+      <c r="B6475" s="5" t="s">
+        <v>11849</v>
+      </c>
+    </row>
+    <row r="6476" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6476" s="5" t="s">
+        <v>11838</v>
+      </c>
+      <c r="B6476" s="5" t="s">
+        <v>11850</v>
+      </c>
+    </row>
+    <row r="6477" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6477" s="5" t="s">
+        <v>11839</v>
+      </c>
+      <c r="B6477" s="5" t="s">
+        <v>11851</v>
+      </c>
+    </row>
+    <row r="6478" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6478" s="5" t="s">
+        <v>11840</v>
+      </c>
+      <c r="B6478" s="5" t="s">
+        <v>11852</v>
+      </c>
+    </row>
+    <row r="6479" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6479" s="5" t="s">
+        <v>11841</v>
+      </c>
+      <c r="B6479" s="5" t="s">
+        <v>11853</v>
+      </c>
+    </row>
+    <row r="6480" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6480" s="5" t="s">
+        <v>11842</v>
+      </c>
+      <c r="B6480" s="5" t="s">
+        <v>11854</v>
+      </c>
+    </row>
+    <row r="6481" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6481" s="5" t="s">
+        <v>11843</v>
+      </c>
+      <c r="B6481" s="5" t="s">
+        <v>11855</v>
+      </c>
+    </row>
+    <row r="6482" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6482" s="5" t="s">
+        <v>11844</v>
+      </c>
+      <c r="B6482" s="5" t="s">
+        <v>11856</v>
+      </c>
+    </row>
+    <row r="6483" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6483" s="5" t="s">
+        <v>11845</v>
+      </c>
+      <c r="B6483" s="5" t="s">
+        <v>11857</v>
+      </c>
+    </row>
+    <row r="6484" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6484" s="5" t="s">
+        <v>11846</v>
+      </c>
+      <c r="B6484" s="5" t="s">
+        <v>11858</v>
+      </c>
+    </row>
+    <row r="6485" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6485" s="5" t="s">
+        <v>11847</v>
+      </c>
+      <c r="B6485" s="5" t="s">
+        <v>11859</v>
+      </c>
+    </row>
+    <row r="6486" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6486" s="5" t="s">
+        <v>11860</v>
+      </c>
+      <c r="B6486" s="5" t="s">
+        <v>11861</v>
+      </c>
+    </row>
+    <row r="6487" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6487" s="5" t="s">
+        <v>11862</v>
+      </c>
+      <c r="B6487" s="5" t="s">
+        <v>11866</v>
+      </c>
+    </row>
+    <row r="6488" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6488" s="5" t="s">
+        <v>11863</v>
+      </c>
+      <c r="B6488" s="5" t="s">
+        <v>11867</v>
+      </c>
+    </row>
+    <row r="6489" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6489" s="5" t="s">
+        <v>11864</v>
+      </c>
+      <c r="B6489" s="5" t="s">
+        <v>11868</v>
+      </c>
+    </row>
+    <row r="6490" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6490" s="5" t="s">
+        <v>11865</v>
+      </c>
+      <c r="B6490" s="5" t="s">
+        <v>11869</v>
+      </c>
+    </row>
+    <row r="6491" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6491" s="5" t="s">
+        <v>11870</v>
+      </c>
+      <c r="B6491" s="5" t="s">
+        <v>11887</v>
+      </c>
+    </row>
+    <row r="6492" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6492" s="5" t="s">
+        <v>11871</v>
+      </c>
+      <c r="B6492" s="5" t="s">
+        <v>11886</v>
+      </c>
+    </row>
+    <row r="6493" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6493" s="5" t="s">
+        <v>11872</v>
+      </c>
+      <c r="B6493" s="5" t="s">
+        <v>11888</v>
+      </c>
+    </row>
+    <row r="6494" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6494" s="5" t="s">
+        <v>11873</v>
+      </c>
+      <c r="B6494" s="5" t="s">
+        <v>11889</v>
+      </c>
+    </row>
+    <row r="6495" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6495" s="5" t="s">
+        <v>11874</v>
+      </c>
+      <c r="B6495" s="5" t="s">
+        <v>11890</v>
+      </c>
+    </row>
+    <row r="6496" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6496" s="5" t="s">
+        <v>11875</v>
+      </c>
+      <c r="B6496" s="5" t="s">
+        <v>11887</v>
+      </c>
+    </row>
+    <row r="6497" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6497" s="5" t="s">
+        <v>11876</v>
+      </c>
+      <c r="B6497" s="5" t="s">
+        <v>11891</v>
+      </c>
+    </row>
+    <row r="6498" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6498" s="5" t="s">
+        <v>11877</v>
+      </c>
+      <c r="B6498" s="5" t="s">
+        <v>11892</v>
+      </c>
+    </row>
+    <row r="6499" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6499" s="5" t="s">
+        <v>11878</v>
+      </c>
+      <c r="B6499" s="5" t="s">
+        <v>11893</v>
+      </c>
+    </row>
+    <row r="6500" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6500" s="5" t="s">
+        <v>11879</v>
+      </c>
+      <c r="B6500" s="5" t="s">
+        <v>11894</v>
+      </c>
+    </row>
+    <row r="6501" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6501" s="5" t="s">
+        <v>11880</v>
+      </c>
+      <c r="B6501" s="5" t="s">
+        <v>11895</v>
+      </c>
+    </row>
+    <row r="6502" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6502" s="5" t="s">
+        <v>11881</v>
+      </c>
+      <c r="B6502" s="5" t="s">
+        <v>11896</v>
+      </c>
+    </row>
+    <row r="6503" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6503" s="5" t="s">
+        <v>11882</v>
+      </c>
+      <c r="B6503" s="5" t="s">
+        <v>11897</v>
+      </c>
+    </row>
+    <row r="6504" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6504" s="5" t="s">
+        <v>11883</v>
+      </c>
+      <c r="B6504" s="5" t="s">
+        <v>11898</v>
+      </c>
+    </row>
+    <row r="6505" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6505" s="5" t="s">
+        <v>11884</v>
+      </c>
+      <c r="B6505" s="5" t="s">
+        <v>11899</v>
+      </c>
+    </row>
+    <row r="6506" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6506" s="5" t="s">
+        <v>11885</v>
+      </c>
+      <c r="B6506" s="5" t="s">
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="6507" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6507" s="5" t="s">
+        <v>11876</v>
+      </c>
+      <c r="B6507" s="5" t="s">
+        <v>11891</v>
+      </c>
+    </row>
+    <row r="6508" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6508" s="5" t="s">
+        <v>11901</v>
+      </c>
+      <c r="B6508" s="5" t="s">
+        <v>11902</v>
+      </c>
+    </row>
+    <row r="6509" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6509" s="5" t="s">
+        <v>11903</v>
+      </c>
+      <c r="B6509" s="5" t="s">
+        <v>11915</v>
+      </c>
+    </row>
+    <row r="6510" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6510" s="5" t="s">
+        <v>11904</v>
+      </c>
+      <c r="B6510" s="5" t="s">
+        <v>11916</v>
+      </c>
+    </row>
+    <row r="6511" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6511" s="5" t="s">
+        <v>11905</v>
+      </c>
+      <c r="B6511" s="5" t="s">
+        <v>11917</v>
+      </c>
+    </row>
+    <row r="6512" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6512" s="5" t="s">
+        <v>11906</v>
+      </c>
+      <c r="B6512" s="5" t="s">
+        <v>11918</v>
+      </c>
+    </row>
+    <row r="6513" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6513" s="5" t="s">
+        <v>11907</v>
+      </c>
+      <c r="B6513" s="5" t="s">
+        <v>11919</v>
+      </c>
+    </row>
+    <row r="6514" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6514" s="5" t="s">
+        <v>11908</v>
+      </c>
+      <c r="B6514" s="5" t="s">
+        <v>11920</v>
+      </c>
+    </row>
+    <row r="6515" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6515" s="5" t="s">
+        <v>11909</v>
+      </c>
+      <c r="B6515" s="5" t="s">
+        <v>11921</v>
+      </c>
+    </row>
+    <row r="6516" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6516" s="5" t="s">
+        <v>11910</v>
+      </c>
+      <c r="B6516" s="5" t="s">
+        <v>11922</v>
+      </c>
+    </row>
+    <row r="6517" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6517" s="5" t="s">
+        <v>11911</v>
+      </c>
+      <c r="B6517" s="5" t="s">
+        <v>11923</v>
+      </c>
+    </row>
+    <row r="6518" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6518" s="5" t="s">
+        <v>11912</v>
+      </c>
+      <c r="B6518" s="5" t="s">
+        <v>11924</v>
+      </c>
+    </row>
+    <row r="6519" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6519" s="5" t="s">
+        <v>11913</v>
+      </c>
+      <c r="B6519" s="5" t="s">
+        <v>11925</v>
+      </c>
+    </row>
+    <row r="6520" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6520" s="5" t="s">
+        <v>11914</v>
+      </c>
+      <c r="B6520" s="5" t="s">
+        <v>11926</v>
+      </c>
+    </row>
+    <row r="6521" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6521" s="5" t="s">
+        <v>11927</v>
+      </c>
+      <c r="B6521" s="5" t="s">
+        <v>11928</v>
+      </c>
+    </row>
+    <row r="6522" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6522" s="5" t="s">
+        <v>11929</v>
+      </c>
+      <c r="B6522" s="5" t="s">
+        <v>11941</v>
+      </c>
+    </row>
+    <row r="6523" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6523" s="5" t="s">
+        <v>11930</v>
+      </c>
+      <c r="B6523" s="5" t="s">
+        <v>11942</v>
+      </c>
+    </row>
+    <row r="6524" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6524" s="5" t="s">
+        <v>11931</v>
+      </c>
+      <c r="B6524" s="5" t="s">
+        <v>11943</v>
+      </c>
+    </row>
+    <row r="6525" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6525" s="5" t="s">
+        <v>11932</v>
+      </c>
+      <c r="B6525" s="5" t="s">
+        <v>11944</v>
+      </c>
+    </row>
+    <row r="6526" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6526" s="5" t="s">
+        <v>11933</v>
+      </c>
+      <c r="B6526" s="5" t="s">
+        <v>11945</v>
+      </c>
+    </row>
+    <row r="6527" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6527" s="5" t="s">
+        <v>11934</v>
+      </c>
+      <c r="B6527" s="5" t="s">
+        <v>11946</v>
+      </c>
+    </row>
+    <row r="6528" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6528" s="5" t="s">
+        <v>11935</v>
+      </c>
+      <c r="B6528" s="5" t="s">
+        <v>11947</v>
+      </c>
+    </row>
+    <row r="6529" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6529" s="5" t="s">
+        <v>11936</v>
+      </c>
+      <c r="B6529" s="5" t="s">
+        <v>11948</v>
+      </c>
+    </row>
+    <row r="6530" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6530" s="5" t="s">
+        <v>11937</v>
+      </c>
+      <c r="B6530" s="5" t="s">
+        <v>11949</v>
+      </c>
+    </row>
+    <row r="6531" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6531" s="5" t="s">
+        <v>11938</v>
+      </c>
+      <c r="B6531" s="5" t="s">
+        <v>11950</v>
+      </c>
+    </row>
+    <row r="6532" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6532" s="5" t="s">
+        <v>11939</v>
+      </c>
+      <c r="B6532" s="5" t="s">
+        <v>11951</v>
+      </c>
+    </row>
+    <row r="6533" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6533" s="5" t="s">
+        <v>11940</v>
+      </c>
+      <c r="B6533" s="5" t="s">
+        <v>11952</v>
+      </c>
+    </row>
+    <row r="6534" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6534" s="5" t="s">
+        <v>11953</v>
+      </c>
+      <c r="B6534" s="5" t="s">
+        <v>11954</v>
+      </c>
+    </row>
+    <row r="6535" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6535" s="5" t="s">
+        <v>11955</v>
+      </c>
+      <c r="B6535" s="5" t="s">
+        <v>11967</v>
+      </c>
+    </row>
+    <row r="6536" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6536" s="5" t="s">
+        <v>11956</v>
+      </c>
+      <c r="B6536" s="5" t="s">
+        <v>11968</v>
+      </c>
+    </row>
+    <row r="6537" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6537" s="5" t="s">
+        <v>11957</v>
+      </c>
+      <c r="B6537" s="5" t="s">
+        <v>11969</v>
+      </c>
+    </row>
+    <row r="6538" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6538" s="5" t="s">
+        <v>11958</v>
+      </c>
+      <c r="B6538" s="5" t="s">
+        <v>11970</v>
+      </c>
+    </row>
+    <row r="6539" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6539" s="5" t="s">
+        <v>11959</v>
+      </c>
+      <c r="B6539" s="5" t="s">
+        <v>11971</v>
+      </c>
+    </row>
+    <row r="6540" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6540" s="5" t="s">
+        <v>11960</v>
+      </c>
+      <c r="B6540" s="5" t="s">
+        <v>11972</v>
+      </c>
+    </row>
+    <row r="6541" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6541" s="5" t="s">
+        <v>11961</v>
+      </c>
+      <c r="B6541" s="5" t="s">
+        <v>11973</v>
+      </c>
+    </row>
+    <row r="6542" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6542" s="5" t="s">
+        <v>11962</v>
+      </c>
+      <c r="B6542" s="5" t="s">
+        <v>11974</v>
+      </c>
+    </row>
+    <row r="6543" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6543" s="5" t="s">
+        <v>11963</v>
+      </c>
+      <c r="B6543" s="5" t="s">
+        <v>11977</v>
+      </c>
+    </row>
+    <row r="6544" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6544" s="5" t="s">
+        <v>11964</v>
+      </c>
+      <c r="B6544" s="5" t="s">
+        <v>11978</v>
+      </c>
+    </row>
+    <row r="6545" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6545" s="5" t="s">
+        <v>11965</v>
+      </c>
+      <c r="B6545" s="5" t="s">
+        <v>11975</v>
+      </c>
+    </row>
+    <row r="6546" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6546" s="5" t="s">
+        <v>11966</v>
+      </c>
+      <c r="B6546" s="5" t="s">
+        <v>11976</v>
+      </c>
+    </row>
+    <row r="6547" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6547" s="5" t="s">
+        <v>11979</v>
+      </c>
+      <c r="B6547" s="5" t="s">
+        <v>11993</v>
+      </c>
+    </row>
+    <row r="6548" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6548" s="5" t="s">
+        <v>11980</v>
+      </c>
+      <c r="B6548" s="5" t="s">
+        <v>11994</v>
+      </c>
+    </row>
+    <row r="6549" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6549" s="5" t="s">
+        <v>11981</v>
+      </c>
+      <c r="B6549" s="5" t="s">
+        <v>11995</v>
+      </c>
+    </row>
+    <row r="6550" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6550" s="5" t="s">
+        <v>11982</v>
+      </c>
+      <c r="B6550" s="5" t="s">
+        <v>11996</v>
+      </c>
+    </row>
+    <row r="6551" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6551" s="5" t="s">
+        <v>11983</v>
+      </c>
+      <c r="B6551" s="5" t="s">
+        <v>11997</v>
+      </c>
+    </row>
+    <row r="6552" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6552" s="5" t="s">
+        <v>11984</v>
+      </c>
+      <c r="B6552" s="5" t="s">
+        <v>11998</v>
+      </c>
+    </row>
+    <row r="6553" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6553" s="5" t="s">
+        <v>11985</v>
+      </c>
+      <c r="B6553" s="5" t="s">
+        <v>11999</v>
+      </c>
+    </row>
+    <row r="6554" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6554" s="5" t="s">
+        <v>11986</v>
+      </c>
+      <c r="B6554" s="5" t="s">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="6555" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6555" s="5" t="s">
+        <v>11987</v>
+      </c>
+      <c r="B6555" s="5" t="s">
+        <v>12001</v>
+      </c>
+    </row>
+    <row r="6556" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6556" s="5" t="s">
+        <v>11988</v>
+      </c>
+      <c r="B6556" s="5" t="s">
+        <v>12002</v>
+      </c>
+    </row>
+    <row r="6557" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6557" s="5" t="s">
+        <v>11989</v>
+      </c>
+      <c r="B6557" s="5" t="s">
+        <v>12003</v>
+      </c>
+    </row>
+    <row r="6558" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6558" s="5" t="s">
+        <v>11990</v>
+      </c>
+      <c r="B6558" s="5" t="s">
+        <v>12004</v>
+      </c>
+    </row>
+    <row r="6559" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6559" s="5" t="s">
+        <v>11991</v>
+      </c>
+      <c r="B6559" s="5" t="s">
+        <v>12005</v>
+      </c>
+    </row>
+    <row r="6560" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6560" s="5" t="s">
+        <v>11992</v>
+      </c>
+      <c r="B6560" s="5" t="s">
+        <v>12006</v>
+      </c>
+    </row>
+    <row r="6561" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6561" s="5" t="s">
+        <v>12007</v>
+      </c>
+      <c r="B6561" s="5" t="s">
+        <v>12008</v>
+      </c>
+    </row>
+    <row r="6562" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6562" s="5" t="s">
+        <v>12009</v>
+      </c>
+      <c r="B6562" s="5" t="s">
+        <v>12012</v>
+      </c>
+    </row>
+    <row r="6563" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6563" s="5" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B6563" s="5" t="s">
+        <v>12013</v>
+      </c>
+    </row>
+    <row r="6564" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6564" s="5" t="s">
+        <v>12010</v>
+      </c>
+      <c r="B6564" s="5" t="s">
+        <v>12014</v>
+      </c>
+    </row>
+    <row r="6565" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6565" s="5" t="s">
+        <v>12011</v>
+      </c>
+      <c r="B6565" s="5" t="s">
+        <v>12015</v>
+      </c>
+    </row>
+    <row r="6566" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6566" s="5" t="s">
+        <v>12016</v>
+      </c>
+    </row>
+    <row r="6567" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6567" s="5" t="s">
+        <v>12017</v>
+      </c>
+    </row>
+    <row r="6568" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6568" s="5" t="s">
+        <v>12018</v>
+      </c>
+      <c r="B6568" s="5" t="s">
+        <v>12019</v>
+      </c>
+    </row>
+    <row r="6569" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6569" s="5" t="s">
+        <v>12020</v>
+      </c>
+      <c r="B6569" s="5" t="s">
+        <v>12027</v>
+      </c>
+    </row>
+    <row r="6570" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6570" s="5" t="s">
+        <v>12021</v>
+      </c>
+      <c r="B6570" s="5" t="s">
+        <v>12028</v>
+      </c>
+    </row>
+    <row r="6571" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6571" s="5" t="s">
+        <v>12022</v>
+      </c>
+      <c r="B6571" s="5" t="s">
+        <v>12028</v>
+      </c>
+    </row>
+    <row r="6572" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6572" s="5" t="s">
+        <v>12023</v>
+      </c>
+      <c r="B6572" s="5" t="s">
+        <v>12029</v>
+      </c>
+    </row>
+    <row r="6573" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6573" s="5" t="s">
+        <v>12024</v>
+      </c>
+      <c r="B6573" s="5" t="s">
+        <v>12030</v>
+      </c>
+    </row>
+    <row r="6574" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6574" s="5" t="s">
+        <v>12025</v>
+      </c>
+      <c r="B6574" s="5" t="s">
+        <v>12031</v>
+      </c>
+    </row>
+    <row r="6575" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6575" s="5" t="s">
+        <v>12026</v>
+      </c>
+      <c r="B6575" s="5" t="s">
+        <v>12032</v>
+      </c>
+    </row>
+    <row r="6576" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6576" s="5" t="s">
+        <v>12033</v>
+      </c>
+    </row>
+    <row r="6577" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6577" s="5" t="s">
+        <v>12034</v>
+      </c>
+      <c r="B6577" s="5" t="s">
+        <v>12035</v>
+      </c>
+    </row>
+    <row r="6578" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6578" s="5" t="s">
+        <v>12036</v>
+      </c>
+      <c r="B6578" s="5" t="s">
+        <v>12047</v>
+      </c>
+    </row>
+    <row r="6579" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6579" s="5" t="s">
+        <v>12037</v>
+      </c>
+      <c r="B6579" s="5" t="s">
+        <v>12048</v>
+      </c>
+    </row>
+    <row r="6580" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6580" s="5" t="s">
+        <v>12038</v>
+      </c>
+      <c r="B6580" s="5" t="s">
+        <v>12049</v>
+      </c>
+    </row>
+    <row r="6581" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6581" s="5" t="s">
+        <v>12039</v>
+      </c>
+      <c r="B6581" s="5" t="s">
+        <v>12050</v>
+      </c>
+    </row>
+    <row r="6582" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6582" s="5" t="s">
+        <v>12040</v>
+      </c>
+      <c r="B6582" s="5" t="s">
+        <v>12051</v>
+      </c>
+    </row>
+    <row r="6583" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6583" s="5" t="s">
+        <v>12041</v>
+      </c>
+      <c r="B6583" s="5" t="s">
+        <v>12052</v>
+      </c>
+    </row>
+    <row r="6584" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6584" s="5" t="s">
+        <v>12042</v>
+      </c>
+      <c r="B6584" s="5" t="s">
+        <v>12053</v>
+      </c>
+    </row>
+    <row r="6585" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6585" s="5" t="s">
+        <v>12043</v>
+      </c>
+      <c r="B6585" s="5" t="s">
+        <v>12054</v>
+      </c>
+    </row>
+    <row r="6586" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6586" s="5" t="s">
+        <v>12044</v>
+      </c>
+      <c r="B6586" s="5" t="s">
+        <v>12055</v>
+      </c>
+    </row>
+    <row r="6587" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6587" s="5" t="s">
+        <v>12045</v>
+      </c>
+      <c r="B6587" s="5" t="s">
+        <v>12056</v>
+      </c>
+    </row>
+    <row r="6588" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6588" s="5" t="s">
+        <v>12046</v>
+      </c>
+      <c r="B6588" s="5" t="s">
+        <v>12057</v>
+      </c>
+    </row>
+    <row r="6589" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6589" s="5" t="s">
+        <v>12058</v>
+      </c>
+      <c r="B6589" s="5" t="s">
+        <v>12059</v>
+      </c>
+    </row>
+    <row r="6590" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6590" s="5" t="s">
+        <v>12060</v>
+      </c>
+      <c r="B6590" s="5" t="s">
+        <v>12059</v>
+      </c>
+    </row>
+    <row r="6591" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6591" s="5" t="s">
+        <v>12061</v>
+      </c>
+      <c r="B6591" s="5" t="s">
+        <v>12065</v>
+      </c>
+    </row>
+    <row r="6592" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6592" s="5" t="s">
+        <v>12062</v>
+      </c>
+      <c r="B6592" s="5" t="s">
+        <v>12066</v>
+      </c>
+    </row>
+    <row r="6593" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6593" s="5" t="s">
+        <v>12063</v>
+      </c>
+      <c r="B6593" s="5" t="s">
+        <v>12067</v>
+      </c>
+    </row>
+    <row r="6594" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6594" s="5" t="s">
+        <v>12064</v>
+      </c>
+      <c r="B6594" s="5" t="s">
+        <v>12068</v>
+      </c>
+    </row>
+    <row r="6595" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6595" s="5" t="s">
+        <v>12069</v>
+      </c>
+      <c r="B6595" s="5" t="s">
+        <v>12070</v>
+      </c>
+    </row>
+    <row r="6596" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6596" s="5" t="s">
+        <v>12071</v>
+      </c>
+      <c r="B6596" s="5" t="s">
+        <v>12079</v>
+      </c>
+    </row>
+    <row r="6597" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6597" s="5" t="s">
+        <v>12072</v>
+      </c>
+      <c r="B6597" s="5" t="s">
+        <v>12080</v>
+      </c>
+    </row>
+    <row r="6598" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6598" s="5" t="s">
+        <v>12073</v>
+      </c>
+      <c r="B6598" s="5" t="s">
+        <v>12081</v>
+      </c>
+    </row>
+    <row r="6599" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6599" s="5" t="s">
+        <v>12074</v>
+      </c>
+      <c r="B6599" s="5" t="s">
+        <v>12082</v>
+      </c>
+    </row>
+    <row r="6600" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6600" s="5" t="s">
+        <v>12075</v>
+      </c>
+      <c r="B6600" s="5" t="s">
+        <v>12083</v>
+      </c>
+    </row>
+    <row r="6601" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6601" s="5" t="s">
+        <v>12076</v>
+      </c>
+      <c r="B6601" s="5" t="s">
+        <v>12084</v>
+      </c>
+    </row>
+    <row r="6602" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6602" s="5" t="s">
+        <v>12074</v>
+      </c>
+      <c r="B6602" s="5" t="s">
+        <v>12082</v>
+      </c>
+    </row>
+    <row r="6603" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6603" s="5" t="s">
+        <v>12077</v>
+      </c>
+      <c r="B6603" s="5" t="s">
+        <v>12085</v>
+      </c>
+    </row>
+    <row r="6604" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6604" s="5" t="s">
+        <v>12078</v>
+      </c>
+      <c r="B6604" s="5" t="s">
+        <v>12086</v>
+      </c>
+    </row>
+    <row r="6605" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6605" s="5" t="s">
+        <v>12087</v>
+      </c>
+      <c r="B6605" s="5" t="s">
+        <v>12088</v>
+      </c>
+    </row>
+    <row r="6606" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6606" s="5" t="s">
+        <v>12089</v>
+      </c>
+      <c r="B6606" s="5" t="s">
+        <v>12096</v>
+      </c>
+    </row>
+    <row r="6607" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6607" s="5" t="s">
+        <v>12090</v>
+      </c>
+      <c r="B6607" s="5" t="s">
+        <v>12097</v>
+      </c>
+    </row>
+    <row r="6608" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6608" s="5" t="s">
+        <v>12091</v>
+      </c>
+      <c r="B6608" s="5" t="s">
+        <v>12098</v>
+      </c>
+    </row>
+    <row r="6609" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6609" s="5" t="s">
+        <v>12092</v>
+      </c>
+      <c r="B6609" s="5" t="s">
+        <v>12099</v>
+      </c>
+    </row>
+    <row r="6610" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6610" s="5" t="s">
+        <v>12093</v>
+      </c>
+      <c r="B6610" s="5" t="s">
+        <v>12100</v>
+      </c>
+    </row>
+    <row r="6611" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6611" s="5" t="s">
+        <v>12094</v>
+      </c>
+      <c r="B6611" s="5" t="s">
+        <v>12101</v>
+      </c>
+    </row>
+    <row r="6612" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6612" s="5" t="s">
+        <v>12095</v>
+      </c>
+      <c r="B6612" s="5" t="s">
+        <v>12102</v>
+      </c>
+    </row>
+    <row r="6613" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6613" s="5" t="s">
+        <v>11683</v>
+      </c>
+      <c r="B6613" s="5" t="s">
+        <v>11693</v>
+      </c>
+    </row>
+    <row r="6614" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6614" s="5" t="s">
+        <v>11682</v>
+      </c>
+      <c r="B6614" s="5" t="s">
+        <v>11692</v>
+      </c>
+    </row>
+    <row r="6615" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6615" s="5" t="s">
+        <v>11684</v>
+      </c>
+      <c r="B6615" s="5" t="s">
+        <v>11694</v>
+      </c>
+    </row>
+    <row r="6616" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6616" s="5" t="s">
+        <v>11681</v>
+      </c>
+      <c r="B6616" s="5" t="s">
+        <v>11691</v>
+      </c>
+    </row>
+    <row r="6617" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6617" s="5" t="s">
+        <v>11680</v>
+      </c>
+      <c r="B6617" s="5" t="s">
+        <v>11690</v>
+      </c>
+    </row>
+    <row r="6618" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6618" s="5" t="s">
+        <v>11679</v>
+      </c>
+      <c r="B6618" s="5" t="s">
+        <v>11689</v>
+      </c>
+    </row>
+    <row r="6619" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6619" s="5" t="s">
+        <v>11678</v>
+      </c>
+      <c r="B6619" s="5" t="s">
+        <v>11688</v>
+      </c>
+    </row>
+    <row r="6620" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6620" s="5" t="s">
+        <v>12103</v>
+      </c>
+      <c r="B6620" s="5" t="s">
+        <v>12104</v>
+      </c>
+    </row>
+    <row r="6621" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6621" s="5" t="s">
+        <v>12105</v>
+      </c>
+      <c r="B6621" s="5" t="s">
+        <v>12112</v>
+      </c>
+    </row>
+    <row r="6622" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6622" s="5" t="s">
+        <v>12106</v>
+      </c>
+      <c r="B6622" s="5" t="s">
+        <v>12113</v>
+      </c>
+    </row>
+    <row r="6623" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6623" s="5" t="s">
+        <v>12107</v>
+      </c>
+      <c r="B6623" s="5" t="s">
+        <v>12114</v>
+      </c>
+    </row>
+    <row r="6624" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6624" s="5" t="s">
+        <v>12108</v>
+      </c>
+      <c r="B6624" s="5" t="s">
+        <v>12115</v>
+      </c>
+    </row>
+    <row r="6625" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6625" s="5" t="s">
+        <v>12109</v>
+      </c>
+      <c r="B6625" s="5" t="s">
+        <v>12116</v>
+      </c>
+    </row>
+    <row r="6626" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6626" s="5" t="s">
+        <v>12110</v>
+      </c>
+      <c r="B6626" s="5" t="s">
+        <v>12117</v>
+      </c>
+    </row>
+    <row r="6627" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6627" s="5" t="s">
+        <v>12111</v>
+      </c>
+      <c r="B6627" s="5" t="s">
+        <v>12118</v>
+      </c>
+    </row>
+    <row r="6628" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6628" s="5" t="s">
+        <v>12119</v>
+      </c>
+      <c r="B6628" s="5" t="s">
+        <v>12120</v>
+      </c>
+    </row>
+    <row r="6629" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6629" s="5" t="s">
+        <v>12121</v>
+      </c>
+      <c r="B6629" s="5" t="s">
+        <v>12129</v>
+      </c>
+    </row>
+    <row r="6630" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6630" s="5" t="s">
+        <v>12122</v>
+      </c>
+      <c r="B6630" s="5" t="s">
+        <v>12130</v>
+      </c>
+    </row>
+    <row r="6631" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6631" s="5" t="s">
+        <v>12123</v>
+      </c>
+      <c r="B6631" s="5" t="s">
+        <v>12131</v>
+      </c>
+    </row>
+    <row r="6632" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6632" s="5" t="s">
+        <v>12124</v>
+      </c>
+      <c r="B6632" s="5" t="s">
+        <v>12132</v>
+      </c>
+    </row>
+    <row r="6633" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6633" s="5" t="s">
+        <v>12125</v>
+      </c>
+      <c r="B6633" s="5" t="s">
+        <v>12133</v>
+      </c>
+    </row>
+    <row r="6634" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6634" s="5" t="s">
+        <v>12126</v>
+      </c>
+      <c r="B6634" s="5" t="s">
+        <v>12134</v>
+      </c>
+    </row>
+    <row r="6635" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6635" s="5" t="s">
+        <v>12127</v>
+      </c>
+      <c r="B6635" s="5" t="s">
+        <v>12135</v>
+      </c>
+    </row>
+    <row r="6636" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6636" s="5" t="s">
+        <v>12128</v>
+      </c>
+      <c r="B6636" s="5" t="s">
+        <v>12136</v>
+      </c>
+    </row>
+    <row r="6637" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6637" s="5" t="s">
+        <v>12137</v>
+      </c>
+      <c r="B6637" s="5" t="s">
+        <v>12138</v>
+      </c>
+    </row>
+    <row r="6638" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6638" s="5" t="s">
+        <v>12139</v>
+      </c>
+      <c r="B6638" s="5" t="s">
+        <v>12158</v>
+      </c>
+    </row>
+    <row r="6639" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6639" s="5" t="s">
+        <v>12140</v>
+      </c>
+      <c r="B6639" s="5" t="s">
+        <v>12159</v>
+      </c>
+    </row>
+    <row r="6640" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6640" s="5" t="s">
+        <v>12142</v>
+      </c>
+      <c r="B6640" s="5" t="s">
+        <v>12160</v>
+      </c>
+    </row>
+    <row r="6641" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6641" s="5" t="s">
+        <v>12143</v>
+      </c>
+      <c r="B6641" s="5" t="s">
+        <v>12161</v>
+      </c>
+    </row>
+    <row r="6642" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6642" s="5" t="s">
+        <v>12144</v>
+      </c>
+      <c r="B6642" s="5" t="s">
+        <v>12162</v>
+      </c>
+    </row>
+    <row r="6643" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6643" s="5" t="s">
+        <v>12145</v>
+      </c>
+      <c r="B6643" s="5" t="s">
+        <v>12163</v>
+      </c>
+    </row>
+    <row r="6644" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6644" s="5" t="s">
+        <v>12146</v>
+      </c>
+      <c r="B6644" s="5" t="s">
+        <v>12164</v>
+      </c>
+    </row>
+    <row r="6645" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6645" s="5" t="s">
+        <v>12147</v>
+      </c>
+      <c r="B6645" s="5" t="s">
+        <v>12165</v>
+      </c>
+    </row>
+    <row r="6646" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6646" s="5" t="s">
+        <v>12148</v>
+      </c>
+      <c r="B6646" s="5" t="s">
+        <v>12166</v>
+      </c>
+    </row>
+    <row r="6647" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6647" s="5" t="s">
+        <v>12149</v>
+      </c>
+      <c r="B6647" s="5" t="s">
+        <v>12167</v>
+      </c>
+    </row>
+    <row r="6648" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6648" s="5" t="s">
+        <v>12150</v>
+      </c>
+      <c r="B6648" s="5" t="s">
+        <v>12168</v>
+      </c>
+    </row>
+    <row r="6649" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6649" s="5" t="s">
+        <v>12151</v>
+      </c>
+      <c r="B6649" s="5" t="s">
+        <v>12169</v>
+      </c>
+    </row>
+    <row r="6650" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6650" s="5" t="s">
+        <v>12152</v>
+      </c>
+      <c r="B6650" s="5" t="s">
+        <v>12170</v>
+      </c>
+    </row>
+    <row r="6651" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6651" s="5" t="s">
+        <v>12153</v>
+      </c>
+      <c r="B6651" s="5" t="s">
+        <v>12171</v>
+      </c>
+    </row>
+    <row r="6652" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6652" s="5" t="s">
+        <v>12154</v>
+      </c>
+      <c r="B6652" s="5" t="s">
+        <v>12172</v>
+      </c>
+    </row>
+    <row r="6653" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6653" s="5" t="s">
+        <v>12141</v>
+      </c>
+      <c r="B6653" s="5" t="s">
+        <v>12173</v>
+      </c>
+    </row>
+    <row r="6654" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6654" s="5" t="s">
+        <v>12155</v>
+      </c>
+      <c r="B6654" s="5" t="s">
+        <v>12174</v>
+      </c>
+    </row>
+    <row r="6655" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6655" s="5" t="s">
+        <v>12156</v>
+      </c>
+      <c r="B6655" s="5" t="s">
+        <v>12175</v>
+      </c>
+    </row>
+    <row r="6656" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6656" s="5" t="s">
+        <v>12157</v>
+      </c>
+      <c r="B6656" s="5" t="s">
+        <v>12176</v>
+      </c>
+    </row>
+    <row r="6657" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6657" s="5" t="s">
+        <v>12177</v>
+      </c>
+    </row>
+    <row r="6658" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6658" s="5" t="s">
+        <v>12178</v>
+      </c>
+      <c r="B6658" s="5" t="s">
+        <v>12179</v>
+      </c>
+    </row>
+    <row r="6659" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6659" s="5" t="s">
+        <v>12180</v>
+      </c>
+      <c r="B6659" s="5" t="s">
+        <v>12184</v>
+      </c>
+    </row>
+    <row r="6660" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6660" s="5" t="s">
+        <v>12181</v>
+      </c>
+      <c r="B6660" s="5" t="s">
+        <v>12185</v>
+      </c>
+    </row>
+    <row r="6661" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6661" s="5" t="s">
+        <v>12182</v>
+      </c>
+      <c r="B6661" s="5" t="s">
+        <v>12186</v>
+      </c>
+    </row>
+    <row r="6662" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6662" s="5" t="s">
+        <v>12183</v>
+      </c>
+      <c r="B6662" s="5" t="s">
+        <v>12187</v>
+      </c>
+    </row>
+    <row r="6663" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6663" s="5" t="s">
+        <v>12188</v>
+      </c>
+      <c r="B6663" s="5" t="s">
+        <v>12194</v>
+      </c>
+    </row>
+    <row r="6664" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6664" s="5" t="s">
+        <v>12189</v>
+      </c>
+      <c r="B6664" s="5" t="s">
+        <v>12195</v>
+      </c>
+    </row>
+    <row r="6665" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6665" s="5" t="s">
+        <v>12190</v>
+      </c>
+      <c r="B6665" s="5" t="s">
+        <v>12195</v>
+      </c>
+    </row>
+    <row r="6666" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6666" s="5" t="s">
+        <v>12191</v>
+      </c>
+      <c r="B6666" s="5" t="s">
+        <v>12196</v>
+      </c>
+    </row>
+    <row r="6667" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6667" s="5" t="s">
+        <v>12192</v>
+      </c>
+      <c r="B6667" s="5" t="s">
+        <v>12197</v>
+      </c>
+    </row>
+    <row r="6668" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6668" s="5" t="s">
+        <v>12193</v>
+      </c>
+      <c r="B6668" s="5" t="s">
+        <v>12198</v>
+      </c>
+    </row>
+    <row r="6669" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6669" s="5" t="s">
+        <v>12199</v>
+      </c>
+      <c r="B6669" s="5" t="s">
+        <v>12213</v>
+      </c>
+    </row>
+    <row r="6670" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6670" s="5" t="s">
+        <v>12201</v>
+      </c>
+      <c r="B6670" s="5" t="s">
+        <v>12200</v>
+      </c>
+    </row>
+    <row r="6671" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6671" s="5" t="s">
+        <v>12202</v>
+      </c>
+      <c r="B6671" s="5" t="s">
+        <v>12214</v>
+      </c>
+    </row>
+    <row r="6672" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6672" s="5" t="s">
+        <v>12203</v>
+      </c>
+      <c r="B6672" s="5" t="s">
+        <v>12215</v>
+      </c>
+    </row>
+    <row r="6673" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6673" s="5" t="s">
+        <v>12204</v>
+      </c>
+      <c r="B6673" s="5" t="s">
+        <v>12216</v>
+      </c>
+    </row>
+    <row r="6674" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6674" s="5" t="s">
+        <v>12205</v>
+      </c>
+      <c r="B6674" s="5" t="s">
+        <v>12217</v>
+      </c>
+    </row>
+    <row r="6675" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6675" s="5" t="s">
+        <v>12206</v>
+      </c>
+      <c r="B6675" s="5" t="s">
+        <v>12249</v>
+      </c>
+    </row>
+    <row r="6676" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6676" s="5" t="s">
+        <v>12207</v>
+      </c>
+      <c r="B6676" s="5" t="s">
+        <v>12250</v>
+      </c>
+    </row>
+    <row r="6677" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6677" s="5" t="s">
+        <v>12208</v>
+      </c>
+      <c r="B6677" s="5" t="s">
+        <v>12251</v>
+      </c>
+    </row>
+    <row r="6678" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6678" s="5" t="s">
+        <v>12209</v>
+      </c>
+      <c r="B6678" s="5" t="s">
+        <v>12252</v>
+      </c>
+    </row>
+    <row r="6679" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6679" s="5" t="s">
+        <v>12210</v>
+      </c>
+      <c r="B6679" s="5" t="s">
+        <v>12253</v>
+      </c>
+    </row>
+    <row r="6680" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6680" s="5" t="s">
+        <v>12211</v>
+      </c>
+      <c r="B6680" s="5" t="s">
+        <v>12254</v>
+      </c>
+    </row>
+    <row r="6681" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6681" s="5" t="s">
+        <v>12212</v>
+      </c>
+      <c r="B6681" s="5" t="s">
+        <v>12255</v>
+      </c>
+    </row>
+    <row r="6682" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6682" s="5" t="s">
+        <v>12245</v>
+      </c>
+      <c r="B6682" s="5" t="s">
+        <v>12256</v>
+      </c>
+    </row>
+    <row r="6683" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6683" s="5" t="s">
+        <v>12246</v>
+      </c>
+      <c r="B6683" s="5" t="s">
+        <v>12257</v>
+      </c>
+    </row>
+    <row r="6684" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6684" s="5" t="s">
+        <v>12247</v>
+      </c>
+      <c r="B6684" s="5" t="s">
+        <v>12225</v>
+      </c>
+    </row>
+    <row r="6685" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6685" s="5" t="s">
+        <v>12248</v>
+      </c>
+      <c r="B6685" s="5" t="s">
+        <v>12258</v>
+      </c>
+    </row>
+    <row r="6686" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6686" s="5" t="s">
+        <v>12218</v>
+      </c>
+      <c r="B6686" s="5" t="s">
+        <v>12219</v>
+      </c>
+    </row>
+    <row r="6687" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6687" s="5" t="s">
+        <v>12220</v>
+      </c>
+      <c r="B6687" s="5" t="s">
+        <v>12225</v>
+      </c>
+    </row>
+    <row r="6688" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6688" s="5" t="s">
+        <v>12221</v>
+      </c>
+      <c r="B6688" s="5" t="s">
+        <v>12226</v>
+      </c>
+    </row>
+    <row r="6689" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6689" s="5" t="s">
+        <v>12222</v>
+      </c>
+      <c r="B6689" s="5" t="s">
+        <v>12227</v>
+      </c>
+    </row>
+    <row r="6690" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6690" s="5" t="s">
+        <v>12223</v>
+      </c>
+      <c r="B6690" s="5" t="s">
+        <v>12228</v>
+      </c>
+    </row>
+    <row r="6691" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6691" s="5" t="s">
+        <v>12224</v>
+      </c>
+      <c r="B6691" s="5" t="s">
+        <v>12219</v>
+      </c>
+    </row>
+    <row r="6692" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6692" s="5" t="s">
+        <v>12229</v>
+      </c>
+      <c r="B6692" s="5" t="s">
+        <v>12219</v>
+      </c>
+    </row>
+    <row r="6693" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6693" s="5" t="s">
+        <v>12230</v>
+      </c>
+      <c r="B6693" s="5" t="s">
+        <v>12219</v>
+      </c>
+    </row>
+    <row r="6694" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6694" s="5" t="s">
+        <v>12231</v>
+      </c>
+      <c r="B6694" s="5" t="s">
+        <v>12219</v>
+      </c>
+    </row>
+    <row r="6695" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6695" s="5" t="s">
+        <v>12232</v>
+      </c>
+      <c r="B6695" s="5" t="s">
+        <v>12219</v>
+      </c>
+    </row>
+    <row r="6696" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6696" s="5" t="s">
+        <v>12233</v>
+      </c>
+      <c r="B6696" s="5" t="s">
+        <v>12219</v>
+      </c>
+    </row>
+    <row r="6697" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6697" s="5" t="s">
+        <v>12234</v>
+      </c>
+      <c r="B6697" s="5" t="s">
+        <v>12219</v>
+      </c>
+    </row>
+    <row r="6698" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6698" s="5" t="s">
+        <v>12235</v>
+      </c>
+      <c r="B6698" s="5" t="s">
+        <v>12240</v>
+      </c>
+    </row>
+    <row r="6699" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6699" s="5" t="s">
+        <v>12236</v>
+      </c>
+      <c r="B6699" s="5" t="s">
+        <v>12241</v>
+      </c>
+    </row>
+    <row r="6700" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6700" s="5" t="s">
+        <v>12237</v>
+      </c>
+      <c r="B6700" s="5" t="s">
+        <v>12244</v>
+      </c>
+    </row>
+    <row r="6701" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6701" s="5" t="s">
+        <v>12238</v>
+      </c>
+      <c r="B6701" s="5" t="s">
+        <v>12242</v>
+      </c>
+    </row>
+    <row r="6702" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6702" s="5" t="s">
+        <v>12239</v>
+      </c>
+      <c r="B6702" s="5" t="s">
+        <v>12243</v>
+      </c>
+    </row>
+    <row r="6703" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6703" s="5" t="s">
+        <v>12259</v>
+      </c>
+      <c r="B6703" s="5" t="s">
+        <v>12260</v>
+      </c>
+    </row>
+    <row r="6704" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6704" s="5" t="s">
+        <v>12261</v>
+      </c>
+      <c r="B6704" s="5" t="s">
+        <v>12269</v>
+      </c>
+    </row>
+    <row r="6705" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6705" s="5" t="s">
+        <v>12262</v>
+      </c>
+      <c r="B6705" s="5" t="s">
+        <v>12270</v>
+      </c>
+    </row>
+    <row r="6706" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6706" s="5" t="s">
+        <v>12263</v>
+      </c>
+      <c r="B6706" s="5" t="s">
+        <v>12270</v>
+      </c>
+    </row>
+    <row r="6707" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6707" s="5" t="s">
+        <v>12264</v>
+      </c>
+      <c r="B6707" s="5" t="s">
+        <v>12271</v>
+      </c>
+    </row>
+    <row r="6708" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6708" s="5" t="s">
+        <v>12265</v>
+      </c>
+      <c r="B6708" s="5" t="s">
+        <v>12269</v>
+      </c>
+    </row>
+    <row r="6709" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6709" s="5" t="s">
+        <v>12266</v>
+      </c>
+      <c r="B6709" s="5" t="s">
+        <v>12272</v>
+      </c>
+    </row>
+    <row r="6710" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6710" s="5" t="s">
+        <v>12267</v>
+      </c>
+      <c r="B6710" s="5" t="s">
+        <v>12273</v>
+      </c>
+    </row>
+    <row r="6711" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6711" s="5" t="s">
+        <v>12268</v>
+      </c>
+      <c r="B6711" s="5" t="s">
+        <v>12274</v>
+      </c>
+    </row>
+    <row r="6712" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6712" s="5" t="s">
+        <v>12275</v>
+      </c>
+    </row>
+    <row r="6713" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6713" s="5" t="s">
+        <v>12276</v>
+      </c>
+      <c r="B6713" s="5" t="s">
+        <v>12277</v>
+      </c>
+    </row>
+    <row r="6714" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6714" s="5" t="s">
+        <v>12278</v>
+      </c>
+      <c r="B6714" s="5" t="s">
+        <v>12287</v>
+      </c>
+    </row>
+    <row r="6715" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6715" s="5" t="s">
+        <v>12279</v>
+      </c>
+      <c r="B6715" s="5" t="s">
+        <v>12288</v>
+      </c>
+    </row>
+    <row r="6716" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6716" s="5" t="s">
+        <v>12280</v>
+      </c>
+      <c r="B6716" s="5" t="s">
+        <v>12289</v>
+      </c>
+    </row>
+    <row r="6717" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6717" s="5" t="s">
+        <v>12281</v>
+      </c>
+      <c r="B6717" s="5" t="s">
+        <v>12290</v>
+      </c>
+    </row>
+    <row r="6718" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6718" s="5" t="s">
+        <v>12282</v>
+      </c>
+      <c r="B6718" s="5" t="s">
+        <v>12291</v>
+      </c>
+    </row>
+    <row r="6719" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6719" s="5" t="s">
+        <v>12283</v>
+      </c>
+      <c r="B6719" s="5" t="s">
+        <v>12292</v>
+      </c>
+    </row>
+    <row r="6720" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6720" s="5" t="s">
+        <v>12284</v>
+      </c>
+      <c r="B6720" s="5" t="s">
+        <v>12293</v>
+      </c>
+    </row>
+    <row r="6721" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6721" s="5" t="s">
+        <v>12285</v>
+      </c>
+      <c r="B6721" s="5" t="s">
+        <v>12294</v>
+      </c>
+    </row>
+    <row r="6722" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6722" s="5" t="s">
+        <v>12286</v>
+      </c>
+      <c r="B6722" s="5" t="s">
+        <v>12295</v>
+      </c>
+    </row>
+    <row r="6723" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6723" s="5" t="s">
+        <v>12296</v>
+      </c>
+      <c r="B6723" s="5" t="s">
+        <v>12297</v>
+      </c>
+    </row>
+    <row r="6724" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6724" s="5" t="s">
+        <v>12298</v>
+      </c>
+      <c r="B6724" s="5" t="s">
+        <v>12302</v>
+      </c>
+    </row>
+    <row r="6725" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6725" s="5" t="s">
+        <v>12299</v>
+      </c>
+      <c r="B6725" s="5" t="s">
+        <v>12303</v>
+      </c>
+    </row>
+    <row r="6726" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6726" s="5" t="s">
+        <v>12300</v>
+      </c>
+      <c r="B6726" s="5" t="s">
+        <v>12304</v>
+      </c>
+    </row>
+    <row r="6727" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6727" s="5" t="s">
+        <v>12301</v>
+      </c>
+      <c r="B6727" s="5" t="s">
+        <v>12305</v>
       </c>
     </row>
   </sheetData>

--- a/словари/переведённые_слова.xlsx
+++ b/словари/переведённые_слова.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C16E5B1-85EF-478F-995E-D5CFC30DD50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919FE7D2-0AF6-4C24-9E1B-69CA5294D619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9225" yWindow="60" windowWidth="18270" windowHeight="14100" tabRatio="831" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13575" yWindow="0" windowWidth="13890" windowHeight="14775" tabRatio="831" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="переведенные слова" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Лист1" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Лист3!$A$1:$B$6375</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Лист3!$A$1:$B$6386</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13374" uniqueCount="12306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13386" uniqueCount="12315">
   <si>
     <t>Абонемент - подписка</t>
   </si>
@@ -36951,6 +36951,33 @@
   </si>
   <si>
     <t>ковку</t>
+  </si>
+  <si>
+    <t>круизы</t>
+  </si>
+  <si>
+    <t>альтруистичная</t>
+  </si>
+  <si>
+    <t>альтруистично</t>
+  </si>
+  <si>
+    <t>альтруистичности</t>
+  </si>
+  <si>
+    <t>альтруистичность</t>
+  </si>
+  <si>
+    <t>альтруистичностью</t>
+  </si>
+  <si>
+    <t>альтруистичностями</t>
+  </si>
+  <si>
+    <t>альтруистичностям</t>
+  </si>
+  <si>
+    <t>альтруистичностей</t>
   </si>
 </sst>
 </file>
@@ -37029,7 +37056,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -37045,6 +37072,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF6F6F6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -37077,7 +37110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -37097,6 +37130,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -37423,7 +37457,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C6727"/>
+  <dimension ref="A1:C6739"/>
   <sheetFormatPr defaultColWidth="12.85546875" defaultRowHeight="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.140625" style="5" customWidth="1"/>
@@ -80588,7 +80622,7 @@
         <v>10630</v>
       </c>
     </row>
-    <row r="5507" spans="1:3" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5507" spans="1:3" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5507" s="5" t="s">
         <v>9094</v>
       </c>
@@ -86909,3365 +86943,3425 @@
     </row>
     <row r="6304" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6304" s="5" t="s">
-        <v>11519</v>
-      </c>
-      <c r="B6304" s="5" t="s">
-        <v>10874</v>
+        <v>11499</v>
       </c>
     </row>
     <row r="6305" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6305" s="5" t="s">
-        <v>11520</v>
-      </c>
-      <c r="B6305" s="5" t="s">
-        <v>10873</v>
+        <v>12307</v>
       </c>
     </row>
     <row r="6306" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6306" s="5" t="s">
-        <v>11521</v>
-      </c>
-      <c r="B6306" s="5" t="s">
-        <v>10872</v>
+        <v>12308</v>
       </c>
     </row>
     <row r="6307" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6307" s="5" t="s">
-        <v>11522</v>
-      </c>
-      <c r="B6307" s="5" t="s">
-        <v>11524</v>
+        <v>12309</v>
       </c>
     </row>
     <row r="6308" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6308" s="5" t="s">
-        <v>11523</v>
-      </c>
-      <c r="B6308" s="5" t="s">
-        <v>11525</v>
+        <v>12310</v>
       </c>
     </row>
     <row r="6309" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6309" s="5" t="s">
-        <v>11526</v>
-      </c>
-      <c r="B6309" s="5" t="s">
-        <v>11527</v>
+        <v>12311</v>
       </c>
     </row>
     <row r="6310" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6310" s="5" t="s">
-        <v>11528</v>
-      </c>
-      <c r="B6310" s="5" t="s">
-        <v>11532</v>
+        <v>12312</v>
       </c>
     </row>
     <row r="6311" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6311" s="5" t="s">
-        <v>11529</v>
-      </c>
-      <c r="B6311" s="5" t="s">
-        <v>11533</v>
+        <v>12313</v>
       </c>
     </row>
     <row r="6312" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6312" s="5" t="s">
-        <v>11530</v>
-      </c>
-      <c r="B6312" s="5" t="s">
-        <v>11534</v>
+        <v>12314</v>
       </c>
     </row>
     <row r="6313" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6313" s="5" t="s">
-        <v>11531</v>
-      </c>
-      <c r="B6313" s="5" t="s">
-        <v>11535</v>
+        <v>12312</v>
       </c>
     </row>
     <row r="6314" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6314" s="5" t="s">
-        <v>11536</v>
-      </c>
-      <c r="B6314" s="5" t="s">
-        <v>11537</v>
+        <v>12312</v>
       </c>
     </row>
     <row r="6315" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6315" s="5" t="s">
-        <v>11538</v>
+        <v>11519</v>
       </c>
       <c r="B6315" s="5" t="s">
-        <v>11541</v>
+        <v>10874</v>
       </c>
     </row>
     <row r="6316" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6316" s="5" t="s">
-        <v>11539</v>
+        <v>11520</v>
       </c>
       <c r="B6316" s="5" t="s">
-        <v>11542</v>
+        <v>10873</v>
       </c>
     </row>
     <row r="6317" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6317" s="5" t="s">
-        <v>11540</v>
+        <v>11521</v>
       </c>
       <c r="B6317" s="5" t="s">
-        <v>11543</v>
+        <v>10872</v>
       </c>
     </row>
     <row r="6318" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6318" s="5" t="s">
-        <v>11544</v>
+        <v>11522</v>
       </c>
       <c r="B6318" s="5" t="s">
-        <v>11545</v>
+        <v>11524</v>
       </c>
     </row>
     <row r="6319" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6319" s="5" t="s">
-        <v>11546</v>
+        <v>11523</v>
       </c>
       <c r="B6319" s="5" t="s">
-        <v>11550</v>
+        <v>11525</v>
       </c>
     </row>
     <row r="6320" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6320" s="5" t="s">
-        <v>11547</v>
+        <v>11526</v>
       </c>
       <c r="B6320" s="5" t="s">
-        <v>11550</v>
+        <v>11527</v>
       </c>
     </row>
     <row r="6321" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6321" s="5" t="s">
-        <v>11548</v>
+        <v>11528</v>
       </c>
       <c r="B6321" s="5" t="s">
-        <v>11550</v>
+        <v>11532</v>
       </c>
     </row>
     <row r="6322" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6322" s="5" t="s">
-        <v>11549</v>
+        <v>11529</v>
       </c>
       <c r="B6322" s="5" t="s">
-        <v>11550</v>
+        <v>11533</v>
       </c>
     </row>
     <row r="6323" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6323" s="5" t="s">
-        <v>11551</v>
+        <v>11530</v>
       </c>
       <c r="B6323" s="5" t="s">
-        <v>11642</v>
+        <v>11534</v>
       </c>
     </row>
     <row r="6324" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6324" s="5" t="s">
-        <v>11552</v>
+        <v>11531</v>
       </c>
       <c r="B6324" s="5" t="s">
-        <v>11643</v>
+        <v>11535</v>
       </c>
     </row>
     <row r="6325" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6325" s="5" t="s">
-        <v>11553</v>
+        <v>11536</v>
       </c>
       <c r="B6325" s="5" t="s">
-        <v>11644</v>
+        <v>11537</v>
       </c>
     </row>
     <row r="6326" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6326" s="5" t="s">
-        <v>11554</v>
+        <v>11538</v>
       </c>
       <c r="B6326" s="5" t="s">
-        <v>11645</v>
+        <v>11541</v>
       </c>
     </row>
     <row r="6327" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6327" s="5" t="s">
-        <v>11555</v>
+        <v>11539</v>
       </c>
       <c r="B6327" s="5" t="s">
-        <v>11646</v>
+        <v>11542</v>
       </c>
     </row>
     <row r="6328" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6328" s="5" t="s">
-        <v>11556</v>
+        <v>11540</v>
       </c>
       <c r="B6328" s="5" t="s">
-        <v>11560</v>
+        <v>11543</v>
       </c>
     </row>
     <row r="6329" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6329" s="5" t="s">
-        <v>8899</v>
+        <v>11544</v>
       </c>
       <c r="B6329" s="5" t="s">
-        <v>11557</v>
+        <v>11545</v>
       </c>
     </row>
     <row r="6330" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6330" s="5" t="s">
-        <v>11558</v>
+        <v>11546</v>
       </c>
       <c r="B6330" s="5" t="s">
-        <v>11561</v>
+        <v>11550</v>
       </c>
     </row>
     <row r="6331" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6331" s="5" t="s">
-        <v>11559</v>
+        <v>11547</v>
       </c>
       <c r="B6331" s="5" t="s">
-        <v>11562</v>
+        <v>11550</v>
       </c>
     </row>
     <row r="6332" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6332" s="5" t="s">
-        <v>11563</v>
+        <v>11548</v>
       </c>
       <c r="B6332" s="5" t="s">
-        <v>11564</v>
+        <v>11550</v>
       </c>
     </row>
     <row r="6333" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6333" s="5" t="s">
-        <v>11565</v>
+        <v>11549</v>
       </c>
       <c r="B6333" s="5" t="s">
-        <v>11570</v>
+        <v>11550</v>
       </c>
     </row>
     <row r="6334" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6334" s="5" t="s">
-        <v>11566</v>
+        <v>11551</v>
       </c>
       <c r="B6334" s="5" t="s">
-        <v>11571</v>
+        <v>11642</v>
       </c>
     </row>
     <row r="6335" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6335" s="5" t="s">
-        <v>11567</v>
+        <v>11552</v>
       </c>
       <c r="B6335" s="5" t="s">
-        <v>11572</v>
+        <v>11643</v>
       </c>
     </row>
     <row r="6336" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6336" s="5" t="s">
-        <v>11568</v>
+        <v>11553</v>
       </c>
       <c r="B6336" s="5" t="s">
-        <v>11573</v>
+        <v>11644</v>
       </c>
     </row>
     <row r="6337" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6337" s="5" t="s">
-        <v>11569</v>
+        <v>11554</v>
       </c>
       <c r="B6337" s="5" t="s">
-        <v>11574</v>
+        <v>11645</v>
       </c>
     </row>
     <row r="6338" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6338" s="5" t="s">
-        <v>11575</v>
+        <v>11555</v>
       </c>
       <c r="B6338" s="5" t="s">
-        <v>11576</v>
+        <v>11646</v>
       </c>
     </row>
     <row r="6339" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6339" s="5" t="s">
-        <v>11577</v>
+        <v>11556</v>
       </c>
       <c r="B6339" s="5" t="s">
-        <v>11593</v>
+        <v>11560</v>
       </c>
     </row>
     <row r="6340" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6340" s="5" t="s">
-        <v>11578</v>
+        <v>8899</v>
       </c>
       <c r="B6340" s="5" t="s">
-        <v>11594</v>
+        <v>11557</v>
       </c>
     </row>
     <row r="6341" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6341" s="5" t="s">
-        <v>11579</v>
+        <v>11558</v>
       </c>
       <c r="B6341" s="5" t="s">
-        <v>11597</v>
+        <v>11561</v>
       </c>
     </row>
     <row r="6342" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6342" s="5" t="s">
-        <v>11580</v>
+        <v>11559</v>
       </c>
       <c r="B6342" s="5" t="s">
-        <v>11598</v>
+        <v>11562</v>
       </c>
     </row>
     <row r="6343" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6343" s="5" t="s">
-        <v>11577</v>
+        <v>11563</v>
       </c>
       <c r="B6343" s="5" t="s">
-        <v>11593</v>
+        <v>11564</v>
       </c>
     </row>
     <row r="6344" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6344" s="5" t="s">
-        <v>11581</v>
+        <v>11565</v>
       </c>
       <c r="B6344" s="5" t="s">
-        <v>11599</v>
+        <v>11570</v>
       </c>
     </row>
     <row r="6345" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6345" s="5" t="s">
-        <v>11582</v>
+        <v>11566</v>
       </c>
       <c r="B6345" s="5" t="s">
-        <v>11600</v>
+        <v>11571</v>
       </c>
     </row>
     <row r="6346" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6346" s="5" t="s">
-        <v>11583</v>
+        <v>11567</v>
       </c>
       <c r="B6346" s="5" t="s">
-        <v>11601</v>
+        <v>11572</v>
       </c>
     </row>
     <row r="6347" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6347" s="5" t="s">
-        <v>11584</v>
+        <v>11568</v>
       </c>
       <c r="B6347" s="5" t="s">
-        <v>11602</v>
+        <v>11573</v>
       </c>
     </row>
     <row r="6348" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6348" s="5" t="s">
-        <v>11585</v>
+        <v>11569</v>
       </c>
       <c r="B6348" s="5" t="s">
-        <v>11603</v>
+        <v>11574</v>
       </c>
     </row>
     <row r="6349" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6349" s="5" t="s">
-        <v>11586</v>
+        <v>11575</v>
       </c>
       <c r="B6349" s="5" t="s">
-        <v>11595</v>
+        <v>11576</v>
       </c>
     </row>
     <row r="6350" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6350" s="5" t="s">
-        <v>11587</v>
+        <v>11577</v>
       </c>
       <c r="B6350" s="5" t="s">
-        <v>11596</v>
+        <v>11593</v>
       </c>
     </row>
     <row r="6351" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6351" s="5" t="s">
-        <v>11588</v>
+        <v>11578</v>
       </c>
       <c r="B6351" s="5" t="s">
-        <v>11604</v>
+        <v>11594</v>
       </c>
     </row>
     <row r="6352" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6352" s="5" t="s">
-        <v>11589</v>
+        <v>11579</v>
       </c>
       <c r="B6352" s="5" t="s">
-        <v>11605</v>
+        <v>11597</v>
       </c>
     </row>
     <row r="6353" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6353" s="5" t="s">
-        <v>11590</v>
+        <v>11580</v>
       </c>
       <c r="B6353" s="5" t="s">
-        <v>11606</v>
+        <v>11598</v>
       </c>
     </row>
     <row r="6354" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6354" s="5" t="s">
-        <v>11591</v>
+        <v>11577</v>
       </c>
       <c r="B6354" s="5" t="s">
-        <v>11607</v>
+        <v>11593</v>
       </c>
     </row>
     <row r="6355" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6355" s="5" t="s">
-        <v>11592</v>
+        <v>11581</v>
       </c>
       <c r="B6355" s="5" t="s">
-        <v>11608</v>
+        <v>11599</v>
       </c>
     </row>
     <row r="6356" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6356" s="5" t="s">
-        <v>11609</v>
+        <v>11582</v>
       </c>
       <c r="B6356" s="5" t="s">
-        <v>11610</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="6357" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6357" s="5" t="s">
-        <v>11611</v>
+        <v>11583</v>
       </c>
       <c r="B6357" s="5" t="s">
-        <v>11615</v>
+        <v>11601</v>
       </c>
     </row>
     <row r="6358" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6358" s="5" t="s">
-        <v>11612</v>
+        <v>11584</v>
       </c>
       <c r="B6358" s="5" t="s">
-        <v>11616</v>
+        <v>11602</v>
       </c>
     </row>
     <row r="6359" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6359" s="5" t="s">
-        <v>11613</v>
+        <v>11585</v>
       </c>
       <c r="B6359" s="5" t="s">
-        <v>11617</v>
+        <v>11603</v>
       </c>
     </row>
     <row r="6360" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6360" s="5" t="s">
-        <v>11614</v>
+        <v>11586</v>
       </c>
       <c r="B6360" s="5" t="s">
-        <v>11618</v>
+        <v>11595</v>
       </c>
     </row>
     <row r="6361" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6361" s="5" t="s">
-        <v>11619</v>
+        <v>11587</v>
+      </c>
+      <c r="B6361" s="5" t="s">
+        <v>11596</v>
       </c>
     </row>
     <row r="6362" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6362" s="5" t="s">
-        <v>11620</v>
+        <v>11588</v>
       </c>
       <c r="B6362" s="5" t="s">
-        <v>11621</v>
+        <v>11604</v>
       </c>
     </row>
     <row r="6363" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6363" s="5" t="s">
-        <v>11622</v>
+        <v>11589</v>
       </c>
       <c r="B6363" s="5" t="s">
-        <v>11627</v>
+        <v>11605</v>
       </c>
     </row>
     <row r="6364" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6364" s="5" t="s">
-        <v>11623</v>
+        <v>11590</v>
       </c>
       <c r="B6364" s="5" t="s">
-        <v>11628</v>
+        <v>11606</v>
       </c>
     </row>
     <row r="6365" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6365" s="5" t="s">
-        <v>11624</v>
+        <v>11591</v>
       </c>
       <c r="B6365" s="5" t="s">
-        <v>11629</v>
+        <v>11607</v>
       </c>
     </row>
     <row r="6366" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6366" s="5" t="s">
-        <v>11625</v>
+        <v>11592</v>
       </c>
       <c r="B6366" s="5" t="s">
-        <v>2382</v>
+        <v>11608</v>
       </c>
     </row>
     <row r="6367" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6367" s="5" t="s">
-        <v>11626</v>
+        <v>11609</v>
       </c>
       <c r="B6367" s="5" t="s">
-        <v>2388</v>
+        <v>11610</v>
       </c>
     </row>
     <row r="6368" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6368" s="5" t="s">
-        <v>11630</v>
+        <v>11611</v>
       </c>
       <c r="B6368" s="5" t="s">
-        <v>11631</v>
+        <v>11615</v>
       </c>
     </row>
     <row r="6369" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6369" s="5" t="s">
-        <v>11632</v>
+        <v>11612</v>
       </c>
       <c r="B6369" s="5" t="s">
-        <v>11631</v>
+        <v>11616</v>
       </c>
     </row>
     <row r="6370" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6370" s="5" t="s">
-        <v>11633</v>
+        <v>11613</v>
       </c>
       <c r="B6370" s="5" t="s">
-        <v>11635</v>
+        <v>11617</v>
       </c>
     </row>
     <row r="6371" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6371" s="5" t="s">
-        <v>11634</v>
+        <v>11614</v>
       </c>
       <c r="B6371" s="5" t="s">
-        <v>11636</v>
+        <v>11618</v>
       </c>
     </row>
     <row r="6372" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6372" s="5" t="s">
-        <v>11637</v>
+        <v>11619</v>
       </c>
     </row>
     <row r="6373" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6373" s="5" t="s">
-        <v>11638</v>
+        <v>11620</v>
+      </c>
+      <c r="B6373" s="5" t="s">
+        <v>11621</v>
       </c>
     </row>
     <row r="6374" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6374" s="5" t="s">
-        <v>11639</v>
+        <v>11622</v>
+      </c>
+      <c r="B6374" s="5" t="s">
+        <v>11627</v>
       </c>
     </row>
     <row r="6375" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6375" s="5" t="s">
-        <v>11640</v>
+        <v>11623</v>
+      </c>
+      <c r="B6375" s="5" t="s">
+        <v>11628</v>
       </c>
     </row>
     <row r="6376" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6376" s="5" t="s">
-        <v>11647</v>
+        <v>11624</v>
       </c>
       <c r="B6376" s="5" t="s">
-        <v>11648</v>
+        <v>11629</v>
       </c>
     </row>
     <row r="6377" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6377" s="5" t="s">
-        <v>11649</v>
+        <v>11625</v>
       </c>
       <c r="B6377" s="5" t="s">
-        <v>11661</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="6378" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6378" s="5" t="s">
-        <v>11650</v>
+        <v>11626</v>
       </c>
       <c r="B6378" s="5" t="s">
-        <v>11662</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="6379" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6379" s="5" t="s">
-        <v>11651</v>
+        <v>11630</v>
       </c>
       <c r="B6379" s="5" t="s">
-        <v>11663</v>
+        <v>11631</v>
       </c>
     </row>
     <row r="6380" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6380" s="5" t="s">
-        <v>11652</v>
+        <v>11632</v>
       </c>
       <c r="B6380" s="5" t="s">
-        <v>11664</v>
+        <v>11631</v>
       </c>
     </row>
     <row r="6381" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6381" s="5" t="s">
-        <v>11653</v>
+        <v>11633</v>
       </c>
       <c r="B6381" s="5" t="s">
-        <v>11665</v>
+        <v>11635</v>
       </c>
     </row>
     <row r="6382" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6382" s="5" t="s">
-        <v>11654</v>
+        <v>11634</v>
       </c>
       <c r="B6382" s="5" t="s">
-        <v>11666</v>
+        <v>11636</v>
       </c>
     </row>
     <row r="6383" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6383" s="5" t="s">
-        <v>11655</v>
-      </c>
-      <c r="B6383" s="5" t="s">
-        <v>11667</v>
+        <v>11637</v>
       </c>
     </row>
     <row r="6384" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6384" s="5" t="s">
-        <v>11656</v>
-      </c>
-      <c r="B6384" s="5" t="s">
-        <v>11668</v>
+        <v>11638</v>
       </c>
     </row>
     <row r="6385" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6385" s="5" t="s">
-        <v>11657</v>
-      </c>
-      <c r="B6385" s="5" t="s">
-        <v>11669</v>
+        <v>11639</v>
       </c>
     </row>
     <row r="6386" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6386" s="5" t="s">
-        <v>11658</v>
-      </c>
-      <c r="B6386" s="5" t="s">
-        <v>11670</v>
+        <v>11640</v>
       </c>
     </row>
     <row r="6387" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6387" s="5" t="s">
-        <v>11659</v>
+        <v>11647</v>
       </c>
       <c r="B6387" s="5" t="s">
-        <v>11671</v>
+        <v>11648</v>
       </c>
     </row>
     <row r="6388" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6388" s="5" t="s">
-        <v>11660</v>
+        <v>11649</v>
       </c>
       <c r="B6388" s="5" t="s">
-        <v>11672</v>
+        <v>11661</v>
       </c>
     </row>
     <row r="6389" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6389" s="5" t="s">
-        <v>11673</v>
+        <v>11650</v>
       </c>
       <c r="B6389" s="5" t="s">
-        <v>11674</v>
+        <v>11662</v>
       </c>
     </row>
     <row r="6390" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6390" s="5" t="s">
-        <v>11675</v>
+        <v>11651</v>
       </c>
       <c r="B6390" s="5" t="s">
-        <v>11685</v>
+        <v>11663</v>
       </c>
     </row>
     <row r="6391" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6391" s="5" t="s">
-        <v>11676</v>
+        <v>11652</v>
       </c>
       <c r="B6391" s="5" t="s">
-        <v>11686</v>
+        <v>11664</v>
       </c>
     </row>
     <row r="6392" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6392" s="5" t="s">
-        <v>11677</v>
+        <v>11653</v>
       </c>
       <c r="B6392" s="5" t="s">
-        <v>11687</v>
+        <v>11665</v>
       </c>
     </row>
     <row r="6393" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6393" s="5" t="s">
-        <v>11678</v>
+        <v>11654</v>
       </c>
       <c r="B6393" s="5" t="s">
-        <v>11688</v>
+        <v>11666</v>
       </c>
     </row>
     <row r="6394" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6394" s="5" t="s">
-        <v>11679</v>
+        <v>11655</v>
       </c>
       <c r="B6394" s="5" t="s">
-        <v>11689</v>
+        <v>11667</v>
       </c>
     </row>
     <row r="6395" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6395" s="5" t="s">
-        <v>11680</v>
+        <v>11656</v>
       </c>
       <c r="B6395" s="5" t="s">
-        <v>11690</v>
+        <v>11668</v>
       </c>
     </row>
     <row r="6396" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6396" s="5" t="s">
-        <v>11681</v>
+        <v>11657</v>
       </c>
       <c r="B6396" s="5" t="s">
-        <v>11691</v>
+        <v>11669</v>
       </c>
     </row>
     <row r="6397" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6397" s="5" t="s">
-        <v>11682</v>
+        <v>11658</v>
       </c>
       <c r="B6397" s="5" t="s">
-        <v>11692</v>
+        <v>11670</v>
       </c>
     </row>
     <row r="6398" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6398" s="5" t="s">
-        <v>11683</v>
+        <v>11659</v>
       </c>
       <c r="B6398" s="5" t="s">
-        <v>11693</v>
+        <v>11671</v>
       </c>
     </row>
     <row r="6399" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6399" s="5" t="s">
-        <v>11684</v>
+        <v>11660</v>
       </c>
       <c r="B6399" s="5" t="s">
-        <v>11694</v>
+        <v>11672</v>
       </c>
     </row>
     <row r="6400" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6400" s="5" t="s">
-        <v>11695</v>
+        <v>11673</v>
       </c>
       <c r="B6400" s="5" t="s">
-        <v>11696</v>
+        <v>11674</v>
       </c>
     </row>
     <row r="6401" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6401" s="5" t="s">
-        <v>11697</v>
+        <v>11675</v>
       </c>
       <c r="B6401" s="5" t="s">
-        <v>11707</v>
+        <v>11685</v>
       </c>
     </row>
     <row r="6402" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6402" s="5" t="s">
-        <v>11698</v>
+        <v>11676</v>
       </c>
       <c r="B6402" s="5" t="s">
-        <v>11708</v>
+        <v>11686</v>
       </c>
     </row>
     <row r="6403" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6403" s="5" t="s">
-        <v>11699</v>
+        <v>11677</v>
       </c>
       <c r="B6403" s="5" t="s">
-        <v>11709</v>
+        <v>11687</v>
       </c>
     </row>
     <row r="6404" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6404" s="5" t="s">
-        <v>11700</v>
+        <v>11678</v>
       </c>
       <c r="B6404" s="5" t="s">
-        <v>11710</v>
+        <v>11688</v>
       </c>
     </row>
     <row r="6405" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6405" s="5" t="s">
-        <v>11701</v>
+        <v>11679</v>
       </c>
       <c r="B6405" s="5" t="s">
-        <v>11711</v>
+        <v>11689</v>
       </c>
     </row>
     <row r="6406" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6406" s="5" t="s">
-        <v>11702</v>
+        <v>11680</v>
       </c>
       <c r="B6406" s="5" t="s">
-        <v>11708</v>
+        <v>11690</v>
       </c>
     </row>
     <row r="6407" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6407" s="5" t="s">
-        <v>11703</v>
+        <v>11681</v>
       </c>
       <c r="B6407" s="5" t="s">
-        <v>11712</v>
+        <v>11691</v>
       </c>
     </row>
     <row r="6408" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6408" s="5" t="s">
-        <v>11704</v>
+        <v>11682</v>
       </c>
       <c r="B6408" s="5" t="s">
-        <v>11713</v>
+        <v>11692</v>
       </c>
     </row>
     <row r="6409" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6409" s="5" t="s">
-        <v>11705</v>
+        <v>11683</v>
       </c>
       <c r="B6409" s="5" t="s">
-        <v>11714</v>
+        <v>11693</v>
       </c>
     </row>
     <row r="6410" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6410" s="5" t="s">
-        <v>11706</v>
+        <v>11684</v>
       </c>
       <c r="B6410" s="5" t="s">
-        <v>11715</v>
+        <v>11694</v>
       </c>
     </row>
     <row r="6411" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6411" s="5" t="s">
-        <v>11716</v>
+        <v>11695</v>
       </c>
       <c r="B6411" s="5" t="s">
-        <v>11717</v>
+        <v>11696</v>
       </c>
     </row>
     <row r="6412" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6412" s="5" t="s">
-        <v>11718</v>
+        <v>11697</v>
       </c>
       <c r="B6412" s="5" t="s">
-        <v>11722</v>
+        <v>11707</v>
       </c>
     </row>
     <row r="6413" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6413" s="5" t="s">
-        <v>11719</v>
+        <v>11698</v>
       </c>
       <c r="B6413" s="5" t="s">
-        <v>11723</v>
+        <v>11708</v>
       </c>
     </row>
     <row r="6414" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6414" s="5" t="s">
-        <v>11720</v>
+        <v>11699</v>
       </c>
       <c r="B6414" s="5" t="s">
-        <v>11724</v>
+        <v>11709</v>
       </c>
     </row>
     <row r="6415" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6415" s="5" t="s">
-        <v>11721</v>
+        <v>11700</v>
       </c>
       <c r="B6415" s="5" t="s">
-        <v>11725</v>
+        <v>11710</v>
       </c>
     </row>
     <row r="6416" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6416" s="5" t="s">
-        <v>11726</v>
+        <v>11701</v>
       </c>
       <c r="B6416" s="5" t="s">
-        <v>11727</v>
+        <v>11711</v>
       </c>
     </row>
     <row r="6417" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6417" s="5" t="s">
-        <v>11728</v>
+        <v>11702</v>
       </c>
       <c r="B6417" s="5" t="s">
-        <v>11738</v>
+        <v>11708</v>
       </c>
     </row>
     <row r="6418" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6418" s="5" t="s">
-        <v>11729</v>
+        <v>11703</v>
       </c>
       <c r="B6418" s="5" t="s">
-        <v>11739</v>
+        <v>11712</v>
       </c>
     </row>
     <row r="6419" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6419" s="5" t="s">
-        <v>11730</v>
+        <v>11704</v>
       </c>
       <c r="B6419" s="5" t="s">
-        <v>11740</v>
+        <v>11713</v>
       </c>
     </row>
     <row r="6420" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6420" s="5" t="s">
-        <v>11731</v>
+        <v>11705</v>
       </c>
       <c r="B6420" s="5" t="s">
-        <v>11741</v>
+        <v>11714</v>
       </c>
     </row>
     <row r="6421" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6421" s="5" t="s">
+        <v>11706</v>
+      </c>
+      <c r="B6421" s="5" t="s">
+        <v>11715</v>
+      </c>
+    </row>
+    <row r="6422" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6422" s="15" t="s">
+        <v>11716</v>
+      </c>
+      <c r="B6422" s="5" t="s">
+        <v>11717</v>
+      </c>
+    </row>
+    <row r="6423" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6423" s="15" t="s">
+        <v>11718</v>
+      </c>
+      <c r="B6423" s="5" t="s">
+        <v>11722</v>
+      </c>
+    </row>
+    <row r="6424" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6424" s="15" t="s">
+        <v>11719</v>
+      </c>
+      <c r="B6424" s="5" t="s">
+        <v>11723</v>
+      </c>
+    </row>
+    <row r="6425" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6425" s="15" t="s">
+        <v>11720</v>
+      </c>
+      <c r="B6425" s="5" t="s">
+        <v>11724</v>
+      </c>
+    </row>
+    <row r="6426" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6426" s="15" t="s">
+        <v>11721</v>
+      </c>
+      <c r="B6426" s="5" t="s">
+        <v>11725</v>
+      </c>
+    </row>
+    <row r="6427" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6427" s="15" t="s">
+        <v>11726</v>
+      </c>
+      <c r="B6427" s="5" t="s">
+        <v>11727</v>
+      </c>
+    </row>
+    <row r="6428" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6428" s="15" t="s">
+        <v>11728</v>
+      </c>
+      <c r="B6428" s="5" t="s">
+        <v>11738</v>
+      </c>
+    </row>
+    <row r="6429" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6429" s="15" t="s">
+        <v>11729</v>
+      </c>
+      <c r="B6429" s="5" t="s">
+        <v>11739</v>
+      </c>
+    </row>
+    <row r="6430" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6430" s="15" t="s">
+        <v>11730</v>
+      </c>
+      <c r="B6430" s="5" t="s">
+        <v>11740</v>
+      </c>
+    </row>
+    <row r="6431" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6431" s="15" t="s">
+        <v>11731</v>
+      </c>
+      <c r="B6431" s="5" t="s">
+        <v>11741</v>
+      </c>
+    </row>
+    <row r="6432" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6432" s="15" t="s">
         <v>11732</v>
       </c>
-      <c r="B6421" s="5" t="s">
+      <c r="B6432" s="5" t="s">
         <v>11742</v>
       </c>
     </row>
-    <row r="6422" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6422" s="5" t="s">
+    <row r="6433" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6433" s="15" t="s">
         <v>11733</v>
       </c>
-      <c r="B6422" s="5" t="s">
+      <c r="B6433" s="5" t="s">
         <v>11743</v>
       </c>
     </row>
-    <row r="6423" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6423" s="5" t="s">
+    <row r="6434" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6434" s="15" t="s">
         <v>11734</v>
       </c>
-      <c r="B6423" s="5" t="s">
+      <c r="B6434" s="5" t="s">
         <v>11744</v>
       </c>
     </row>
-    <row r="6424" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6424" s="5" t="s">
+    <row r="6435" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6435" s="15" t="s">
         <v>11735</v>
       </c>
-      <c r="B6424" s="5" t="s">
+      <c r="B6435" s="5" t="s">
         <v>11745</v>
       </c>
     </row>
-    <row r="6425" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6425" s="5" t="s">
+    <row r="6436" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6436" s="15" t="s">
         <v>11736</v>
       </c>
-      <c r="B6425" s="5" t="s">
+      <c r="B6436" s="5" t="s">
         <v>11746</v>
       </c>
     </row>
-    <row r="6426" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6426" s="5" t="s">
+    <row r="6437" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6437" s="15" t="s">
         <v>11737</v>
       </c>
-      <c r="B6426" s="5" t="s">
+      <c r="B6437" s="5" t="s">
         <v>11747</v>
       </c>
     </row>
-    <row r="6427" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6427" s="5" t="s">
+    <row r="6438" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6438" s="15" t="s">
         <v>11748</v>
       </c>
-      <c r="B6427" s="5" t="s">
+      <c r="B6438" s="5" t="s">
         <v>11749</v>
       </c>
     </row>
-    <row r="6428" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6428" s="5" t="s">
+    <row r="6439" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6439" s="15" t="s">
         <v>11750</v>
       </c>
-      <c r="B6428" s="5" t="s">
+      <c r="B6439" s="5" t="s">
         <v>11754</v>
       </c>
     </row>
-    <row r="6429" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6429" s="5" t="s">
+    <row r="6440" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6440" s="15" t="s">
         <v>11751</v>
       </c>
-      <c r="B6429" s="5" t="s">
+      <c r="B6440" s="5" t="s">
         <v>11755</v>
       </c>
     </row>
-    <row r="6430" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6430" s="5" t="s">
+    <row r="6441" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6441" s="15" t="s">
         <v>11752</v>
       </c>
-      <c r="B6430" s="5" t="s">
+      <c r="B6441" s="5" t="s">
         <v>11756</v>
       </c>
     </row>
-    <row r="6431" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6431" s="5" t="s">
+    <row r="6442" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6442" s="15" t="s">
         <v>11753</v>
       </c>
-      <c r="B6431" s="5" t="s">
+      <c r="B6442" s="5" t="s">
         <v>11757</v>
-      </c>
-    </row>
-    <row r="6432" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6432" s="5" t="s">
-        <v>11758</v>
-      </c>
-      <c r="B6432" s="5" t="s">
-        <v>11759</v>
-      </c>
-    </row>
-    <row r="6433" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6433" s="5" t="s">
-        <v>11760</v>
-      </c>
-      <c r="B6433" s="5" t="s">
-        <v>11763</v>
-      </c>
-    </row>
-    <row r="6434" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6434" s="5" t="s">
-        <v>11761</v>
-      </c>
-      <c r="B6434" s="5" t="s">
-        <v>11764</v>
-      </c>
-    </row>
-    <row r="6435" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6435" s="5" t="s">
-        <v>11762</v>
-      </c>
-      <c r="B6435" s="5" t="s">
-        <v>11765</v>
-      </c>
-    </row>
-    <row r="6436" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6436" s="5" t="s">
-        <v>11766</v>
-      </c>
-      <c r="B6436" s="5" t="s">
-        <v>11767</v>
-      </c>
-    </row>
-    <row r="6437" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6437" s="5" t="s">
-        <v>11768</v>
-      </c>
-      <c r="B6437" s="5" t="s">
-        <v>11776</v>
-      </c>
-    </row>
-    <row r="6438" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6438" s="5" t="s">
-        <v>11769</v>
-      </c>
-      <c r="B6438" s="5" t="s">
-        <v>11777</v>
-      </c>
-    </row>
-    <row r="6439" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6439" s="5" t="s">
-        <v>11770</v>
-      </c>
-      <c r="B6439" s="5" t="s">
-        <v>11778</v>
-      </c>
-    </row>
-    <row r="6440" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6440" s="5" t="s">
-        <v>11771</v>
-      </c>
-      <c r="B6440" s="5" t="s">
-        <v>11779</v>
-      </c>
-    </row>
-    <row r="6441" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6441" s="5" t="s">
-        <v>11772</v>
-      </c>
-      <c r="B6441" s="5" t="s">
-        <v>11780</v>
-      </c>
-    </row>
-    <row r="6442" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6442" s="5" t="s">
-        <v>11773</v>
-      </c>
-      <c r="B6442" s="5" t="s">
-        <v>11781</v>
       </c>
     </row>
     <row r="6443" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6443" s="5" t="s">
-        <v>11774</v>
+        <v>11758</v>
       </c>
       <c r="B6443" s="5" t="s">
-        <v>11782</v>
+        <v>11759</v>
       </c>
     </row>
     <row r="6444" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6444" s="5" t="s">
-        <v>11775</v>
+        <v>11760</v>
       </c>
       <c r="B6444" s="5" t="s">
-        <v>11783</v>
+        <v>11763</v>
       </c>
     </row>
     <row r="6445" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6445" s="5" t="s">
-        <v>11784</v>
+        <v>11761</v>
       </c>
       <c r="B6445" s="5" t="s">
-        <v>11785</v>
+        <v>11764</v>
       </c>
     </row>
     <row r="6446" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6446" s="5" t="s">
-        <v>11786</v>
+        <v>11762</v>
       </c>
       <c r="B6446" s="5" t="s">
-        <v>11790</v>
+        <v>11765</v>
       </c>
     </row>
     <row r="6447" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6447" s="5" t="s">
-        <v>11787</v>
+        <v>11766</v>
       </c>
       <c r="B6447" s="5" t="s">
-        <v>11791</v>
+        <v>11767</v>
       </c>
     </row>
     <row r="6448" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6448" s="5" t="s">
-        <v>11788</v>
+        <v>11768</v>
       </c>
       <c r="B6448" s="5" t="s">
-        <v>11792</v>
+        <v>11776</v>
       </c>
     </row>
     <row r="6449" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6449" s="5" t="s">
-        <v>11789</v>
+        <v>11769</v>
       </c>
       <c r="B6449" s="5" t="s">
-        <v>11793</v>
+        <v>11777</v>
       </c>
     </row>
     <row r="6450" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6450" s="5" t="s">
-        <v>11794</v>
+        <v>11770</v>
       </c>
       <c r="B6450" s="5" t="s">
-        <v>11795</v>
+        <v>11778</v>
       </c>
     </row>
     <row r="6451" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6451" s="5" t="s">
-        <v>11796</v>
+        <v>11771</v>
       </c>
       <c r="B6451" s="5" t="s">
-        <v>11805</v>
+        <v>11779</v>
       </c>
     </row>
     <row r="6452" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6452" s="5" t="s">
-        <v>11797</v>
+        <v>11772</v>
       </c>
       <c r="B6452" s="5" t="s">
-        <v>11805</v>
+        <v>11780</v>
       </c>
     </row>
     <row r="6453" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6453" s="5" t="s">
-        <v>11798</v>
+        <v>11773</v>
       </c>
       <c r="B6453" s="5" t="s">
-        <v>11805</v>
+        <v>11781</v>
       </c>
     </row>
     <row r="6454" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6454" s="5" t="s">
-        <v>11799</v>
+        <v>11774</v>
       </c>
       <c r="B6454" s="5" t="s">
-        <v>11806</v>
+        <v>11782</v>
       </c>
     </row>
     <row r="6455" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6455" s="5" t="s">
-        <v>11800</v>
+        <v>11775</v>
       </c>
       <c r="B6455" s="5" t="s">
-        <v>11805</v>
+        <v>11783</v>
       </c>
     </row>
     <row r="6456" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6456" s="5" t="s">
-        <v>11801</v>
+        <v>11784</v>
       </c>
       <c r="B6456" s="5" t="s">
-        <v>11807</v>
+        <v>11785</v>
       </c>
     </row>
     <row r="6457" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6457" s="5" t="s">
-        <v>11802</v>
+        <v>11786</v>
       </c>
       <c r="B6457" s="5" t="s">
-        <v>11808</v>
+        <v>11790</v>
       </c>
     </row>
     <row r="6458" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6458" s="5" t="s">
-        <v>11803</v>
+        <v>11787</v>
       </c>
       <c r="B6458" s="5" t="s">
-        <v>11809</v>
+        <v>11791</v>
       </c>
     </row>
     <row r="6459" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6459" s="5" t="s">
-        <v>11804</v>
+        <v>11788</v>
       </c>
       <c r="B6459" s="5" t="s">
-        <v>11810</v>
+        <v>11792</v>
       </c>
     </row>
     <row r="6460" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6460" s="5" t="s">
-        <v>11811</v>
+        <v>11789</v>
       </c>
       <c r="B6460" s="5" t="s">
-        <v>11812</v>
+        <v>11793</v>
       </c>
     </row>
     <row r="6461" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6461" s="5" t="s">
-        <v>11813</v>
+        <v>11794</v>
       </c>
       <c r="B6461" s="5" t="s">
-        <v>11823</v>
+        <v>11795</v>
       </c>
     </row>
     <row r="6462" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6462" s="5" t="s">
-        <v>11814</v>
+        <v>11796</v>
       </c>
       <c r="B6462" s="5" t="s">
-        <v>11824</v>
+        <v>11805</v>
       </c>
     </row>
     <row r="6463" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6463" s="5" t="s">
-        <v>11815</v>
+        <v>11797</v>
       </c>
       <c r="B6463" s="5" t="s">
-        <v>11825</v>
+        <v>11805</v>
       </c>
     </row>
     <row r="6464" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6464" s="5" t="s">
-        <v>11816</v>
+        <v>11798</v>
       </c>
       <c r="B6464" s="5" t="s">
-        <v>11826</v>
+        <v>11805</v>
       </c>
     </row>
     <row r="6465" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6465" s="5" t="s">
-        <v>11817</v>
+        <v>11799</v>
       </c>
       <c r="B6465" s="5" t="s">
-        <v>11827</v>
+        <v>11806</v>
       </c>
     </row>
     <row r="6466" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6466" s="5" t="s">
-        <v>11818</v>
+        <v>11800</v>
       </c>
       <c r="B6466" s="5" t="s">
-        <v>11828</v>
+        <v>11805</v>
       </c>
     </row>
     <row r="6467" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6467" s="5" t="s">
-        <v>11819</v>
+        <v>11801</v>
       </c>
       <c r="B6467" s="5" t="s">
-        <v>11829</v>
+        <v>11807</v>
       </c>
     </row>
     <row r="6468" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6468" s="5" t="s">
-        <v>11820</v>
+        <v>11802</v>
       </c>
       <c r="B6468" s="5" t="s">
-        <v>11830</v>
+        <v>11808</v>
       </c>
     </row>
     <row r="6469" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6469" s="5" t="s">
-        <v>11814</v>
+        <v>11803</v>
       </c>
       <c r="B6469" s="5" t="s">
-        <v>11824</v>
+        <v>11809</v>
       </c>
     </row>
     <row r="6470" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6470" s="5" t="s">
-        <v>11821</v>
+        <v>11804</v>
       </c>
       <c r="B6470" s="5" t="s">
-        <v>11831</v>
+        <v>11810</v>
       </c>
     </row>
     <row r="6471" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6471" s="5" t="s">
-        <v>11822</v>
+        <v>11811</v>
       </c>
       <c r="B6471" s="5" t="s">
-        <v>11832</v>
+        <v>11812</v>
       </c>
     </row>
     <row r="6472" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6472" s="5" t="s">
-        <v>11833</v>
+        <v>11813</v>
+      </c>
+      <c r="B6472" s="5" t="s">
+        <v>11823</v>
       </c>
     </row>
     <row r="6473" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6473" s="5" t="s">
-        <v>11834</v>
+        <v>11814</v>
       </c>
       <c r="B6473" s="5" t="s">
-        <v>11835</v>
+        <v>11824</v>
       </c>
     </row>
     <row r="6474" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6474" s="5" t="s">
-        <v>11836</v>
+        <v>11815</v>
       </c>
       <c r="B6474" s="5" t="s">
-        <v>11848</v>
+        <v>11825</v>
       </c>
     </row>
     <row r="6475" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6475" s="5" t="s">
-        <v>11837</v>
+        <v>11816</v>
       </c>
       <c r="B6475" s="5" t="s">
-        <v>11849</v>
+        <v>11826</v>
       </c>
     </row>
     <row r="6476" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6476" s="5" t="s">
-        <v>11838</v>
+        <v>11817</v>
       </c>
       <c r="B6476" s="5" t="s">
-        <v>11850</v>
+        <v>11827</v>
       </c>
     </row>
     <row r="6477" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6477" s="5" t="s">
-        <v>11839</v>
+        <v>11818</v>
       </c>
       <c r="B6477" s="5" t="s">
-        <v>11851</v>
+        <v>11828</v>
       </c>
     </row>
     <row r="6478" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6478" s="5" t="s">
-        <v>11840</v>
+        <v>11819</v>
       </c>
       <c r="B6478" s="5" t="s">
-        <v>11852</v>
+        <v>11829</v>
       </c>
     </row>
     <row r="6479" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6479" s="5" t="s">
-        <v>11841</v>
+        <v>11820</v>
       </c>
       <c r="B6479" s="5" t="s">
-        <v>11853</v>
+        <v>11830</v>
       </c>
     </row>
     <row r="6480" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6480" s="5" t="s">
-        <v>11842</v>
+        <v>11814</v>
       </c>
       <c r="B6480" s="5" t="s">
-        <v>11854</v>
+        <v>11824</v>
       </c>
     </row>
     <row r="6481" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6481" s="5" t="s">
-        <v>11843</v>
+        <v>11821</v>
       </c>
       <c r="B6481" s="5" t="s">
-        <v>11855</v>
+        <v>11831</v>
       </c>
     </row>
     <row r="6482" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6482" s="5" t="s">
-        <v>11844</v>
+        <v>11822</v>
       </c>
       <c r="B6482" s="5" t="s">
-        <v>11856</v>
+        <v>11832</v>
       </c>
     </row>
     <row r="6483" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6483" s="5" t="s">
-        <v>11845</v>
-      </c>
-      <c r="B6483" s="5" t="s">
-        <v>11857</v>
+        <v>11833</v>
       </c>
     </row>
     <row r="6484" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6484" s="5" t="s">
-        <v>11846</v>
+        <v>11834</v>
       </c>
       <c r="B6484" s="5" t="s">
-        <v>11858</v>
+        <v>11835</v>
       </c>
     </row>
     <row r="6485" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6485" s="5" t="s">
-        <v>11847</v>
+        <v>11836</v>
       </c>
       <c r="B6485" s="5" t="s">
-        <v>11859</v>
+        <v>11848</v>
       </c>
     </row>
     <row r="6486" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6486" s="5" t="s">
-        <v>11860</v>
+        <v>11837</v>
       </c>
       <c r="B6486" s="5" t="s">
-        <v>11861</v>
+        <v>11849</v>
       </c>
     </row>
     <row r="6487" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6487" s="5" t="s">
-        <v>11862</v>
+        <v>11838</v>
       </c>
       <c r="B6487" s="5" t="s">
-        <v>11866</v>
+        <v>11850</v>
       </c>
     </row>
     <row r="6488" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6488" s="5" t="s">
-        <v>11863</v>
+        <v>11839</v>
       </c>
       <c r="B6488" s="5" t="s">
-        <v>11867</v>
+        <v>11851</v>
       </c>
     </row>
     <row r="6489" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6489" s="5" t="s">
-        <v>11864</v>
+        <v>11840</v>
       </c>
       <c r="B6489" s="5" t="s">
-        <v>11868</v>
+        <v>11852</v>
       </c>
     </row>
     <row r="6490" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6490" s="5" t="s">
-        <v>11865</v>
+        <v>11841</v>
       </c>
       <c r="B6490" s="5" t="s">
-        <v>11869</v>
+        <v>11853</v>
       </c>
     </row>
     <row r="6491" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6491" s="5" t="s">
-        <v>11870</v>
+      <c r="A6491" s="15" t="s">
+        <v>11842</v>
       </c>
       <c r="B6491" s="5" t="s">
-        <v>11887</v>
+        <v>11854</v>
       </c>
     </row>
     <row r="6492" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6492" s="5" t="s">
-        <v>11871</v>
+      <c r="A6492" s="15" t="s">
+        <v>11843</v>
       </c>
       <c r="B6492" s="5" t="s">
-        <v>11886</v>
+        <v>11855</v>
       </c>
     </row>
     <row r="6493" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6493" s="5" t="s">
-        <v>11872</v>
+      <c r="A6493" s="15" t="s">
+        <v>11844</v>
       </c>
       <c r="B6493" s="5" t="s">
-        <v>11888</v>
+        <v>11856</v>
       </c>
     </row>
     <row r="6494" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6494" s="5" t="s">
-        <v>11873</v>
+      <c r="A6494" s="15" t="s">
+        <v>11845</v>
       </c>
       <c r="B6494" s="5" t="s">
-        <v>11889</v>
+        <v>11857</v>
       </c>
     </row>
     <row r="6495" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6495" s="5" t="s">
-        <v>11874</v>
+      <c r="A6495" s="15" t="s">
+        <v>11846</v>
       </c>
       <c r="B6495" s="5" t="s">
-        <v>11890</v>
+        <v>11858</v>
       </c>
     </row>
     <row r="6496" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6496" s="5" t="s">
-        <v>11875</v>
+      <c r="A6496" s="15" t="s">
+        <v>11847</v>
       </c>
       <c r="B6496" s="5" t="s">
-        <v>11887</v>
+        <v>11859</v>
       </c>
     </row>
     <row r="6497" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6497" s="5" t="s">
-        <v>11876</v>
+        <v>11860</v>
       </c>
       <c r="B6497" s="5" t="s">
-        <v>11891</v>
+        <v>11861</v>
       </c>
     </row>
     <row r="6498" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6498" s="5" t="s">
-        <v>11877</v>
+        <v>11862</v>
       </c>
       <c r="B6498" s="5" t="s">
-        <v>11892</v>
+        <v>11866</v>
       </c>
     </row>
     <row r="6499" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6499" s="5" t="s">
-        <v>11878</v>
+        <v>11863</v>
       </c>
       <c r="B6499" s="5" t="s">
-        <v>11893</v>
+        <v>11867</v>
       </c>
     </row>
     <row r="6500" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6500" s="5" t="s">
-        <v>11879</v>
+        <v>11864</v>
       </c>
       <c r="B6500" s="5" t="s">
-        <v>11894</v>
+        <v>11868</v>
       </c>
     </row>
     <row r="6501" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6501" s="5" t="s">
-        <v>11880</v>
+        <v>11865</v>
       </c>
       <c r="B6501" s="5" t="s">
-        <v>11895</v>
+        <v>11869</v>
       </c>
     </row>
     <row r="6502" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6502" s="5" t="s">
-        <v>11881</v>
+        <v>11870</v>
       </c>
       <c r="B6502" s="5" t="s">
-        <v>11896</v>
+        <v>11887</v>
       </c>
     </row>
     <row r="6503" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6503" s="5" t="s">
-        <v>11882</v>
+        <v>11871</v>
       </c>
       <c r="B6503" s="5" t="s">
-        <v>11897</v>
+        <v>11886</v>
       </c>
     </row>
     <row r="6504" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6504" s="5" t="s">
-        <v>11883</v>
+        <v>11872</v>
       </c>
       <c r="B6504" s="5" t="s">
-        <v>11898</v>
+        <v>11888</v>
       </c>
     </row>
     <row r="6505" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6505" s="5" t="s">
-        <v>11884</v>
+        <v>11873</v>
       </c>
       <c r="B6505" s="5" t="s">
-        <v>11899</v>
+        <v>11889</v>
       </c>
     </row>
     <row r="6506" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6506" s="5" t="s">
-        <v>11885</v>
+        <v>11874</v>
       </c>
       <c r="B6506" s="5" t="s">
-        <v>11900</v>
+        <v>11890</v>
       </c>
     </row>
     <row r="6507" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6507" s="5" t="s">
-        <v>11876</v>
+        <v>11875</v>
       </c>
       <c r="B6507" s="5" t="s">
-        <v>11891</v>
+        <v>11887</v>
       </c>
     </row>
     <row r="6508" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6508" s="5" t="s">
-        <v>11901</v>
+        <v>11876</v>
       </c>
       <c r="B6508" s="5" t="s">
-        <v>11902</v>
+        <v>11891</v>
       </c>
     </row>
     <row r="6509" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6509" s="5" t="s">
-        <v>11903</v>
+        <v>11877</v>
       </c>
       <c r="B6509" s="5" t="s">
-        <v>11915</v>
+        <v>11892</v>
       </c>
     </row>
     <row r="6510" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6510" s="5" t="s">
-        <v>11904</v>
+        <v>11878</v>
       </c>
       <c r="B6510" s="5" t="s">
-        <v>11916</v>
+        <v>11893</v>
       </c>
     </row>
     <row r="6511" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6511" s="5" t="s">
-        <v>11905</v>
+        <v>11879</v>
       </c>
       <c r="B6511" s="5" t="s">
-        <v>11917</v>
+        <v>11894</v>
       </c>
     </row>
     <row r="6512" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6512" s="5" t="s">
-        <v>11906</v>
+        <v>11880</v>
       </c>
       <c r="B6512" s="5" t="s">
-        <v>11918</v>
+        <v>11895</v>
       </c>
     </row>
     <row r="6513" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6513" s="5" t="s">
-        <v>11907</v>
+        <v>11881</v>
       </c>
       <c r="B6513" s="5" t="s">
-        <v>11919</v>
+        <v>11896</v>
       </c>
     </row>
     <row r="6514" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6514" s="5" t="s">
-        <v>11908</v>
+        <v>11882</v>
       </c>
       <c r="B6514" s="5" t="s">
-        <v>11920</v>
+        <v>11897</v>
       </c>
     </row>
     <row r="6515" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6515" s="5" t="s">
-        <v>11909</v>
+        <v>11883</v>
       </c>
       <c r="B6515" s="5" t="s">
-        <v>11921</v>
+        <v>11898</v>
       </c>
     </row>
     <row r="6516" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6516" s="5" t="s">
-        <v>11910</v>
+        <v>11884</v>
       </c>
       <c r="B6516" s="5" t="s">
-        <v>11922</v>
+        <v>11899</v>
       </c>
     </row>
     <row r="6517" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6517" s="5" t="s">
-        <v>11911</v>
+        <v>11885</v>
       </c>
       <c r="B6517" s="5" t="s">
-        <v>11923</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="6518" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6518" s="5" t="s">
-        <v>11912</v>
+        <v>11876</v>
       </c>
       <c r="B6518" s="5" t="s">
-        <v>11924</v>
+        <v>11891</v>
       </c>
     </row>
     <row r="6519" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6519" s="5" t="s">
-        <v>11913</v>
+        <v>11901</v>
       </c>
       <c r="B6519" s="5" t="s">
-        <v>11925</v>
+        <v>11902</v>
       </c>
     </row>
     <row r="6520" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6520" s="5" t="s">
-        <v>11914</v>
+        <v>11903</v>
       </c>
       <c r="B6520" s="5" t="s">
-        <v>11926</v>
+        <v>11915</v>
       </c>
     </row>
     <row r="6521" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6521" s="5" t="s">
-        <v>11927</v>
+        <v>11904</v>
       </c>
       <c r="B6521" s="5" t="s">
-        <v>11928</v>
+        <v>11916</v>
       </c>
     </row>
     <row r="6522" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6522" s="5" t="s">
-        <v>11929</v>
+        <v>11905</v>
       </c>
       <c r="B6522" s="5" t="s">
-        <v>11941</v>
+        <v>11917</v>
       </c>
     </row>
     <row r="6523" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6523" s="5" t="s">
-        <v>11930</v>
+        <v>11906</v>
       </c>
       <c r="B6523" s="5" t="s">
-        <v>11942</v>
+        <v>11918</v>
       </c>
     </row>
     <row r="6524" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6524" s="5" t="s">
-        <v>11931</v>
+        <v>11907</v>
       </c>
       <c r="B6524" s="5" t="s">
-        <v>11943</v>
+        <v>11919</v>
       </c>
     </row>
     <row r="6525" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6525" s="5" t="s">
-        <v>11932</v>
+        <v>11908</v>
       </c>
       <c r="B6525" s="5" t="s">
-        <v>11944</v>
+        <v>11920</v>
       </c>
     </row>
     <row r="6526" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6526" s="5" t="s">
-        <v>11933</v>
+        <v>11909</v>
       </c>
       <c r="B6526" s="5" t="s">
-        <v>11945</v>
+        <v>11921</v>
       </c>
     </row>
     <row r="6527" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6527" s="5" t="s">
-        <v>11934</v>
+        <v>11910</v>
       </c>
       <c r="B6527" s="5" t="s">
-        <v>11946</v>
+        <v>11922</v>
       </c>
     </row>
     <row r="6528" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6528" s="5" t="s">
-        <v>11935</v>
+        <v>11911</v>
       </c>
       <c r="B6528" s="5" t="s">
-        <v>11947</v>
+        <v>11923</v>
       </c>
     </row>
     <row r="6529" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6529" s="5" t="s">
-        <v>11936</v>
+        <v>11912</v>
       </c>
       <c r="B6529" s="5" t="s">
-        <v>11948</v>
+        <v>11924</v>
       </c>
     </row>
     <row r="6530" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6530" s="5" t="s">
-        <v>11937</v>
+        <v>11913</v>
       </c>
       <c r="B6530" s="5" t="s">
-        <v>11949</v>
+        <v>11925</v>
       </c>
     </row>
     <row r="6531" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6531" s="5" t="s">
-        <v>11938</v>
+        <v>11914</v>
       </c>
       <c r="B6531" s="5" t="s">
-        <v>11950</v>
+        <v>11926</v>
       </c>
     </row>
     <row r="6532" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6532" s="5" t="s">
-        <v>11939</v>
+        <v>11927</v>
       </c>
       <c r="B6532" s="5" t="s">
-        <v>11951</v>
+        <v>11928</v>
       </c>
     </row>
     <row r="6533" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6533" s="5" t="s">
-        <v>11940</v>
+        <v>11929</v>
       </c>
       <c r="B6533" s="5" t="s">
-        <v>11952</v>
+        <v>11941</v>
       </c>
     </row>
     <row r="6534" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6534" s="5" t="s">
-        <v>11953</v>
+        <v>11930</v>
       </c>
       <c r="B6534" s="5" t="s">
-        <v>11954</v>
+        <v>11942</v>
       </c>
     </row>
     <row r="6535" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6535" s="5" t="s">
-        <v>11955</v>
+        <v>11931</v>
       </c>
       <c r="B6535" s="5" t="s">
-        <v>11967</v>
+        <v>11943</v>
       </c>
     </row>
     <row r="6536" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6536" s="5" t="s">
-        <v>11956</v>
+      <c r="A6536" s="15" t="s">
+        <v>11932</v>
       </c>
       <c r="B6536" s="5" t="s">
-        <v>11968</v>
+        <v>11944</v>
       </c>
     </row>
     <row r="6537" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6537" s="5" t="s">
-        <v>11957</v>
+      <c r="A6537" s="15" t="s">
+        <v>11933</v>
       </c>
       <c r="B6537" s="5" t="s">
-        <v>11969</v>
+        <v>11945</v>
       </c>
     </row>
     <row r="6538" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6538" s="5" t="s">
-        <v>11958</v>
+      <c r="A6538" s="15" t="s">
+        <v>11934</v>
       </c>
       <c r="B6538" s="5" t="s">
-        <v>11970</v>
+        <v>11946</v>
       </c>
     </row>
     <row r="6539" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6539" s="5" t="s">
-        <v>11959</v>
+      <c r="A6539" s="15" t="s">
+        <v>11935</v>
       </c>
       <c r="B6539" s="5" t="s">
-        <v>11971</v>
+        <v>11947</v>
       </c>
     </row>
     <row r="6540" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6540" s="5" t="s">
-        <v>11960</v>
+      <c r="A6540" s="15" t="s">
+        <v>11936</v>
       </c>
       <c r="B6540" s="5" t="s">
-        <v>11972</v>
+        <v>11948</v>
       </c>
     </row>
     <row r="6541" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6541" s="5" t="s">
-        <v>11961</v>
+      <c r="A6541" s="15" t="s">
+        <v>11937</v>
       </c>
       <c r="B6541" s="5" t="s">
-        <v>11973</v>
+        <v>11949</v>
       </c>
     </row>
     <row r="6542" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6542" s="5" t="s">
-        <v>11962</v>
+        <v>11938</v>
       </c>
       <c r="B6542" s="5" t="s">
-        <v>11974</v>
+        <v>11950</v>
       </c>
     </row>
     <row r="6543" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6543" s="5" t="s">
-        <v>11963</v>
+        <v>11939</v>
       </c>
       <c r="B6543" s="5" t="s">
-        <v>11977</v>
+        <v>11951</v>
       </c>
     </row>
     <row r="6544" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6544" s="5" t="s">
-        <v>11964</v>
+        <v>11940</v>
       </c>
       <c r="B6544" s="5" t="s">
-        <v>11978</v>
+        <v>11952</v>
       </c>
     </row>
     <row r="6545" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6545" s="5" t="s">
-        <v>11965</v>
+        <v>11953</v>
       </c>
       <c r="B6545" s="5" t="s">
-        <v>11975</v>
+        <v>11954</v>
       </c>
     </row>
     <row r="6546" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6546" s="5" t="s">
-        <v>11966</v>
+        <v>11955</v>
       </c>
       <c r="B6546" s="5" t="s">
-        <v>11976</v>
+        <v>11967</v>
       </c>
     </row>
     <row r="6547" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6547" s="5" t="s">
-        <v>11979</v>
+        <v>11956</v>
       </c>
       <c r="B6547" s="5" t="s">
-        <v>11993</v>
+        <v>11968</v>
       </c>
     </row>
     <row r="6548" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6548" s="5" t="s">
-        <v>11980</v>
+        <v>11957</v>
       </c>
       <c r="B6548" s="5" t="s">
-        <v>11994</v>
+        <v>11969</v>
       </c>
     </row>
     <row r="6549" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6549" s="5" t="s">
-        <v>11981</v>
+      <c r="A6549" s="15" t="s">
+        <v>11958</v>
       </c>
       <c r="B6549" s="5" t="s">
-        <v>11995</v>
+        <v>11970</v>
       </c>
     </row>
     <row r="6550" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6550" s="5" t="s">
-        <v>11982</v>
+      <c r="A6550" s="15" t="s">
+        <v>11959</v>
       </c>
       <c r="B6550" s="5" t="s">
-        <v>11996</v>
+        <v>11971</v>
       </c>
     </row>
     <row r="6551" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6551" s="5" t="s">
-        <v>11983</v>
+        <v>11960</v>
       </c>
       <c r="B6551" s="5" t="s">
-        <v>11997</v>
+        <v>11972</v>
       </c>
     </row>
     <row r="6552" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6552" s="5" t="s">
-        <v>11984</v>
+      <c r="A6552" s="15" t="s">
+        <v>11961</v>
       </c>
       <c r="B6552" s="5" t="s">
-        <v>11998</v>
+        <v>11973</v>
       </c>
     </row>
     <row r="6553" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6553" s="5" t="s">
-        <v>11985</v>
+        <v>11962</v>
       </c>
       <c r="B6553" s="5" t="s">
-        <v>11999</v>
+        <v>11974</v>
       </c>
     </row>
     <row r="6554" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6554" s="5" t="s">
-        <v>11986</v>
+        <v>11963</v>
       </c>
       <c r="B6554" s="5" t="s">
-        <v>12000</v>
+        <v>11977</v>
       </c>
     </row>
     <row r="6555" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6555" s="5" t="s">
-        <v>11987</v>
+        <v>11964</v>
       </c>
       <c r="B6555" s="5" t="s">
-        <v>12001</v>
+        <v>11978</v>
       </c>
     </row>
     <row r="6556" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6556" s="5" t="s">
-        <v>11988</v>
+        <v>11965</v>
       </c>
       <c r="B6556" s="5" t="s">
-        <v>12002</v>
+        <v>11975</v>
       </c>
     </row>
     <row r="6557" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6557" s="5" t="s">
-        <v>11989</v>
+        <v>11966</v>
       </c>
       <c r="B6557" s="5" t="s">
-        <v>12003</v>
+        <v>11976</v>
       </c>
     </row>
     <row r="6558" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6558" s="5" t="s">
-        <v>11990</v>
+        <v>11979</v>
       </c>
       <c r="B6558" s="5" t="s">
-        <v>12004</v>
+        <v>11993</v>
       </c>
     </row>
     <row r="6559" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6559" s="5" t="s">
-        <v>11991</v>
+        <v>11980</v>
       </c>
       <c r="B6559" s="5" t="s">
-        <v>12005</v>
+        <v>11994</v>
       </c>
     </row>
     <row r="6560" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6560" s="5" t="s">
-        <v>11992</v>
+        <v>11981</v>
       </c>
       <c r="B6560" s="5" t="s">
-        <v>12006</v>
+        <v>11995</v>
       </c>
     </row>
     <row r="6561" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6561" s="5" t="s">
-        <v>12007</v>
+        <v>11982</v>
       </c>
       <c r="B6561" s="5" t="s">
-        <v>12008</v>
+        <v>11996</v>
       </c>
     </row>
     <row r="6562" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6562" s="5" t="s">
-        <v>12009</v>
+        <v>11983</v>
       </c>
       <c r="B6562" s="5" t="s">
-        <v>12012</v>
+        <v>11997</v>
       </c>
     </row>
     <row r="6563" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6563" s="5" t="s">
-        <v>1695</v>
+        <v>11984</v>
       </c>
       <c r="B6563" s="5" t="s">
-        <v>12013</v>
+        <v>11998</v>
       </c>
     </row>
     <row r="6564" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6564" s="5" t="s">
-        <v>12010</v>
+        <v>11985</v>
       </c>
       <c r="B6564" s="5" t="s">
-        <v>12014</v>
+        <v>11999</v>
       </c>
     </row>
     <row r="6565" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6565" s="5" t="s">
-        <v>12011</v>
+        <v>11986</v>
       </c>
       <c r="B6565" s="5" t="s">
-        <v>12015</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="6566" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6566" s="5" t="s">
-        <v>12016</v>
+        <v>11987</v>
+      </c>
+      <c r="B6566" s="5" t="s">
+        <v>12001</v>
       </c>
     </row>
     <row r="6567" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6567" s="5" t="s">
-        <v>12017</v>
+        <v>11988</v>
+      </c>
+      <c r="B6567" s="5" t="s">
+        <v>12002</v>
       </c>
     </row>
     <row r="6568" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6568" s="5" t="s">
-        <v>12018</v>
+        <v>11989</v>
       </c>
       <c r="B6568" s="5" t="s">
-        <v>12019</v>
+        <v>12003</v>
       </c>
     </row>
     <row r="6569" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6569" s="5" t="s">
-        <v>12020</v>
+        <v>11990</v>
       </c>
       <c r="B6569" s="5" t="s">
-        <v>12027</v>
+        <v>12004</v>
       </c>
     </row>
     <row r="6570" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6570" s="5" t="s">
-        <v>12021</v>
+        <v>11991</v>
       </c>
       <c r="B6570" s="5" t="s">
-        <v>12028</v>
+        <v>12005</v>
       </c>
     </row>
     <row r="6571" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6571" s="5" t="s">
-        <v>12022</v>
+        <v>11992</v>
       </c>
       <c r="B6571" s="5" t="s">
-        <v>12028</v>
+        <v>12006</v>
       </c>
     </row>
     <row r="6572" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6572" s="5" t="s">
-        <v>12023</v>
+        <v>12007</v>
       </c>
       <c r="B6572" s="5" t="s">
-        <v>12029</v>
+        <v>12008</v>
       </c>
     </row>
     <row r="6573" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6573" s="5" t="s">
-        <v>12024</v>
+        <v>12009</v>
       </c>
       <c r="B6573" s="5" t="s">
-        <v>12030</v>
+        <v>12012</v>
       </c>
     </row>
     <row r="6574" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6574" s="5" t="s">
-        <v>12025</v>
+        <v>1695</v>
       </c>
       <c r="B6574" s="5" t="s">
-        <v>12031</v>
+        <v>12013</v>
       </c>
     </row>
     <row r="6575" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6575" s="5" t="s">
-        <v>12026</v>
+        <v>12010</v>
       </c>
       <c r="B6575" s="5" t="s">
-        <v>12032</v>
+        <v>12014</v>
       </c>
     </row>
     <row r="6576" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6576" s="5" t="s">
-        <v>12033</v>
+        <v>12011</v>
+      </c>
+      <c r="B6576" s="5" t="s">
+        <v>12015</v>
       </c>
     </row>
     <row r="6577" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6577" s="5" t="s">
-        <v>12034</v>
-      </c>
-      <c r="B6577" s="5" t="s">
-        <v>12035</v>
+        <v>12016</v>
       </c>
     </row>
     <row r="6578" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6578" s="5" t="s">
-        <v>12036</v>
-      </c>
-      <c r="B6578" s="5" t="s">
-        <v>12047</v>
+        <v>12017</v>
       </c>
     </row>
     <row r="6579" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6579" s="5" t="s">
-        <v>12037</v>
+        <v>12018</v>
       </c>
       <c r="B6579" s="5" t="s">
-        <v>12048</v>
+        <v>12019</v>
       </c>
     </row>
     <row r="6580" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6580" s="5" t="s">
-        <v>12038</v>
+        <v>12020</v>
       </c>
       <c r="B6580" s="5" t="s">
-        <v>12049</v>
+        <v>12027</v>
       </c>
     </row>
     <row r="6581" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6581" s="5" t="s">
-        <v>12039</v>
+        <v>12021</v>
       </c>
       <c r="B6581" s="5" t="s">
-        <v>12050</v>
+        <v>12028</v>
       </c>
     </row>
     <row r="6582" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6582" s="5" t="s">
-        <v>12040</v>
+        <v>12022</v>
       </c>
       <c r="B6582" s="5" t="s">
-        <v>12051</v>
+        <v>12028</v>
       </c>
     </row>
     <row r="6583" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6583" s="5" t="s">
-        <v>12041</v>
+        <v>12023</v>
       </c>
       <c r="B6583" s="5" t="s">
-        <v>12052</v>
+        <v>12029</v>
       </c>
     </row>
     <row r="6584" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6584" s="5" t="s">
-        <v>12042</v>
+        <v>12024</v>
       </c>
       <c r="B6584" s="5" t="s">
-        <v>12053</v>
+        <v>12030</v>
       </c>
     </row>
     <row r="6585" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6585" s="5" t="s">
-        <v>12043</v>
+        <v>12025</v>
       </c>
       <c r="B6585" s="5" t="s">
-        <v>12054</v>
+        <v>12031</v>
       </c>
     </row>
     <row r="6586" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6586" s="5" t="s">
-        <v>12044</v>
+        <v>12026</v>
       </c>
       <c r="B6586" s="5" t="s">
-        <v>12055</v>
+        <v>12032</v>
       </c>
     </row>
     <row r="6587" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6587" s="5" t="s">
-        <v>12045</v>
-      </c>
-      <c r="B6587" s="5" t="s">
-        <v>12056</v>
+        <v>12033</v>
       </c>
     </row>
     <row r="6588" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6588" s="5" t="s">
-        <v>12046</v>
+        <v>12034</v>
       </c>
       <c r="B6588" s="5" t="s">
-        <v>12057</v>
+        <v>12035</v>
       </c>
     </row>
     <row r="6589" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6589" s="5" t="s">
-        <v>12058</v>
+        <v>12036</v>
       </c>
       <c r="B6589" s="5" t="s">
-        <v>12059</v>
+        <v>12047</v>
       </c>
     </row>
     <row r="6590" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6590" s="5" t="s">
-        <v>12060</v>
+        <v>12037</v>
       </c>
       <c r="B6590" s="5" t="s">
-        <v>12059</v>
+        <v>12048</v>
       </c>
     </row>
     <row r="6591" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6591" s="5" t="s">
-        <v>12061</v>
+        <v>12038</v>
       </c>
       <c r="B6591" s="5" t="s">
-        <v>12065</v>
+        <v>12049</v>
       </c>
     </row>
     <row r="6592" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6592" s="5" t="s">
-        <v>12062</v>
+        <v>12039</v>
       </c>
       <c r="B6592" s="5" t="s">
-        <v>12066</v>
+        <v>12050</v>
       </c>
     </row>
     <row r="6593" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6593" s="5" t="s">
-        <v>12063</v>
+        <v>12040</v>
       </c>
       <c r="B6593" s="5" t="s">
-        <v>12067</v>
+        <v>12051</v>
       </c>
     </row>
     <row r="6594" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6594" s="5" t="s">
-        <v>12064</v>
+        <v>12041</v>
       </c>
       <c r="B6594" s="5" t="s">
-        <v>12068</v>
+        <v>12052</v>
       </c>
     </row>
     <row r="6595" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6595" s="5" t="s">
-        <v>12069</v>
+        <v>12042</v>
       </c>
       <c r="B6595" s="5" t="s">
-        <v>12070</v>
+        <v>12053</v>
       </c>
     </row>
     <row r="6596" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6596" s="5" t="s">
-        <v>12071</v>
+      <c r="A6596" s="15" t="s">
+        <v>12043</v>
       </c>
       <c r="B6596" s="5" t="s">
-        <v>12079</v>
+        <v>12054</v>
       </c>
     </row>
     <row r="6597" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6597" s="5" t="s">
-        <v>12072</v>
+        <v>12044</v>
       </c>
       <c r="B6597" s="5" t="s">
-        <v>12080</v>
+        <v>12055</v>
       </c>
     </row>
     <row r="6598" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6598" s="5" t="s">
-        <v>12073</v>
+        <v>12045</v>
       </c>
       <c r="B6598" s="5" t="s">
-        <v>12081</v>
+        <v>12056</v>
       </c>
     </row>
     <row r="6599" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6599" s="5" t="s">
-        <v>12074</v>
+        <v>12046</v>
       </c>
       <c r="B6599" s="5" t="s">
-        <v>12082</v>
+        <v>12057</v>
       </c>
     </row>
     <row r="6600" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6600" s="5" t="s">
-        <v>12075</v>
+        <v>12058</v>
       </c>
       <c r="B6600" s="5" t="s">
-        <v>12083</v>
+        <v>12059</v>
       </c>
     </row>
     <row r="6601" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6601" s="5" t="s">
-        <v>12076</v>
+        <v>12060</v>
       </c>
       <c r="B6601" s="5" t="s">
-        <v>12084</v>
+        <v>12059</v>
       </c>
     </row>
     <row r="6602" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6602" s="5" t="s">
-        <v>12074</v>
+        <v>12061</v>
       </c>
       <c r="B6602" s="5" t="s">
-        <v>12082</v>
+        <v>12065</v>
       </c>
     </row>
     <row r="6603" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6603" s="5" t="s">
-        <v>12077</v>
+        <v>12062</v>
       </c>
       <c r="B6603" s="5" t="s">
-        <v>12085</v>
+        <v>12066</v>
       </c>
     </row>
     <row r="6604" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6604" s="5" t="s">
-        <v>12078</v>
+        <v>12063</v>
       </c>
       <c r="B6604" s="5" t="s">
-        <v>12086</v>
+        <v>12067</v>
       </c>
     </row>
     <row r="6605" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6605" s="5" t="s">
-        <v>12087</v>
+        <v>12064</v>
       </c>
       <c r="B6605" s="5" t="s">
-        <v>12088</v>
+        <v>12068</v>
       </c>
     </row>
     <row r="6606" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6606" s="5" t="s">
-        <v>12089</v>
+      <c r="A6606" s="15" t="s">
+        <v>12069</v>
       </c>
       <c r="B6606" s="5" t="s">
-        <v>12096</v>
+        <v>12070</v>
       </c>
     </row>
     <row r="6607" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6607" s="5" t="s">
-        <v>12090</v>
+      <c r="A6607" s="15" t="s">
+        <v>12071</v>
       </c>
       <c r="B6607" s="5" t="s">
-        <v>12097</v>
+        <v>12079</v>
       </c>
     </row>
     <row r="6608" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6608" s="5" t="s">
-        <v>12091</v>
+      <c r="A6608" s="15" t="s">
+        <v>12072</v>
       </c>
       <c r="B6608" s="5" t="s">
-        <v>12098</v>
+        <v>12080</v>
       </c>
     </row>
     <row r="6609" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6609" s="5" t="s">
-        <v>12092</v>
+      <c r="A6609" s="15" t="s">
+        <v>12073</v>
       </c>
       <c r="B6609" s="5" t="s">
-        <v>12099</v>
+        <v>12081</v>
       </c>
     </row>
     <row r="6610" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6610" s="5" t="s">
-        <v>12093</v>
+      <c r="A6610" s="15" t="s">
+        <v>12074</v>
       </c>
       <c r="B6610" s="5" t="s">
-        <v>12100</v>
+        <v>12082</v>
       </c>
     </row>
     <row r="6611" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6611" s="5" t="s">
-        <v>12094</v>
+      <c r="A6611" s="15" t="s">
+        <v>12075</v>
       </c>
       <c r="B6611" s="5" t="s">
-        <v>12101</v>
+        <v>12083</v>
       </c>
     </row>
     <row r="6612" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6612" s="5" t="s">
-        <v>12095</v>
+      <c r="A6612" s="15" t="s">
+        <v>12076</v>
       </c>
       <c r="B6612" s="5" t="s">
-        <v>12102</v>
+        <v>12084</v>
       </c>
     </row>
     <row r="6613" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6613" s="5" t="s">
-        <v>11683</v>
+      <c r="A6613" s="15" t="s">
+        <v>12074</v>
       </c>
       <c r="B6613" s="5" t="s">
-        <v>11693</v>
+        <v>12082</v>
       </c>
     </row>
     <row r="6614" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6614" s="5" t="s">
-        <v>11682</v>
+      <c r="A6614" s="15" t="s">
+        <v>12077</v>
       </c>
       <c r="B6614" s="5" t="s">
-        <v>11692</v>
+        <v>12085</v>
       </c>
     </row>
     <row r="6615" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6615" s="5" t="s">
-        <v>11684</v>
+      <c r="A6615" s="15" t="s">
+        <v>12078</v>
       </c>
       <c r="B6615" s="5" t="s">
-        <v>11694</v>
+        <v>12086</v>
       </c>
     </row>
     <row r="6616" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6616" s="5" t="s">
-        <v>11681</v>
+        <v>12087</v>
       </c>
       <c r="B6616" s="5" t="s">
-        <v>11691</v>
+        <v>12088</v>
       </c>
     </row>
     <row r="6617" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6617" s="5" t="s">
-        <v>11680</v>
+        <v>12089</v>
       </c>
       <c r="B6617" s="5" t="s">
-        <v>11690</v>
+        <v>12096</v>
       </c>
     </row>
     <row r="6618" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6618" s="5" t="s">
-        <v>11679</v>
+        <v>12090</v>
       </c>
       <c r="B6618" s="5" t="s">
-        <v>11689</v>
+        <v>12097</v>
       </c>
     </row>
     <row r="6619" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6619" s="5" t="s">
-        <v>11678</v>
+        <v>12091</v>
       </c>
       <c r="B6619" s="5" t="s">
-        <v>11688</v>
+        <v>12098</v>
       </c>
     </row>
     <row r="6620" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6620" s="5" t="s">
-        <v>12103</v>
+        <v>12092</v>
       </c>
       <c r="B6620" s="5" t="s">
-        <v>12104</v>
+        <v>12099</v>
       </c>
     </row>
     <row r="6621" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6621" s="5" t="s">
-        <v>12105</v>
+        <v>12093</v>
       </c>
       <c r="B6621" s="5" t="s">
-        <v>12112</v>
+        <v>12100</v>
       </c>
     </row>
     <row r="6622" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6622" s="5" t="s">
-        <v>12106</v>
+        <v>12094</v>
       </c>
       <c r="B6622" s="5" t="s">
-        <v>12113</v>
+        <v>12101</v>
       </c>
     </row>
     <row r="6623" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6623" s="5" t="s">
-        <v>12107</v>
+        <v>12095</v>
       </c>
       <c r="B6623" s="5" t="s">
-        <v>12114</v>
+        <v>12102</v>
       </c>
     </row>
     <row r="6624" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6624" s="5" t="s">
-        <v>12108</v>
+      <c r="A6624" s="15" t="s">
+        <v>11683</v>
       </c>
       <c r="B6624" s="5" t="s">
-        <v>12115</v>
+        <v>11693</v>
       </c>
     </row>
     <row r="6625" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6625" s="5" t="s">
-        <v>12109</v>
+      <c r="A6625" s="15" t="s">
+        <v>11682</v>
       </c>
       <c r="B6625" s="5" t="s">
-        <v>12116</v>
+        <v>11692</v>
       </c>
     </row>
     <row r="6626" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6626" s="5" t="s">
-        <v>12110</v>
+      <c r="A6626" s="15" t="s">
+        <v>11684</v>
       </c>
       <c r="B6626" s="5" t="s">
-        <v>12117</v>
+        <v>11694</v>
       </c>
     </row>
     <row r="6627" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6627" s="5" t="s">
-        <v>12111</v>
+      <c r="A6627" s="15" t="s">
+        <v>11681</v>
       </c>
       <c r="B6627" s="5" t="s">
-        <v>12118</v>
+        <v>11691</v>
       </c>
     </row>
     <row r="6628" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6628" s="5" t="s">
-        <v>12119</v>
+      <c r="A6628" s="15" t="s">
+        <v>11680</v>
       </c>
       <c r="B6628" s="5" t="s">
-        <v>12120</v>
+        <v>11690</v>
       </c>
     </row>
     <row r="6629" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6629" s="5" t="s">
-        <v>12121</v>
+      <c r="A6629" s="15" t="s">
+        <v>11679</v>
       </c>
       <c r="B6629" s="5" t="s">
-        <v>12129</v>
+        <v>11689</v>
       </c>
     </row>
     <row r="6630" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6630" s="5" t="s">
-        <v>12122</v>
+      <c r="A6630" s="15" t="s">
+        <v>11678</v>
       </c>
       <c r="B6630" s="5" t="s">
-        <v>12130</v>
+        <v>11688</v>
       </c>
     </row>
     <row r="6631" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6631" s="5" t="s">
-        <v>12123</v>
+        <v>12103</v>
       </c>
       <c r="B6631" s="5" t="s">
-        <v>12131</v>
+        <v>12104</v>
       </c>
     </row>
     <row r="6632" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6632" s="5" t="s">
-        <v>12124</v>
+        <v>12105</v>
       </c>
       <c r="B6632" s="5" t="s">
-        <v>12132</v>
+        <v>12112</v>
       </c>
     </row>
     <row r="6633" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6633" s="5" t="s">
-        <v>12125</v>
+        <v>12106</v>
       </c>
       <c r="B6633" s="5" t="s">
-        <v>12133</v>
+        <v>12113</v>
       </c>
     </row>
     <row r="6634" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6634" s="5" t="s">
-        <v>12126</v>
+        <v>12107</v>
       </c>
       <c r="B6634" s="5" t="s">
-        <v>12134</v>
+        <v>12114</v>
       </c>
     </row>
     <row r="6635" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6635" s="5" t="s">
-        <v>12127</v>
+        <v>12108</v>
       </c>
       <c r="B6635" s="5" t="s">
-        <v>12135</v>
+        <v>12115</v>
       </c>
     </row>
     <row r="6636" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6636" s="5" t="s">
-        <v>12128</v>
+        <v>12109</v>
       </c>
       <c r="B6636" s="5" t="s">
-        <v>12136</v>
+        <v>12116</v>
       </c>
     </row>
     <row r="6637" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6637" s="5" t="s">
-        <v>12137</v>
+        <v>12110</v>
       </c>
       <c r="B6637" s="5" t="s">
-        <v>12138</v>
+        <v>12117</v>
       </c>
     </row>
     <row r="6638" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6638" s="5" t="s">
-        <v>12139</v>
-      </c>
-      <c r="B6638" s="5" t="s">
-        <v>12158</v>
+        <v>12306</v>
       </c>
     </row>
     <row r="6639" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6639" s="5" t="s">
-        <v>12140</v>
+      <c r="A6639" s="15" t="s">
+        <v>12111</v>
       </c>
       <c r="B6639" s="5" t="s">
-        <v>12159</v>
+        <v>12118</v>
       </c>
     </row>
     <row r="6640" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6640" s="5" t="s">
-        <v>12142</v>
+        <v>12119</v>
       </c>
       <c r="B6640" s="5" t="s">
-        <v>12160</v>
+        <v>12120</v>
       </c>
     </row>
     <row r="6641" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6641" s="5" t="s">
-        <v>12143</v>
+        <v>12121</v>
       </c>
       <c r="B6641" s="5" t="s">
-        <v>12161</v>
+        <v>12129</v>
       </c>
     </row>
     <row r="6642" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6642" s="5" t="s">
-        <v>12144</v>
+        <v>12122</v>
       </c>
       <c r="B6642" s="5" t="s">
-        <v>12162</v>
+        <v>12130</v>
       </c>
     </row>
     <row r="6643" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6643" s="5" t="s">
-        <v>12145</v>
+        <v>12123</v>
       </c>
       <c r="B6643" s="5" t="s">
-        <v>12163</v>
+        <v>12131</v>
       </c>
     </row>
     <row r="6644" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6644" s="5" t="s">
-        <v>12146</v>
+        <v>12124</v>
       </c>
       <c r="B6644" s="5" t="s">
-        <v>12164</v>
+        <v>12132</v>
       </c>
     </row>
     <row r="6645" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6645" s="5" t="s">
-        <v>12147</v>
+        <v>12125</v>
       </c>
       <c r="B6645" s="5" t="s">
-        <v>12165</v>
+        <v>12133</v>
       </c>
     </row>
     <row r="6646" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6646" s="5" t="s">
-        <v>12148</v>
+        <v>12126</v>
       </c>
       <c r="B6646" s="5" t="s">
-        <v>12166</v>
+        <v>12134</v>
       </c>
     </row>
     <row r="6647" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6647" s="5" t="s">
-        <v>12149</v>
+        <v>12127</v>
       </c>
       <c r="B6647" s="5" t="s">
-        <v>12167</v>
+        <v>12135</v>
       </c>
     </row>
     <row r="6648" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6648" s="5" t="s">
-        <v>12150</v>
+        <v>12128</v>
       </c>
       <c r="B6648" s="5" t="s">
-        <v>12168</v>
+        <v>12136</v>
       </c>
     </row>
     <row r="6649" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6649" s="5" t="s">
-        <v>12151</v>
+        <v>12137</v>
       </c>
       <c r="B6649" s="5" t="s">
-        <v>12169</v>
+        <v>12138</v>
       </c>
     </row>
     <row r="6650" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6650" s="5" t="s">
-        <v>12152</v>
+        <v>12139</v>
       </c>
       <c r="B6650" s="5" t="s">
-        <v>12170</v>
+        <v>12158</v>
       </c>
     </row>
     <row r="6651" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6651" s="5" t="s">
-        <v>12153</v>
+        <v>12140</v>
       </c>
       <c r="B6651" s="5" t="s">
-        <v>12171</v>
+        <v>12159</v>
       </c>
     </row>
     <row r="6652" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6652" s="5" t="s">
-        <v>12154</v>
+        <v>12142</v>
       </c>
       <c r="B6652" s="5" t="s">
-        <v>12172</v>
+        <v>12160</v>
       </c>
     </row>
     <row r="6653" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6653" s="5" t="s">
-        <v>12141</v>
+        <v>12143</v>
       </c>
       <c r="B6653" s="5" t="s">
-        <v>12173</v>
+        <v>12161</v>
       </c>
     </row>
     <row r="6654" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6654" s="5" t="s">
-        <v>12155</v>
+        <v>12144</v>
       </c>
       <c r="B6654" s="5" t="s">
-        <v>12174</v>
+        <v>12162</v>
       </c>
     </row>
     <row r="6655" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6655" s="5" t="s">
-        <v>12156</v>
+        <v>12145</v>
       </c>
       <c r="B6655" s="5" t="s">
-        <v>12175</v>
+        <v>12163</v>
       </c>
     </row>
     <row r="6656" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6656" s="5" t="s">
-        <v>12157</v>
+        <v>12146</v>
       </c>
       <c r="B6656" s="5" t="s">
-        <v>12176</v>
+        <v>12164</v>
       </c>
     </row>
     <row r="6657" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6657" s="5" t="s">
-        <v>12177</v>
+        <v>12147</v>
+      </c>
+      <c r="B6657" s="5" t="s">
+        <v>12165</v>
       </c>
     </row>
     <row r="6658" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6658" s="5" t="s">
-        <v>12178</v>
+      <c r="A6658" s="15" t="s">
+        <v>12148</v>
       </c>
       <c r="B6658" s="5" t="s">
-        <v>12179</v>
+        <v>12166</v>
       </c>
     </row>
     <row r="6659" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6659" s="5" t="s">
-        <v>12180</v>
+        <v>12149</v>
       </c>
       <c r="B6659" s="5" t="s">
-        <v>12184</v>
+        <v>12167</v>
       </c>
     </row>
     <row r="6660" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6660" s="5" t="s">
-        <v>12181</v>
+        <v>12150</v>
       </c>
       <c r="B6660" s="5" t="s">
-        <v>12185</v>
+        <v>12168</v>
       </c>
     </row>
     <row r="6661" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6661" s="5" t="s">
-        <v>12182</v>
+        <v>12151</v>
       </c>
       <c r="B6661" s="5" t="s">
-        <v>12186</v>
+        <v>12169</v>
       </c>
     </row>
     <row r="6662" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6662" s="5" t="s">
-        <v>12183</v>
+        <v>12152</v>
       </c>
       <c r="B6662" s="5" t="s">
-        <v>12187</v>
+        <v>12170</v>
       </c>
     </row>
     <row r="6663" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6663" s="5" t="s">
-        <v>12188</v>
+        <v>12153</v>
       </c>
       <c r="B6663" s="5" t="s">
-        <v>12194</v>
+        <v>12171</v>
       </c>
     </row>
     <row r="6664" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6664" s="5" t="s">
-        <v>12189</v>
+        <v>12154</v>
       </c>
       <c r="B6664" s="5" t="s">
-        <v>12195</v>
+        <v>12172</v>
       </c>
     </row>
     <row r="6665" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6665" s="5" t="s">
-        <v>12190</v>
+        <v>12141</v>
       </c>
       <c r="B6665" s="5" t="s">
-        <v>12195</v>
+        <v>12173</v>
       </c>
     </row>
     <row r="6666" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6666" s="5" t="s">
-        <v>12191</v>
+        <v>12155</v>
       </c>
       <c r="B6666" s="5" t="s">
-        <v>12196</v>
+        <v>12174</v>
       </c>
     </row>
     <row r="6667" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6667" s="5" t="s">
-        <v>12192</v>
+        <v>12156</v>
       </c>
       <c r="B6667" s="5" t="s">
-        <v>12197</v>
+        <v>12175</v>
       </c>
     </row>
     <row r="6668" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6668" s="5" t="s">
-        <v>12193</v>
+        <v>12157</v>
       </c>
       <c r="B6668" s="5" t="s">
-        <v>12198</v>
+        <v>12176</v>
       </c>
     </row>
     <row r="6669" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6669" s="5" t="s">
-        <v>12199</v>
-      </c>
-      <c r="B6669" s="5" t="s">
-        <v>12213</v>
+      <c r="A6669" s="15" t="s">
+        <v>12177</v>
       </c>
     </row>
     <row r="6670" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6670" s="5" t="s">
-        <v>12201</v>
+        <v>12178</v>
       </c>
       <c r="B6670" s="5" t="s">
-        <v>12200</v>
+        <v>12179</v>
       </c>
     </row>
     <row r="6671" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6671" s="5" t="s">
-        <v>12202</v>
+        <v>12180</v>
       </c>
       <c r="B6671" s="5" t="s">
-        <v>12214</v>
+        <v>12184</v>
       </c>
     </row>
     <row r="6672" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6672" s="5" t="s">
-        <v>12203</v>
+        <v>12181</v>
       </c>
       <c r="B6672" s="5" t="s">
-        <v>12215</v>
+        <v>12185</v>
       </c>
     </row>
     <row r="6673" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6673" s="5" t="s">
-        <v>12204</v>
+        <v>12182</v>
       </c>
       <c r="B6673" s="5" t="s">
-        <v>12216</v>
+        <v>12186</v>
       </c>
     </row>
     <row r="6674" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6674" s="5" t="s">
-        <v>12205</v>
+        <v>12183</v>
       </c>
       <c r="B6674" s="5" t="s">
-        <v>12217</v>
+        <v>12187</v>
       </c>
     </row>
     <row r="6675" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6675" s="5" t="s">
-        <v>12206</v>
+        <v>12188</v>
       </c>
       <c r="B6675" s="5" t="s">
-        <v>12249</v>
+        <v>12194</v>
       </c>
     </row>
     <row r="6676" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6676" s="5" t="s">
-        <v>12207</v>
+        <v>12189</v>
       </c>
       <c r="B6676" s="5" t="s">
-        <v>12250</v>
+        <v>12195</v>
       </c>
     </row>
     <row r="6677" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6677" s="5" t="s">
-        <v>12208</v>
+        <v>12190</v>
       </c>
       <c r="B6677" s="5" t="s">
-        <v>12251</v>
+        <v>12195</v>
       </c>
     </row>
     <row r="6678" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6678" s="5" t="s">
-        <v>12209</v>
+        <v>12191</v>
       </c>
       <c r="B6678" s="5" t="s">
-        <v>12252</v>
+        <v>12196</v>
       </c>
     </row>
     <row r="6679" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6679" s="5" t="s">
-        <v>12210</v>
+        <v>12192</v>
       </c>
       <c r="B6679" s="5" t="s">
-        <v>12253</v>
+        <v>12197</v>
       </c>
     </row>
     <row r="6680" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6680" s="5" t="s">
-        <v>12211</v>
+        <v>12193</v>
       </c>
       <c r="B6680" s="5" t="s">
-        <v>12254</v>
+        <v>12198</v>
       </c>
     </row>
     <row r="6681" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6681" s="5" t="s">
-        <v>12212</v>
+        <v>12199</v>
       </c>
       <c r="B6681" s="5" t="s">
-        <v>12255</v>
+        <v>12213</v>
       </c>
     </row>
     <row r="6682" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6682" s="5" t="s">
-        <v>12245</v>
+        <v>12201</v>
       </c>
       <c r="B6682" s="5" t="s">
-        <v>12256</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="6683" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6683" s="5" t="s">
-        <v>12246</v>
+        <v>12202</v>
       </c>
       <c r="B6683" s="5" t="s">
-        <v>12257</v>
+        <v>12214</v>
       </c>
     </row>
     <row r="6684" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6684" s="5" t="s">
-        <v>12247</v>
+        <v>12203</v>
       </c>
       <c r="B6684" s="5" t="s">
-        <v>12225</v>
+        <v>12215</v>
       </c>
     </row>
     <row r="6685" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6685" s="5" t="s">
-        <v>12248</v>
+        <v>12204</v>
       </c>
       <c r="B6685" s="5" t="s">
-        <v>12258</v>
+        <v>12216</v>
       </c>
     </row>
     <row r="6686" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6686" s="5" t="s">
-        <v>12218</v>
+        <v>12205</v>
       </c>
       <c r="B6686" s="5" t="s">
-        <v>12219</v>
+        <v>12217</v>
       </c>
     </row>
     <row r="6687" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6687" s="5" t="s">
-        <v>12220</v>
+        <v>12206</v>
       </c>
       <c r="B6687" s="5" t="s">
-        <v>12225</v>
+        <v>12249</v>
       </c>
     </row>
     <row r="6688" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6688" s="5" t="s">
-        <v>12221</v>
-      </c>
-      <c r="B6688" s="5" t="s">
-        <v>12226</v>
+        <v>12207</v>
+      </c>
+      <c r="B6688" s="9" t="s">
+        <v>12250</v>
       </c>
     </row>
     <row r="6689" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6689" s="5" t="s">
-        <v>12222</v>
-      </c>
-      <c r="B6689" s="5" t="s">
-        <v>12227</v>
+        <v>12208</v>
+      </c>
+      <c r="B6689" s="9" t="s">
+        <v>12251</v>
       </c>
     </row>
     <row r="6690" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6690" s="5" t="s">
-        <v>12223</v>
-      </c>
-      <c r="B6690" s="5" t="s">
-        <v>12228</v>
+        <v>12209</v>
+      </c>
+      <c r="B6690" s="9" t="s">
+        <v>12252</v>
       </c>
     </row>
     <row r="6691" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6691" s="5" t="s">
-        <v>12224</v>
-      </c>
-      <c r="B6691" s="5" t="s">
-        <v>12219</v>
+        <v>12210</v>
+      </c>
+      <c r="B6691" s="9" t="s">
+        <v>12253</v>
       </c>
     </row>
     <row r="6692" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6692" s="5" t="s">
-        <v>12229</v>
-      </c>
-      <c r="B6692" s="5" t="s">
-        <v>12219</v>
+        <v>12211</v>
+      </c>
+      <c r="B6692" s="9" t="s">
+        <v>12254</v>
       </c>
     </row>
     <row r="6693" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6693" s="5" t="s">
-        <v>12230</v>
-      </c>
-      <c r="B6693" s="5" t="s">
-        <v>12219</v>
+        <v>12212</v>
+      </c>
+      <c r="B6693" s="9" t="s">
+        <v>12255</v>
       </c>
     </row>
     <row r="6694" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6694" s="5" t="s">
-        <v>12231</v>
-      </c>
-      <c r="B6694" s="5" t="s">
-        <v>12219</v>
+        <v>12245</v>
+      </c>
+      <c r="B6694" s="9" t="s">
+        <v>12256</v>
       </c>
     </row>
     <row r="6695" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6695" s="5" t="s">
-        <v>12232</v>
-      </c>
-      <c r="B6695" s="5" t="s">
-        <v>12219</v>
+        <v>12246</v>
+      </c>
+      <c r="B6695" s="9" t="s">
+        <v>12257</v>
       </c>
     </row>
     <row r="6696" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6696" s="5" t="s">
-        <v>12233</v>
-      </c>
-      <c r="B6696" s="5" t="s">
-        <v>12219</v>
+        <v>12247</v>
+      </c>
+      <c r="B6696" s="9" t="s">
+        <v>12225</v>
       </c>
     </row>
     <row r="6697" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6697" s="5" t="s">
-        <v>12234</v>
-      </c>
-      <c r="B6697" s="5" t="s">
-        <v>12219</v>
+        <v>12248</v>
+      </c>
+      <c r="B6697" s="9" t="s">
+        <v>12258</v>
       </c>
     </row>
     <row r="6698" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6698" s="5" t="s">
-        <v>12235</v>
+        <v>12218</v>
       </c>
       <c r="B6698" s="5" t="s">
-        <v>12240</v>
+        <v>12219</v>
       </c>
     </row>
     <row r="6699" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6699" s="5" t="s">
-        <v>12236</v>
+        <v>12220</v>
       </c>
       <c r="B6699" s="5" t="s">
-        <v>12241</v>
+        <v>12225</v>
       </c>
     </row>
     <row r="6700" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6700" s="5" t="s">
-        <v>12237</v>
+        <v>12221</v>
       </c>
       <c r="B6700" s="5" t="s">
-        <v>12244</v>
+        <v>12226</v>
       </c>
     </row>
     <row r="6701" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6701" s="5" t="s">
-        <v>12238</v>
+        <v>12222</v>
       </c>
       <c r="B6701" s="5" t="s">
-        <v>12242</v>
+        <v>12227</v>
       </c>
     </row>
     <row r="6702" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6702" s="5" t="s">
-        <v>12239</v>
+        <v>12223</v>
       </c>
       <c r="B6702" s="5" t="s">
-        <v>12243</v>
+        <v>12228</v>
       </c>
     </row>
     <row r="6703" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6703" s="5" t="s">
-        <v>12259</v>
-      </c>
-      <c r="B6703" s="5" t="s">
-        <v>12260</v>
+        <v>12224</v>
+      </c>
+      <c r="B6703" s="9" t="s">
+        <v>12219</v>
       </c>
     </row>
     <row r="6704" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6704" s="5" t="s">
-        <v>12261</v>
-      </c>
-      <c r="B6704" s="5" t="s">
-        <v>12269</v>
+        <v>12229</v>
+      </c>
+      <c r="B6704" s="9" t="s">
+        <v>12219</v>
       </c>
     </row>
     <row r="6705" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6705" s="5" t="s">
-        <v>12262</v>
-      </c>
-      <c r="B6705" s="5" t="s">
-        <v>12270</v>
+        <v>12230</v>
+      </c>
+      <c r="B6705" s="9" t="s">
+        <v>12219</v>
       </c>
     </row>
     <row r="6706" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6706" s="5" t="s">
-        <v>12263</v>
-      </c>
-      <c r="B6706" s="5" t="s">
-        <v>12270</v>
+        <v>12231</v>
+      </c>
+      <c r="B6706" s="9" t="s">
+        <v>12219</v>
       </c>
     </row>
     <row r="6707" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6707" s="5" t="s">
-        <v>12264</v>
-      </c>
-      <c r="B6707" s="5" t="s">
-        <v>12271</v>
+        <v>12232</v>
+      </c>
+      <c r="B6707" s="9" t="s">
+        <v>12219</v>
       </c>
     </row>
     <row r="6708" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6708" s="5" t="s">
-        <v>12265</v>
-      </c>
-      <c r="B6708" s="5" t="s">
-        <v>12269</v>
+        <v>12233</v>
+      </c>
+      <c r="B6708" s="9" t="s">
+        <v>12219</v>
       </c>
     </row>
     <row r="6709" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6709" s="5" t="s">
-        <v>12266</v>
-      </c>
-      <c r="B6709" s="5" t="s">
-        <v>12272</v>
+        <v>12234</v>
+      </c>
+      <c r="B6709" s="9" t="s">
+        <v>12219</v>
       </c>
     </row>
     <row r="6710" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6710" s="5" t="s">
-        <v>12267</v>
+        <v>12235</v>
       </c>
       <c r="B6710" s="5" t="s">
-        <v>12273</v>
+        <v>12240</v>
       </c>
     </row>
     <row r="6711" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6711" s="5" t="s">
-        <v>12268</v>
+        <v>12236</v>
       </c>
       <c r="B6711" s="5" t="s">
-        <v>12274</v>
+        <v>12241</v>
       </c>
     </row>
     <row r="6712" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6712" s="5" t="s">
-        <v>12275</v>
+        <v>12237</v>
+      </c>
+      <c r="B6712" s="5" t="s">
+        <v>12244</v>
       </c>
     </row>
     <row r="6713" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6713" s="5" t="s">
-        <v>12276</v>
+        <v>12238</v>
       </c>
       <c r="B6713" s="5" t="s">
-        <v>12277</v>
+        <v>12242</v>
       </c>
     </row>
     <row r="6714" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6714" s="5" t="s">
-        <v>12278</v>
+        <v>12239</v>
       </c>
       <c r="B6714" s="5" t="s">
-        <v>12287</v>
+        <v>12243</v>
       </c>
     </row>
     <row r="6715" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6715" s="5" t="s">
-        <v>12279</v>
+        <v>12259</v>
       </c>
       <c r="B6715" s="5" t="s">
-        <v>12288</v>
+        <v>12260</v>
       </c>
     </row>
     <row r="6716" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6716" s="5" t="s">
-        <v>12280</v>
+        <v>12261</v>
       </c>
       <c r="B6716" s="5" t="s">
-        <v>12289</v>
+        <v>12269</v>
       </c>
     </row>
     <row r="6717" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6717" s="5" t="s">
-        <v>12281</v>
+        <v>12262</v>
       </c>
       <c r="B6717" s="5" t="s">
-        <v>12290</v>
+        <v>12270</v>
       </c>
     </row>
     <row r="6718" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6718" s="5" t="s">
-        <v>12282</v>
+        <v>12263</v>
       </c>
       <c r="B6718" s="5" t="s">
-        <v>12291</v>
+        <v>12270</v>
       </c>
     </row>
     <row r="6719" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6719" s="5" t="s">
-        <v>12283</v>
+        <v>12264</v>
       </c>
       <c r="B6719" s="5" t="s">
-        <v>12292</v>
+        <v>12271</v>
       </c>
     </row>
     <row r="6720" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6720" s="5" t="s">
-        <v>12284</v>
+        <v>12265</v>
       </c>
       <c r="B6720" s="5" t="s">
-        <v>12293</v>
+        <v>12269</v>
       </c>
     </row>
     <row r="6721" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6721" s="5" t="s">
-        <v>12285</v>
+        <v>12266</v>
       </c>
       <c r="B6721" s="5" t="s">
-        <v>12294</v>
+        <v>12272</v>
       </c>
     </row>
     <row r="6722" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6722" s="5" t="s">
-        <v>12286</v>
+        <v>12267</v>
       </c>
       <c r="B6722" s="5" t="s">
-        <v>12295</v>
+        <v>12273</v>
       </c>
     </row>
     <row r="6723" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6723" s="5" t="s">
-        <v>12296</v>
+        <v>12268</v>
       </c>
       <c r="B6723" s="5" t="s">
-        <v>12297</v>
+        <v>12274</v>
       </c>
     </row>
     <row r="6724" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6724" s="5" t="s">
-        <v>12298</v>
-      </c>
-      <c r="B6724" s="5" t="s">
-        <v>12302</v>
+        <v>12275</v>
       </c>
     </row>
     <row r="6725" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6725" s="5" t="s">
-        <v>12299</v>
+        <v>12276</v>
       </c>
       <c r="B6725" s="5" t="s">
-        <v>12303</v>
+        <v>12277</v>
       </c>
     </row>
     <row r="6726" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6726" s="5" t="s">
-        <v>12300</v>
+        <v>12278</v>
       </c>
       <c r="B6726" s="5" t="s">
-        <v>12304</v>
+        <v>12287</v>
       </c>
     </row>
     <row r="6727" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6727" s="5" t="s">
+        <v>12279</v>
+      </c>
+      <c r="B6727" s="5" t="s">
+        <v>12288</v>
+      </c>
+    </row>
+    <row r="6728" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6728" s="5" t="s">
+        <v>12280</v>
+      </c>
+      <c r="B6728" s="5" t="s">
+        <v>12289</v>
+      </c>
+    </row>
+    <row r="6729" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6729" s="5" t="s">
+        <v>12281</v>
+      </c>
+      <c r="B6729" s="5" t="s">
+        <v>12290</v>
+      </c>
+    </row>
+    <row r="6730" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6730" s="5" t="s">
+        <v>12282</v>
+      </c>
+      <c r="B6730" s="5" t="s">
+        <v>12291</v>
+      </c>
+    </row>
+    <row r="6731" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6731" s="5" t="s">
+        <v>12283</v>
+      </c>
+      <c r="B6731" s="5" t="s">
+        <v>12292</v>
+      </c>
+    </row>
+    <row r="6732" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6732" s="5" t="s">
+        <v>12284</v>
+      </c>
+      <c r="B6732" s="5" t="s">
+        <v>12293</v>
+      </c>
+    </row>
+    <row r="6733" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6733" s="5" t="s">
+        <v>12285</v>
+      </c>
+      <c r="B6733" s="5" t="s">
+        <v>12294</v>
+      </c>
+    </row>
+    <row r="6734" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6734" s="5" t="s">
+        <v>12286</v>
+      </c>
+      <c r="B6734" s="5" t="s">
+        <v>12295</v>
+      </c>
+    </row>
+    <row r="6735" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6735" s="5" t="s">
+        <v>12296</v>
+      </c>
+      <c r="B6735" s="5" t="s">
+        <v>12297</v>
+      </c>
+    </row>
+    <row r="6736" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6736" s="5" t="s">
+        <v>12298</v>
+      </c>
+      <c r="B6736" s="5" t="s">
+        <v>12302</v>
+      </c>
+    </row>
+    <row r="6737" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6737" s="5" t="s">
+        <v>12299</v>
+      </c>
+      <c r="B6737" s="5" t="s">
+        <v>12303</v>
+      </c>
+    </row>
+    <row r="6738" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6738" s="5" t="s">
+        <v>12300</v>
+      </c>
+      <c r="B6738" s="5" t="s">
+        <v>12304</v>
+      </c>
+    </row>
+    <row r="6739" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6739" s="5" t="s">
         <v>12301</v>
       </c>
-      <c r="B6727" s="5" t="s">
+      <c r="B6739" s="5" t="s">
         <v>12305</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6375" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:B6386" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B1135">
     <sortCondition ref="A1:A1135"/>
   </sortState>

--- a/словари/переведённые_слова.xlsx
+++ b/словари/переведённые_слова.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Книги\переводчик_книг\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DFFC35-C120-4D04-89FE-AF33E6A6E71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5938A8CE-CFD9-481F-8616-DACD7B2B59AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5940" yWindow="60" windowWidth="18270" windowHeight="14100" tabRatio="831" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13402" uniqueCount="12324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13404" uniqueCount="12324">
   <si>
     <t>Абонемент - подписка</t>
   </si>
@@ -42881,145 +42881,153 @@
         <v>700</v>
       </c>
     </row>
+    <row r="706" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A706" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="B706" s="5" t="s">
+        <v>717</v>
+      </c>
+    </row>
     <row r="707" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="5" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="B707" s="5" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
     </row>
     <row r="708" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="5" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B708" s="5" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
     </row>
     <row r="709" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="5" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="B709" s="5" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
     </row>
     <row r="710" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="5" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B710" s="5" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="711" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="5" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B711" s="5" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="712" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="5" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B712" s="5" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
     </row>
     <row r="713" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="5" t="s">
-        <v>707</v>
-      </c>
-      <c r="B713" s="5" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="714" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="5" t="s">
-        <v>719</v>
+        <v>720</v>
+      </c>
+      <c r="B714" s="5" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="715" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="5" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B715" s="5" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
     </row>
     <row r="716" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="5" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="B716" s="5" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
     </row>
     <row r="717" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="5" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B717" s="5" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="718" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="5" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B718" s="5" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="719" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="5" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="B719" s="5" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
     </row>
     <row r="720" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="5" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="B720" s="5" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
     </row>
     <row r="721" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="5" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="B721" s="5" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
     </row>
     <row r="722" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="5" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B722" s="5" t="s">
-        <v>727</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="723" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="5" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="B723" s="5" t="s">
-        <v>3517</v>
+        <v>734</v>
       </c>
     </row>
     <row r="724" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="5" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B724" s="5" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
     </row>
     <row r="725" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
